--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C466"/>
+  <dimension ref="A1:C478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4562,211 +4562,211 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>报告</v>
+        <v>HDR</v>
       </c>
       <c r="C378" t="str">
-        <v>報告</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>失败</v>
+        <v>代码点</v>
       </c>
       <c r="C379" t="str">
-        <v>失敗</v>
+        <v>代碼點</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>项检查</v>
+        <v>增益曲线</v>
       </c>
       <c r="C380" t="str">
-        <v>項檢查</v>
+        <v>增益曲線</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>色度基色</v>
       </c>
       <c r="C381" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>传递特性</v>
       </c>
       <c r="C382" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C383" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C384" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>订阅</v>
+        <v>全范围</v>
       </c>
       <c r="C385" t="str">
-        <v>訂閱</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>有限范围</v>
       </c>
       <c r="C386" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>订阅新版本通知</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C387" t="str">
-        <v>訂閱新版本通知</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>关闭</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C388" t="str">
-        <v>關閉</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C389" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>电子邮件地址</v>
+        <v>报告</v>
       </c>
       <c r="C390" t="str">
-        <v>電子郵件地址</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>you@example.com</v>
+        <v>失败</v>
       </c>
       <c r="C391" t="str">
-        <v>you@example.com</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>项检查</v>
       </c>
       <c r="C392" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>（选填）</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C393" t="str">
-        <v>（選填）</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C394" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C395" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>取消</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C396" t="str">
-        <v>取消</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="397">
@@ -4782,24 +4782,24 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C398" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C399" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="400">
@@ -4815,733 +4815,865 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>隐私声明</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C401" t="str">
-        <v>隱私聲明</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C402" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C403" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>请检查表单后重试。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C404" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>（选填）</v>
       </c>
       <c r="C405" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>网络错误，请重试。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C406" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>错误：</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C407" t="str">
-        <v>錯誤：</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>转换为 XML</v>
+        <v>取消</v>
       </c>
       <c r="C408" t="str">
-        <v>轉換為 XML</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>转换为 JSON</v>
+        <v>订阅</v>
       </c>
       <c r="C409" t="str">
-        <v>轉換為 JSON</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>转换为 ICC</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C410" t="str">
-        <v>轉換為 ICC</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>正在转换为 XML…</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C411" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>关闭</v>
       </c>
       <c r="C412" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>隐私声明</v>
       </c>
       <c r="C413" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C414" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C415" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>配置文件 ID</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C416" t="str">
-        <v>設定檔 ID</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>未找到标签。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C417" t="str">
-        <v>找不到標籤。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>标签名称</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C418" t="str">
-        <v>標籤名稱</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>错误：</v>
       </c>
       <c r="C419" t="str">
-        <v>ID</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>偏移</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C420" t="str">
-        <v>偏移</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>大小</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C421" t="str">
-        <v>大小</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>填充</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C422" t="str">
-        <v>填充</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>加载后字节已更改</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C423" t="str">
-        <v>載入後位元組已變更</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>类型</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C424" t="str">
-        <v>類型</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>{type} 数组</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C425" t="str">
-        <v>{type} 陣列</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>（无内容）</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C426" t="str">
-        <v>（無內容）</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>字节</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C427" t="str">
-        <v>位元組</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>正在加载完整描述…</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C428" t="str">
-        <v>正在載入完整描述…</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>无法加载完整描述：</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C429" t="str">
-        <v>無法載入完整描述：</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>标签名称</v>
       </c>
       <c r="C430" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>ID</v>
       </c>
       <c r="C431" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>无验证输出</v>
+        <v>偏移</v>
       </c>
       <c r="C432" t="str">
-        <v>無驗證輸出</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>配置文件有效</v>
+        <v>大小</v>
       </c>
       <c r="C433" t="str">
-        <v>設定檔有效</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>配置文件有警告</v>
+        <v>填充</v>
       </c>
       <c r="C434" t="str">
-        <v>設定檔有警告</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>配置文件不合规</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C435" t="str">
-        <v>設定檔不符合規範</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>严重验证错误</v>
+        <v>类型</v>
       </c>
       <c r="C436" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>未知验证状态</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C437" t="str">
-        <v>未知驗證狀態</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>（无内容）</v>
       </c>
       <c r="C438" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>未发现警告或错误。</v>
+        <v>字节</v>
       </c>
       <c r="C439" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>有效</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C440" t="str">
-        <v>有效</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>警告</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C441" t="str">
-        <v>警告</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>错误</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C442" t="str">
-        <v>錯誤</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>未知</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C443" t="str">
-        <v>未知</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>通过</v>
+        <v>无验证输出</v>
       </c>
       <c r="C444" t="str">
-        <v>通過</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>失败</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C445" t="str">
-        <v>失敗</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>在上下文中查看</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C446" t="str">
-        <v>在上下文中檢視</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>验证详情</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C447" t="str">
-        <v>驗證詳情</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>触发字段</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C448" t="str">
-        <v>觸發欄位</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>字段</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C449" t="str">
-        <v>欄位</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>当前值</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C450" t="str">
-        <v>目前值</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>要求：0</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C451" t="str">
-        <v>要求：0</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>预期：{value}</v>
+        <v>有效</v>
       </c>
       <c r="C452" t="str">
-        <v>預期：{value}</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>无效</v>
+        <v>警告</v>
       </c>
       <c r="C453" t="str">
-        <v>無效</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>错误</v>
       </c>
       <c r="C454" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>关闭</v>
+        <v>未知</v>
       </c>
       <c r="C455" t="str">
-        <v>關閉</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>通过</v>
       </c>
       <c r="C456" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>失败</v>
       </c>
       <c r="C457" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C458" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>验证详情</v>
       </c>
       <c r="C459" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>触发字段</v>
       </c>
       <c r="C460" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>字段</v>
       </c>
       <c r="C461" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>当前值</v>
       </c>
       <c r="C462" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>要求：0</v>
       </c>
       <c r="C463" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>缩进</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C464" t="str">
-        <v>縮排</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>排序键</v>
+        <v>无效</v>
       </c>
       <c r="C465" t="str">
-        <v>排序鍵</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C466" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C467" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C468" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C469" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C470" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C471" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C472" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C473" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C474" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C475" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C476" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C477" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C466" t="str">
+      <c r="C478" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C478"/>
+  <dimension ref="A1:C498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4595,1085 +4595,1305 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>色度基色</v>
+        <v>环境</v>
       </c>
       <c r="C381" t="str">
-        <v>色度基色</v>
+        <v>環境</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>传递特性</v>
+        <v>检测中…</v>
       </c>
       <c r="C382" t="str">
-        <v>轉換特性</v>
+        <v>偵測中…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>矩阵系数</v>
+        <v>无法检测环境。</v>
       </c>
       <c r="C383" t="str">
-        <v>矩陣係數</v>
+        <v>無法偵測環境。</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>视频全范围标志</v>
+        <v>HDR 显示器</v>
       </c>
       <c r="C384" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>HDR 顯示器</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>全范围</v>
+        <v>广色域</v>
       </c>
       <c r="C385" t="str">
-        <v>全範圍</v>
+        <v>廣色域</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>有限范围</v>
+        <v>HDR 画布路径</v>
       </c>
       <c r="C386" t="str">
-        <v>有限範圍</v>
+        <v>HDR 畫布路徑</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>sRGB</v>
       </c>
       <c r="C387" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>无</v>
       </c>
       <c r="C388" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>無</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>是</v>
       </c>
       <c r="C389" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>是</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>报告</v>
+        <v>否</v>
       </c>
       <c r="C390" t="str">
-        <v>報告</v>
+        <v>否</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>失败</v>
+        <v>未报告</v>
       </c>
       <c r="C391" t="str">
-        <v>失敗</v>
+        <v>未回報</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>项检查</v>
+        <v>格式</v>
       </c>
       <c r="C392" t="str">
-        <v>項檢查</v>
+        <v>格式</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>检查</v>
       </c>
       <c r="C393" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>檢查</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>显示</v>
       </c>
       <c r="C394" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>顯示</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>HDR</v>
       </c>
       <c r="C395" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>读取嵌入的 ICC 配置文件 — 无需解码器</v>
       </c>
       <c r="C396" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>讀取內嵌的 ICC 設定檔 — 不需解碼器</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>订阅</v>
+        <v>显示像素</v>
       </c>
       <c r="C397" t="str">
-        <v>訂閱</v>
+        <v>顯示像素</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>渲染高于白色的亮度</v>
       </c>
       <c r="C398" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>算繪高於白色的亮度</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>订阅新版本通知</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C399" t="str">
-        <v>訂閱新版本通知</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>关闭</v>
+        <v>浏览器无法报告显示器的 HDR 余量，只能报告是否存在 HDR 路径。</v>
       </c>
       <c r="C400" t="str">
-        <v>關閉</v>
+        <v>瀏覽器無法回報顯示器的 HDR 餘量，只能回報是否存在 HDR 路徑。</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>色度基色</v>
       </c>
       <c r="C401" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>电子邮件地址</v>
+        <v>传递特性</v>
       </c>
       <c r="C402" t="str">
-        <v>電子郵件地址</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>you@example.com</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C403" t="str">
-        <v>you@example.com</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C404" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>（选填）</v>
+        <v>全范围</v>
       </c>
       <c r="C405" t="str">
-        <v>（選填）</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>有限范围</v>
       </c>
       <c r="C406" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C407" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>取消</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C408" t="str">
-        <v>取消</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>订阅</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C409" t="str">
-        <v>訂閱</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>报告</v>
       </c>
       <c r="C410" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>失败</v>
       </c>
       <c r="C411" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>关闭</v>
+        <v>项检查</v>
       </c>
       <c r="C412" t="str">
-        <v>關閉</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>隐私声明</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C413" t="str">
-        <v>隱私聲明</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C414" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C415" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>请检查表单后重试。</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C416" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>订阅</v>
       </c>
       <c r="C417" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>网络错误，请重试。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C418" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>错误：</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C419" t="str">
-        <v>錯誤：</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>转换为 XML</v>
+        <v>关闭</v>
       </c>
       <c r="C420" t="str">
-        <v>轉換為 XML</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>转换为 JSON</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C421" t="str">
-        <v>轉換為 JSON</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>转换为 ICC</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C422" t="str">
-        <v>轉換為 ICC</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>正在转换为 XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="C423" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C424" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>（选填）</v>
       </c>
       <c r="C425" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C426" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C427" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>配置文件 ID</v>
+        <v>取消</v>
       </c>
       <c r="C428" t="str">
-        <v>設定檔 ID</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>未找到标签。</v>
+        <v>订阅</v>
       </c>
       <c r="C429" t="str">
-        <v>找不到標籤。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>标签名称</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C430" t="str">
-        <v>標籤名稱</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C431" t="str">
-        <v>ID</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>偏移</v>
+        <v>关闭</v>
       </c>
       <c r="C432" t="str">
-        <v>偏移</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>大小</v>
+        <v>隐私声明</v>
       </c>
       <c r="C433" t="str">
-        <v>大小</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>填充</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C434" t="str">
-        <v>填充</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>加载后字节已更改</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C435" t="str">
-        <v>載入後位元組已變更</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>类型</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C436" t="str">
-        <v>類型</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>{type} 数组</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C437" t="str">
-        <v>{type} 陣列</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>（无内容）</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C438" t="str">
-        <v>（無內容）</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>字节</v>
+        <v>错误：</v>
       </c>
       <c r="C439" t="str">
-        <v>位元組</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>正在加载完整描述…</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C440" t="str">
-        <v>正在載入完整描述…</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>无法加载完整描述：</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C441" t="str">
-        <v>無法載入完整描述：</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C442" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C443" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>无验证输出</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C444" t="str">
-        <v>無驗證輸出</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>配置文件有效</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C445" t="str">
-        <v>設定檔有效</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>配置文件有警告</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C446" t="str">
-        <v>設定檔有警告</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>配置文件不合规</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C447" t="str">
-        <v>設定檔不符合規範</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C448" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>未知验证状态</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C449" t="str">
-        <v>未知驗證狀態</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>标签名称</v>
       </c>
       <c r="C450" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>未发现警告或错误。</v>
+        <v>ID</v>
       </c>
       <c r="C451" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>有效</v>
+        <v>偏移</v>
       </c>
       <c r="C452" t="str">
-        <v>有效</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>警告</v>
+        <v>大小</v>
       </c>
       <c r="C453" t="str">
-        <v>警告</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>错误</v>
+        <v>填充</v>
       </c>
       <c r="C454" t="str">
-        <v>錯誤</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>未知</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C455" t="str">
-        <v>未知</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>通过</v>
+        <v>类型</v>
       </c>
       <c r="C456" t="str">
-        <v>通過</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>失败</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C457" t="str">
-        <v>失敗</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>在上下文中查看</v>
+        <v>（无内容）</v>
       </c>
       <c r="C458" t="str">
-        <v>在上下文中檢視</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>验证详情</v>
+        <v>字节</v>
       </c>
       <c r="C459" t="str">
-        <v>驗證詳情</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>触发字段</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C460" t="str">
-        <v>觸發欄位</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>字段</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C461" t="str">
-        <v>欄位</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>当前值</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C462" t="str">
-        <v>目前值</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>要求：0</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C463" t="str">
-        <v>要求：0</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>预期：{value}</v>
+        <v>无验证输出</v>
       </c>
       <c r="C464" t="str">
-        <v>預期：{value}</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>无效</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C465" t="str">
-        <v>無效</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C466" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>关闭</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C467" t="str">
-        <v>關閉</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C468" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C469" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C470" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C471" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>有效</v>
       </c>
       <c r="C472" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>警告</v>
       </c>
       <c r="C473" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>错误</v>
       </c>
       <c r="C474" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>未知</v>
       </c>
       <c r="C475" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>缩进</v>
+        <v>通过</v>
       </c>
       <c r="C476" t="str">
-        <v>縮排</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>排序键</v>
+        <v>失败</v>
       </c>
       <c r="C477" t="str">
-        <v>排序鍵</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C478" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C479" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C480" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C481" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C482" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C483" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C484" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C485" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C486" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C487" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C488" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C489" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C490" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C491" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C492" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C493" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C494" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C495" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C496" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C497" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C478" t="str">
+      <c r="C498" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C498"/>
+  <dimension ref="A1:C502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4606,1294 +4606,1338 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>检测中…</v>
+        <v>显示 SDR 回退</v>
       </c>
       <c r="C382" t="str">
-        <v>偵測中…</v>
+        <v>顯示 SDR 回退</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>无法检测环境。</v>
+        <v>链中包含 HDR 配置文件</v>
       </c>
       <c r="C383" t="str">
-        <v>無法偵測環境。</v>
+        <v>鏈中包含 HDR 設定檔</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>HDR 显示器</v>
+        <v>通过 HDR 配置文件的转换会使用其 AToB0Tag——即 8.10.6 条款要求的固化 SDR 渲染——因为 8.10.1 条款不允许其包含 TRC 标签。结果是该回退，而非 HDR 行为。</v>
       </c>
       <c r="C384" t="str">
-        <v>HDR 顯示器</v>
+        <v>透過 HDR 設定檔的轉換會使用其 AToB0Tag——即 8.10.6 條款要求的固化 SDR 算繪——因為 8.10.1 條款不允許其包含 TRC 標籤。結果是該回退，而非 HDR 行為。</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>广色域</v>
+        <v>这些是 HDR 配置文件，不含 TRC 标签，因此色域由 AToB0Tag 构建——即 8.10.6 条款要求为无 HDR 处理的消费者提供的固化 SDR 渲染。这不是配置文件的 HDR 色域，后者无法在有界 PCS 中绘制。</v>
       </c>
       <c r="C385" t="str">
-        <v>廣色域</v>
+        <v>這些是 HDR 設定檔，不含 TRC 標籤，因此色域由 AToB0Tag 建構——即 8.10.6 條款要求為無 HDR 處理的消費者提供的固化 SDR 算繪。這不是設定檔的 HDR 色域，後者無法在有界 PCS 中繪製。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>HDR 画布路径</v>
+        <v>检测中…</v>
       </c>
       <c r="C386" t="str">
-        <v>HDR 畫布路徑</v>
+        <v>偵測中…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>无法检测环境。</v>
       </c>
       <c r="C387" t="str">
-        <v>sRGB</v>
+        <v>無法偵測環境。</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>无</v>
+        <v>HDR 显示器</v>
       </c>
       <c r="C388" t="str">
-        <v>無</v>
+        <v>HDR 顯示器</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>是</v>
+        <v>广色域</v>
       </c>
       <c r="C389" t="str">
-        <v>是</v>
+        <v>廣色域</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>否</v>
+        <v>HDR 画布路径</v>
       </c>
       <c r="C390" t="str">
-        <v>否</v>
+        <v>HDR 畫布路徑</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>未报告</v>
+        <v>sRGB</v>
       </c>
       <c r="C391" t="str">
-        <v>未回報</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>格式</v>
+        <v>无</v>
       </c>
       <c r="C392" t="str">
-        <v>格式</v>
+        <v>無</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>检查</v>
+        <v>是</v>
       </c>
       <c r="C393" t="str">
-        <v>檢查</v>
+        <v>是</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>显示</v>
+        <v>否</v>
       </c>
       <c r="C394" t="str">
-        <v>顯示</v>
+        <v>否</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>未报告</v>
       </c>
       <c r="C395" t="str">
-        <v>HDR</v>
+        <v>未回報</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>读取嵌入的 ICC 配置文件 — 无需解码器</v>
+        <v>格式</v>
       </c>
       <c r="C396" t="str">
-        <v>讀取內嵌的 ICC 設定檔 — 不需解碼器</v>
+        <v>格式</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>显示像素</v>
+        <v>检查</v>
       </c>
       <c r="C397" t="str">
-        <v>顯示像素</v>
+        <v>檢查</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>渲染高于白色的亮度</v>
+        <v>显示</v>
       </c>
       <c r="C398" t="str">
-        <v>算繪高於白色的亮度</v>
+        <v>顯示</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>由 profiletool 自行解码，因此与浏览器无关</v>
+        <v>HDR</v>
       </c>
       <c r="C399" t="str">
-        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>浏览器无法报告显示器的 HDR 余量，只能报告是否存在 HDR 路径。</v>
+        <v>读取嵌入的 ICC 配置文件 — 无需解码器</v>
       </c>
       <c r="C400" t="str">
-        <v>瀏覽器無法回報顯示器的 HDR 餘量，只能回報是否存在 HDR 路徑。</v>
+        <v>讀取內嵌的 ICC 設定檔 — 不需解碼器</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>色度基色</v>
+        <v>显示像素</v>
       </c>
       <c r="C401" t="str">
-        <v>色度基色</v>
+        <v>顯示像素</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>传递特性</v>
+        <v>渲染高于白色的亮度</v>
       </c>
       <c r="C402" t="str">
-        <v>轉換特性</v>
+        <v>算繪高於白色的亮度</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>矩阵系数</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C403" t="str">
-        <v>矩陣係數</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>视频全范围标志</v>
+        <v>浏览器无法报告显示器的 HDR 余量，只能报告是否存在 HDR 路径。</v>
       </c>
       <c r="C404" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>瀏覽器無法回報顯示器的 HDR 餘量，只能回報是否存在 HDR 路徑。</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>全范围</v>
+        <v>色度基色</v>
       </c>
       <c r="C405" t="str">
-        <v>全範圍</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>有限范围</v>
+        <v>传递特性</v>
       </c>
       <c r="C406" t="str">
-        <v>有限範圍</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C407" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C408" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>全范围</v>
       </c>
       <c r="C409" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>报告</v>
+        <v>有限范围</v>
       </c>
       <c r="C410" t="str">
-        <v>報告</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>失败</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C411" t="str">
-        <v>失敗</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>项检查</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C412" t="str">
-        <v>項檢查</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C413" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>报告</v>
       </c>
       <c r="C414" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>失败</v>
       </c>
       <c r="C415" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>项检查</v>
       </c>
       <c r="C416" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>订阅</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C417" t="str">
-        <v>訂閱</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C418" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>订阅新版本通知</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C419" t="str">
-        <v>訂閱新版本通知</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>关闭</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C420" t="str">
-        <v>關閉</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>订阅</v>
       </c>
       <c r="C421" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>电子邮件地址</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C422" t="str">
-        <v>電子郵件地址</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>you@example.com</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C423" t="str">
-        <v>you@example.com</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>关闭</v>
       </c>
       <c r="C424" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>（选填）</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C425" t="str">
-        <v>（選填）</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C426" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C427" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>取消</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C428" t="str">
-        <v>取消</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>订阅</v>
+        <v>（选填）</v>
       </c>
       <c r="C429" t="str">
-        <v>訂閱</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C430" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C431" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>关闭</v>
+        <v>取消</v>
       </c>
       <c r="C432" t="str">
-        <v>關閉</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>隐私声明</v>
+        <v>订阅</v>
       </c>
       <c r="C433" t="str">
-        <v>隱私聲明</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C434" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C435" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>请检查表单后重试。</v>
+        <v>关闭</v>
       </c>
       <c r="C436" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C437" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>网络错误，请重试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C438" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>错误：</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C439" t="str">
-        <v>錯誤：</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>转换为 XML</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C440" t="str">
-        <v>轉換為 XML</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>转换为 JSON</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C441" t="str">
-        <v>轉換為 JSON</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>转换为 ICC</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C442" t="str">
-        <v>轉換為 ICC</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>正在转换为 XML…</v>
+        <v>错误：</v>
       </c>
       <c r="C443" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C444" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C445" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C446" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C447" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>配置文件 ID</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C448" t="str">
-        <v>設定檔 ID</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>未找到标签。</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C449" t="str">
-        <v>找不到標籤。</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>标签名称</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C450" t="str">
-        <v>標籤名稱</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C451" t="str">
-        <v>ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>偏移</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C452" t="str">
-        <v>偏移</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>大小</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C453" t="str">
-        <v>大小</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>填充</v>
+        <v>标签名称</v>
       </c>
       <c r="C454" t="str">
-        <v>填充</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>加载后字节已更改</v>
+        <v>ID</v>
       </c>
       <c r="C455" t="str">
-        <v>載入後位元組已變更</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>类型</v>
+        <v>偏移</v>
       </c>
       <c r="C456" t="str">
-        <v>類型</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>{type} 数组</v>
+        <v>大小</v>
       </c>
       <c r="C457" t="str">
-        <v>{type} 陣列</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>（无内容）</v>
+        <v>填充</v>
       </c>
       <c r="C458" t="str">
-        <v>（無內容）</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>字节</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C459" t="str">
-        <v>位元組</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>正在加载完整描述…</v>
+        <v>类型</v>
       </c>
       <c r="C460" t="str">
-        <v>正在載入完整描述…</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>无法加载完整描述：</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C461" t="str">
-        <v>無法載入完整描述：</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>（无内容）</v>
       </c>
       <c r="C462" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>字节</v>
       </c>
       <c r="C463" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>无验证输出</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C464" t="str">
-        <v>無驗證輸出</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>配置文件有效</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C465" t="str">
-        <v>設定檔有效</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>配置文件有警告</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C466" t="str">
-        <v>設定檔有警告</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>配置文件不合规</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C467" t="str">
-        <v>設定檔不符合規範</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>严重验证错误</v>
+        <v>无验证输出</v>
       </c>
       <c r="C468" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>未知验证状态</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C469" t="str">
-        <v>未知驗證狀態</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C470" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>未发现警告或错误。</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C471" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>有效</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C472" t="str">
-        <v>有效</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>警告</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C473" t="str">
-        <v>警告</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>错误</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C474" t="str">
-        <v>錯誤</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>未知</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C475" t="str">
-        <v>未知</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>通过</v>
+        <v>有效</v>
       </c>
       <c r="C476" t="str">
-        <v>通過</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>失败</v>
+        <v>警告</v>
       </c>
       <c r="C477" t="str">
-        <v>失敗</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>在上下文中查看</v>
+        <v>错误</v>
       </c>
       <c r="C478" t="str">
-        <v>在上下文中檢視</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>验证详情</v>
+        <v>未知</v>
       </c>
       <c r="C479" t="str">
-        <v>驗證詳情</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>触发字段</v>
+        <v>通过</v>
       </c>
       <c r="C480" t="str">
-        <v>觸發欄位</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>字段</v>
+        <v>失败</v>
       </c>
       <c r="C481" t="str">
-        <v>欄位</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>当前值</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C482" t="str">
-        <v>目前值</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>要求：0</v>
+        <v>验证详情</v>
       </c>
       <c r="C483" t="str">
-        <v>要求：0</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>预期：{value}</v>
+        <v>触发字段</v>
       </c>
       <c r="C484" t="str">
-        <v>預期：{value}</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>无效</v>
+        <v>字段</v>
       </c>
       <c r="C485" t="str">
-        <v>無效</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>当前值</v>
       </c>
       <c r="C486" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>关闭</v>
+        <v>要求：0</v>
       </c>
       <c r="C487" t="str">
-        <v>關閉</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C488" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>无效</v>
       </c>
       <c r="C489" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C490" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>关闭</v>
       </c>
       <c r="C491" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C492" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C493" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C494" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C495" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>缩进</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C496" t="str">
-        <v>縮排</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>排序键</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C497" t="str">
-        <v>排序鍵</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C498" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C499" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C500" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C501" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C498" t="str">
+      <c r="C502" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C502"/>
+  <dimension ref="A1:C512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4859,1085 +4859,1195 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>色度基色</v>
+        <v>浏览器标志</v>
       </c>
       <c r="C405" t="str">
-        <v>色度基色</v>
+        <v>瀏覽器旗標</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>传递特性</v>
+        <v>已开启</v>
       </c>
       <c r="C406" t="str">
-        <v>轉換特性</v>
+        <v>已開啟</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>矩阵系数</v>
+        <v>未开启</v>
       </c>
       <c r="C407" t="str">
-        <v>矩陣係數</v>
+        <v>未開啟</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>视频全范围标志</v>
+        <v>此处无法检测</v>
       </c>
       <c r="C408" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>此處無法偵測</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>全范围</v>
+        <v>此浏览器进行 HDR 渲染所必需：没有 WebGPU 时，HDR 画布是唯一途径。配置文件检查不受影响。</v>
       </c>
       <c r="C409" t="str">
-        <v>全範圍</v>
+        <v>此瀏覽器進行 HDR 算繪所必需：沒有 WebGPU 時，HDR 畫布是唯一途徑。設定檔檢查不受影響。</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>有限范围</v>
+        <v>可选：HDR 可通过 WebGPU 渲染，但开启后会增加 HDR 画布途径，并让 profiletool 读取屏幕的真实 HDR 余量。</v>
       </c>
       <c r="C410" t="str">
-        <v>有限範圍</v>
+        <v>選用：HDR 可透過 WebGPU 算繪，但開啟後會增加 HDR 畫布途徑，並讓 profiletool 讀取螢幕的真實 HDR 餘量。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>网页无法打开标志页面。请将其粘贴到地址栏，设为 Enabled，然后重启浏览器。</v>
       </c>
       <c r="C411" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>網頁無法開啟旗標頁面。請將其貼到網址列，設為 Enabled，然後重新啟動瀏覽器。</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>复制</v>
       </c>
       <c r="C412" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>複製</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>已复制</v>
       </c>
       <c r="C413" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>已複製</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>报告</v>
+        <v>复制失败 — 请选中地址并复制。</v>
       </c>
       <c r="C414" t="str">
-        <v>報告</v>
+        <v>複製失敗 — 請選取網址並複製。</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>失败</v>
+        <v>色度基色</v>
       </c>
       <c r="C415" t="str">
-        <v>失敗</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>项检查</v>
+        <v>传递特性</v>
       </c>
       <c r="C416" t="str">
-        <v>項檢查</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C417" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C418" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>全范围</v>
       </c>
       <c r="C419" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>有限范围</v>
       </c>
       <c r="C420" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>订阅</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C421" t="str">
-        <v>訂閱</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C422" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>订阅新版本通知</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C423" t="str">
-        <v>訂閱新版本通知</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>关闭</v>
+        <v>报告</v>
       </c>
       <c r="C424" t="str">
-        <v>關閉</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>失败</v>
       </c>
       <c r="C425" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>电子邮件地址</v>
+        <v>项检查</v>
       </c>
       <c r="C426" t="str">
-        <v>電子郵件地址</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>you@example.com</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C427" t="str">
-        <v>you@example.com</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C428" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>（选填）</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C429" t="str">
-        <v>（選填）</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C430" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>订阅</v>
       </c>
       <c r="C431" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>取消</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C432" t="str">
-        <v>取消</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>订阅</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C433" t="str">
-        <v>訂閱</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>关闭</v>
       </c>
       <c r="C434" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C435" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>关闭</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C436" t="str">
-        <v>關閉</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>隐私声明</v>
+        <v>you@example.com</v>
       </c>
       <c r="C437" t="str">
-        <v>隱私聲明</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C438" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>（选填）</v>
       </c>
       <c r="C439" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>请检查表单后重试。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C440" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C441" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>网络错误，请重试。</v>
+        <v>取消</v>
       </c>
       <c r="C442" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>错误：</v>
+        <v>订阅</v>
       </c>
       <c r="C443" t="str">
-        <v>錯誤：</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>转换为 XML</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C444" t="str">
-        <v>轉換為 XML</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>转换为 JSON</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C445" t="str">
-        <v>轉換為 JSON</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>转换为 ICC</v>
+        <v>关闭</v>
       </c>
       <c r="C446" t="str">
-        <v>轉換為 ICC</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>正在转换为 XML…</v>
+        <v>隐私声明</v>
       </c>
       <c r="C447" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C448" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C449" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C450" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C451" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>配置文件 ID</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C452" t="str">
-        <v>設定檔 ID</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>未找到标签。</v>
+        <v>错误：</v>
       </c>
       <c r="C453" t="str">
-        <v>找不到標籤。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>标签名称</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C454" t="str">
-        <v>標籤名稱</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C455" t="str">
-        <v>ID</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>偏移</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C456" t="str">
-        <v>偏移</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>大小</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C457" t="str">
-        <v>大小</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>填充</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C458" t="str">
-        <v>填充</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>加载后字节已更改</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C459" t="str">
-        <v>載入後位元組已變更</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>类型</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C460" t="str">
-        <v>類型</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>{type} 数组</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C461" t="str">
-        <v>{type} 陣列</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>（无内容）</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C462" t="str">
-        <v>（無內容）</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>字节</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C463" t="str">
-        <v>位元組</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>正在加载完整描述…</v>
+        <v>标签名称</v>
       </c>
       <c r="C464" t="str">
-        <v>正在載入完整描述…</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>无法加载完整描述：</v>
+        <v>ID</v>
       </c>
       <c r="C465" t="str">
-        <v>無法載入完整描述：</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>偏移</v>
       </c>
       <c r="C466" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>大小</v>
       </c>
       <c r="C467" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>无验证输出</v>
+        <v>填充</v>
       </c>
       <c r="C468" t="str">
-        <v>無驗證輸出</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>配置文件有效</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C469" t="str">
-        <v>設定檔有效</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>配置文件有警告</v>
+        <v>类型</v>
       </c>
       <c r="C470" t="str">
-        <v>設定檔有警告</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>配置文件不合规</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C471" t="str">
-        <v>設定檔不符合規範</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>严重验证错误</v>
+        <v>（无内容）</v>
       </c>
       <c r="C472" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>未知验证状态</v>
+        <v>字节</v>
       </c>
       <c r="C473" t="str">
-        <v>未知驗證狀態</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C474" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>未发现警告或错误。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C475" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>有效</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C476" t="str">
-        <v>有效</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>警告</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C477" t="str">
-        <v>警告</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>错误</v>
+        <v>无验证输出</v>
       </c>
       <c r="C478" t="str">
-        <v>錯誤</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>未知</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C479" t="str">
-        <v>未知</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>通过</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C480" t="str">
-        <v>通過</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>失败</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C481" t="str">
-        <v>失敗</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>在上下文中查看</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C482" t="str">
-        <v>在上下文中檢視</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>验证详情</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C483" t="str">
-        <v>驗證詳情</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>触发字段</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C484" t="str">
-        <v>觸發欄位</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>字段</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C485" t="str">
-        <v>欄位</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>当前值</v>
+        <v>有效</v>
       </c>
       <c r="C486" t="str">
-        <v>目前值</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>要求：0</v>
+        <v>警告</v>
       </c>
       <c r="C487" t="str">
-        <v>要求：0</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>预期：{value}</v>
+        <v>错误</v>
       </c>
       <c r="C488" t="str">
-        <v>預期：{value}</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>无效</v>
+        <v>未知</v>
       </c>
       <c r="C489" t="str">
-        <v>無效</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>通过</v>
       </c>
       <c r="C490" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>关闭</v>
+        <v>失败</v>
       </c>
       <c r="C491" t="str">
-        <v>關閉</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C492" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>验证详情</v>
       </c>
       <c r="C493" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>触发字段</v>
       </c>
       <c r="C494" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>字段</v>
       </c>
       <c r="C495" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>当前值</v>
       </c>
       <c r="C496" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>要求：0</v>
       </c>
       <c r="C497" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C498" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>无效</v>
       </c>
       <c r="C499" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>缩进</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C500" t="str">
-        <v>縮排</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>排序键</v>
+        <v>关闭</v>
       </c>
       <c r="C501" t="str">
-        <v>排序鍵</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C502" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C503" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C504" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C505" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C506" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C507" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C508" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C509" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C510" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C511" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C502" t="str">
+      <c r="C512" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C512"/>
+  <dimension ref="A1:C529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4848,13 +4848,13 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>浏览器无法报告显示器的 HDR 余量，只能报告是否存在 HDR 路径。</v>
+        <v>此浏览器未报告显示器的 HDR 余量，只报告了是否存在 HDR 路径。</v>
       </c>
       <c r="C404" t="str">
-        <v>瀏覽器無法回報顯示器的 HDR 餘量，只能回報是否存在 HDR 路徑。</v>
+        <v>此瀏覽器未回報顯示器的 HDR 餘量，只回報了是否存在 HDR 路徑。</v>
       </c>
     </row>
     <row r="405">
@@ -4969,1085 +4969,1272 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>色度基色</v>
+        <v>像素比</v>
       </c>
       <c r="C415" t="str">
-        <v>色度基色</v>
+        <v>像素比</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>传递特性</v>
+        <v>当前显示器</v>
       </c>
       <c r="C416" t="str">
-        <v>轉換特性</v>
+        <v>目前顯示器</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>矩阵系数</v>
+        <v>未命名</v>
       </c>
       <c r="C417" t="str">
-        <v>矩陣係數</v>
+        <v>未命名</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>视频全范围标志</v>
+        <v>主显示器</v>
       </c>
       <c r="C418" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>主顯示器</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>全范围</v>
+        <v>内置</v>
       </c>
       <c r="C419" t="str">
-        <v>全範圍</v>
+        <v>內建</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>有限范围</v>
+        <v>HDR 余量</v>
       </c>
       <c r="C420" t="str">
-        <v>有限範圍</v>
+        <v>HDR 餘量</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>此浏览器未提供</v>
       </c>
       <c r="C421" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>此瀏覽器未提供</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>按浏览器报告的原值显示。单位尚未标准化；曾观察到 SDR 屏幕报告为 0。</v>
       </c>
       <c r="C422" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>依瀏覽器回報的原值顯示。單位尚未標準化；曾觀察到 SDR 螢幕回報為 0。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C423" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>报告</v>
+        <v>识别显示器</v>
       </c>
       <c r="C424" t="str">
-        <v>報告</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>失败</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C425" t="str">
-        <v>失敗</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>项检查</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C426" t="str">
-        <v>項檢查</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C427" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C428" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C429" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>显示事件</v>
       </c>
       <c r="C430" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>订阅</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C431" t="str">
-        <v>訂閱</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>色度基色</v>
       </c>
       <c r="C432" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>订阅新版本通知</v>
+        <v>传递特性</v>
       </c>
       <c r="C433" t="str">
-        <v>訂閱新版本通知</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>关闭</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C434" t="str">
-        <v>關閉</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C435" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>电子邮件地址</v>
+        <v>全范围</v>
       </c>
       <c r="C436" t="str">
-        <v>電子郵件地址</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>you@example.com</v>
+        <v>有限范围</v>
       </c>
       <c r="C437" t="str">
-        <v>you@example.com</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C438" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>（选填）</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C439" t="str">
-        <v>（選填）</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C440" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>报告</v>
       </c>
       <c r="C441" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>取消</v>
+        <v>失败</v>
       </c>
       <c r="C442" t="str">
-        <v>取消</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>订阅</v>
+        <v>项检查</v>
       </c>
       <c r="C443" t="str">
-        <v>訂閱</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C444" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C445" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>关闭</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C446" t="str">
-        <v>關閉</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>隐私声明</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C447" t="str">
-        <v>隱私聲明</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>订阅</v>
       </c>
       <c r="C448" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C449" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>请检查表单后重试。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C450" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>关闭</v>
       </c>
       <c r="C451" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>网络错误，请重试。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C452" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>错误：</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C453" t="str">
-        <v>錯誤：</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>转换为 XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="C454" t="str">
-        <v>轉換為 XML</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>转换为 JSON</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C455" t="str">
-        <v>轉換為 JSON</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>转换为 ICC</v>
+        <v>（选填）</v>
       </c>
       <c r="C456" t="str">
-        <v>轉換為 ICC</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>正在转换为 XML…</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C457" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C458" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>取消</v>
       </c>
       <c r="C459" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>订阅</v>
       </c>
       <c r="C460" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C461" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>配置文件 ID</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C462" t="str">
-        <v>設定檔 ID</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>未找到标签。</v>
+        <v>关闭</v>
       </c>
       <c r="C463" t="str">
-        <v>找不到標籤。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>标签名称</v>
+        <v>隐私声明</v>
       </c>
       <c r="C464" t="str">
-        <v>標籤名稱</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C465" t="str">
-        <v>ID</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>偏移</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C466" t="str">
-        <v>偏移</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>大小</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C467" t="str">
-        <v>大小</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>填充</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C468" t="str">
-        <v>填充</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>加载后字节已更改</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C469" t="str">
-        <v>載入後位元組已變更</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>类型</v>
+        <v>错误：</v>
       </c>
       <c r="C470" t="str">
-        <v>類型</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>{type} 数组</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C471" t="str">
-        <v>{type} 陣列</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>（无内容）</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C472" t="str">
-        <v>（無內容）</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>字节</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C473" t="str">
-        <v>位元組</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>正在加载完整描述…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C474" t="str">
-        <v>正在載入完整描述…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C475" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C476" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C477" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>无验证输出</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C478" t="str">
-        <v>無驗證輸出</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>配置文件有效</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C479" t="str">
-        <v>設定檔有效</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>配置文件有警告</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C480" t="str">
-        <v>設定檔有警告</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>配置文件不合规</v>
+        <v>标签名称</v>
       </c>
       <c r="C481" t="str">
-        <v>設定檔不符合規範</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>严重验证错误</v>
+        <v>ID</v>
       </c>
       <c r="C482" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>未知验证状态</v>
+        <v>偏移</v>
       </c>
       <c r="C483" t="str">
-        <v>未知驗證狀態</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>大小</v>
       </c>
       <c r="C484" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>未发现警告或错误。</v>
+        <v>填充</v>
       </c>
       <c r="C485" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>有效</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C486" t="str">
-        <v>有效</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>警告</v>
+        <v>类型</v>
       </c>
       <c r="C487" t="str">
-        <v>警告</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>错误</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C488" t="str">
-        <v>錯誤</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>未知</v>
+        <v>（无内容）</v>
       </c>
       <c r="C489" t="str">
-        <v>未知</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>通过</v>
+        <v>字节</v>
       </c>
       <c r="C490" t="str">
-        <v>通過</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>失败</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C491" t="str">
-        <v>失敗</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>在上下文中查看</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C492" t="str">
-        <v>在上下文中檢視</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>验证详情</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C493" t="str">
-        <v>驗證詳情</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>触发字段</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C494" t="str">
-        <v>觸發欄位</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>字段</v>
+        <v>无验证输出</v>
       </c>
       <c r="C495" t="str">
-        <v>欄位</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>当前值</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C496" t="str">
-        <v>目前值</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>要求：0</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C497" t="str">
-        <v>要求：0</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>预期：{value}</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C498" t="str">
-        <v>預期：{value}</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>无效</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C499" t="str">
-        <v>無效</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C500" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>关闭</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C501" t="str">
-        <v>關閉</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C502" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>有效</v>
       </c>
       <c r="C503" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>警告</v>
       </c>
       <c r="C504" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>错误</v>
       </c>
       <c r="C505" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>未知</v>
       </c>
       <c r="C506" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>通过</v>
       </c>
       <c r="C507" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>失败</v>
       </c>
       <c r="C508" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C509" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>缩进</v>
+        <v>验证详情</v>
       </c>
       <c r="C510" t="str">
-        <v>縮排</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>排序键</v>
+        <v>触发字段</v>
       </c>
       <c r="C511" t="str">
-        <v>排序鍵</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C512" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C513" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C514" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C515" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C516" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C517" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C518" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C519" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C520" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C521" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C522" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C523" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C524" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C525" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C526" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C527" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C528" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C512" t="str">
+      <c r="C529" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C529"/>
+  <dimension ref="A1:C530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5046,1195 +5046,1206 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>按浏览器报告的原值显示。单位尚未标准化；曾观察到 SDR 屏幕报告为 0。</v>
+        <v>Chromium 以“档”（stop）报告：显示器峰值亮度 ÷ SDR 白电平的 log₂。在 Windows 上，仅当 Chrome 重新读取显示器（窗口移到另一屏幕或 Chrome 重新激活）时才会刷新，调节亮度不会刷新。</v>
       </c>
       <c r="C422" t="str">
-        <v>依瀏覽器回報的原值顯示。單位尚未標準化；曾觀察到 SDR 螢幕回報為 0。</v>
+        <v>Chromium 以「檔」（stop）回報：顯示器峰值亮度 ÷ SDR 白色準位的 log₂。在 Windows 上，僅當 Chrome 重新讀取顯示器（視窗移到另一螢幕或 Chrome 重新啟用）時才會更新，調整亮度不會更新。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>{stops} 档（≈ SDR 白的 {ratio} 倍）</v>
       </c>
       <c r="C423" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>{stops} 檔（≈ SDR 白的 {ratio} 倍）</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>识别显示器</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C424" t="str">
-        <v>識別顯示器</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C425" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C426" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C427" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C428" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>无法识别显示器。</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C429" t="str">
-        <v>無法識別顯示器。</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>显示事件</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C430" t="str">
-        <v>顯示事件</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>显示事件</v>
       </c>
       <c r="C431" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>色度基色</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C432" t="str">
-        <v>色度基色</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>传递特性</v>
+        <v>色度基色</v>
       </c>
       <c r="C433" t="str">
-        <v>轉換特性</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>矩阵系数</v>
+        <v>传递特性</v>
       </c>
       <c r="C434" t="str">
-        <v>矩陣係數</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>视频全范围标志</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C435" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>全范围</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C436" t="str">
-        <v>全範圍</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>有限范围</v>
+        <v>全范围</v>
       </c>
       <c r="C437" t="str">
-        <v>有限範圍</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>有限范围</v>
       </c>
       <c r="C438" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C439" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C440" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>报告</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C441" t="str">
-        <v>報告</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C442" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C443" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C444" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C445" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C446" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C447" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C448" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C449" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C450" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C451" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C452" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C453" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C454" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C455" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C456" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C457" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C458" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C459" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C460" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C461" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C462" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C463" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C464" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C465" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C466" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C467" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C468" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C469" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C470" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C471" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C472" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C473" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C474" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C475" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C476" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C477" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C478" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C479" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C480" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C481" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C482" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C483" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C484" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C485" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C486" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C487" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C488" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C489" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C490" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C491" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C492" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C493" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C494" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C495" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C496" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C497" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C498" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C499" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C500" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C501" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C502" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C503" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C504" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C505" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C506" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C507" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C508" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C509" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C510" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C511" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C512" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C513" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C514" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C515" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C516" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C517" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C518" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C519" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C520" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C521" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C522" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C523" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C524" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C525" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C526" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C527" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C528" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C529" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C529" t="str">
+      <c r="C530" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C530"/>
+  <dimension ref="A1:C595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5068,1184 +5068,1899 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>HDR</v>
       </c>
       <c r="C424" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>识别显示器</v>
+        <v>指定显示余量下的增益</v>
       </c>
       <c r="C425" t="str">
-        <v>識別顯示器</v>
+        <v>指定顯示餘量下的增益</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>在此显示器上查看一张 HDR 图像。浏览器能解码的文件由浏览器自身显示；OpenEXR 由 profiletool 解码并渲染。</v>
       </c>
       <c r="C426" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>在此顯示器上檢視一張 HDR 影像。瀏覽器能解碼的檔案由瀏覽器自行顯示；OpenEXR 由 profiletool 解碼並算繪。</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>将 HDR 图像拖放到此处，或点击选择</v>
       </c>
       <c r="C427" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>將 HDR 影像拖放到此處，或按一下選擇</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>OpenEXR、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
       </c>
       <c r="C428" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>OpenEXR、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>另选一张</v>
       </c>
       <c r="C429" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>另選一張</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>无法识别显示器。</v>
+        <v>清除</v>
       </c>
       <c r="C430" t="str">
-        <v>無法識別顯示器。</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>显示事件</v>
+        <v>嵌入的 ICC 配置文件</v>
       </c>
       <c r="C431" t="str">
-        <v>顯示事件</v>
+        <v>嵌入的 ICC 描述檔</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>无——OpenEXR 通过色度坐标描述颜色</v>
       </c>
       <c r="C432" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>無——OpenEXR 以色度座標描述色彩</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>色度基色</v>
+        <v>正在检查…</v>
       </c>
       <c r="C433" t="str">
-        <v>色度基色</v>
+        <v>正在檢查…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>传递特性</v>
+        <v>无</v>
       </c>
       <c r="C434" t="str">
-        <v>轉換特性</v>
+        <v>無</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>矩阵系数</v>
+        <v>在“配置文件”标签页中打开</v>
       </c>
       <c r="C435" t="str">
-        <v>矩陣係數</v>
+        <v>在「描述檔」分頁中開啟</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>视频全范围标志</v>
+        <v>增益图</v>
       </c>
       <c r="C436" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>增益圖</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>全范围</v>
+        <v>已检测到，未解码</v>
       </c>
       <c r="C437" t="str">
-        <v>全範圍</v>
+        <v>已偵測到，未解碼</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>有限范围</v>
+        <v>这不是图像。请通过配置文件面板加载配置文件。</v>
       </c>
       <c r="C438" t="str">
-        <v>有限範圍</v>
+        <v>這不是影像。請從描述檔面板載入描述檔。</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>不是 profiletool 能识别的图像格式。</v>
       </c>
       <c r="C439" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>不是 profiletool 能辨識的影像格式。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>此处暂不显示 TIFF 像素：浏览器不解码 TIFF，且 16 位 TIFF 中如何编码 HDR 尚未确定（第 4.3 阶段）。其嵌入的配置文件可以查看。</v>
       </c>
       <c r="C440" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>此處暫不顯示 TIFF 像素：瀏覽器不解碼 TIFF，且 16 位元 TIFF 中如何編碼 HDR 尚未決定（第 4.3 階段）。其嵌入的描述檔可以檢視。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>无法在此显示该图像：</v>
       </c>
       <c r="C441" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>無法在此顯示此影像：</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>报告</v>
+        <v>其嵌入的配置文件仍可查看。</v>
       </c>
       <c r="C442" t="str">
-        <v>報告</v>
+        <v>其嵌入的描述檔仍可檢視。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>失败</v>
+        <v>显示方式</v>
       </c>
       <c r="C443" t="str">
-        <v>失敗</v>
+        <v>顯示方式</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>项检查</v>
+        <v>浏览器</v>
       </c>
       <c r="C444" t="str">
-        <v>項檢查</v>
+        <v>瀏覽器</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>profiletool</v>
       </c>
       <c r="C445" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>HDR 显示器</v>
       </c>
       <c r="C446" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>HDR 顯示器</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>浏览器会忽略仅由嵌入 ICC 配置文件标示的 HDR，因此该图像可能显得暗淡、平淡。</v>
       </c>
       <c r="C447" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>瀏覽器會忽略僅由嵌入 ICC 描述檔標示的 HDR，因此此影像可能看起來暗淡、平板。</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>此浏览器无法在 SDR 与 HDR 之间切换图像，因此按浏览器的渲染显示。</v>
       </c>
       <c r="C448" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>此瀏覽器無法在 SDR 與 HDR 之間切換影像，因此依瀏覽器的算繪顯示。</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>订阅</v>
+        <v>浏览器无法解码此图像。</v>
       </c>
       <c r="C449" t="str">
-        <v>訂閱</v>
+        <v>瀏覽器無法解碼此影像。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>输出</v>
       </c>
       <c r="C450" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>订阅新版本通知</v>
+        <v>HDR 画布（float16）</v>
       </c>
       <c r="C451" t="str">
-        <v>訂閱新版本通知</v>
+        <v>HDR 畫布（float16）</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>关闭</v>
+        <v>WebGPU（扩展范围）</v>
       </c>
       <c r="C452" t="str">
-        <v>關閉</v>
+        <v>WebGPU（延伸範圍）</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>SDR 画布（色调映射）</v>
       </c>
       <c r="C453" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>SDR 畫布（色調映射）</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>电子邮件地址</v>
+        <v>尺寸</v>
       </c>
       <c r="C454" t="str">
-        <v>電子郵件地址</v>
+        <v>尺寸</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>you@example.com</v>
+        <v>最亮像素</v>
       </c>
       <c r="C455" t="str">
-        <v>you@example.com</v>
+        <v>最亮像素</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>SDR 白的 {n} 倍</v>
       </c>
       <c r="C456" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>SDR 白的 {n} 倍</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>（选填）</v>
+        <v>色度坐标</v>
       </c>
       <c r="C457" t="str">
-        <v>（選填）</v>
+        <v>色度座標</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>未注明——假定为 Rec. 709</v>
       </c>
       <c r="C458" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>未註明——假定為 Rec. 709</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>此处无法使用 {from}（{why}）；改用下一种输出。</v>
       </c>
       <c r="C459" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>此處無法使用 {from}（{why}）；改用下一種輸出。</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>取消</v>
+        <v>此输出无法承载比白色更亮的值，因此显示经色调映射的 SDR 渲染。</v>
       </c>
       <c r="C460" t="str">
-        <v>取消</v>
+        <v>此輸出無法承載比白色更亮的值，因此顯示經色調映射的 SDR 算繪。</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>订阅</v>
+        <v>曝光</v>
       </c>
       <c r="C461" t="str">
-        <v>訂閱</v>
+        <v>曝光</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>{n} 档</v>
       </c>
       <c r="C462" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>{n} 檔</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>无法解码：</v>
       </c>
       <c r="C463" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>無法解碼：</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>关闭</v>
+        <v>正在解码…</v>
       </c>
       <c r="C464" t="str">
-        <v>關閉</v>
+        <v>正在解碼…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>隐私声明</v>
+        <v>动态范围</v>
       </c>
       <c r="C465" t="str">
-        <v>隱私聲明</v>
+        <v>動態範圍</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>此浏览器只提供两个端点，不支持混合。</v>
       </c>
       <c r="C466" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C467" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>请检查表单后重试。</v>
+        <v>显示余量</v>
       </c>
       <c r="C468" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C469" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>网络错误，请重试。</v>
+        <v>基准</v>
       </c>
       <c r="C470" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>错误：</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C471" t="str">
-        <v>錯誤：</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>转换为 XML</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C472" t="str">
-        <v>轉換為 XML</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>转换为 JSON</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C473" t="str">
-        <v>轉換為 JSON</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>转换为 ICC</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C474" t="str">
-        <v>轉換為 ICC</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>正在转换为 XML…</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C475" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C476" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C477" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C478" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C479" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>配置文件 ID</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C480" t="str">
-        <v>設定檔 ID</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>未找到标签。</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C481" t="str">
-        <v>找不到標籤。</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>标签名称</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C482" t="str">
-        <v>標籤名稱</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C483" t="str">
-        <v>ID</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>偏移</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C484" t="str">
-        <v>偏移</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>大小</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C485" t="str">
-        <v>大小</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>填充</v>
+        <v>不变</v>
       </c>
       <c r="C486" t="str">
-        <v>填充</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>加载后字节已更改</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C487" t="str">
-        <v>載入後位元組已變更</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>类型</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C488" t="str">
-        <v>類型</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>{type} 数组</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C489" t="str">
-        <v>{type} 陣列</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>（无内容）</v>
+        <v>识别显示器</v>
       </c>
       <c r="C490" t="str">
-        <v>（無內容）</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>字节</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C491" t="str">
-        <v>位元組</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>正在加载完整描述…</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C492" t="str">
-        <v>正在載入完整描述…</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>无法加载完整描述：</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C493" t="str">
-        <v>無法載入完整描述：</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C494" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C495" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>无验证输出</v>
+        <v>显示事件</v>
       </c>
       <c r="C496" t="str">
-        <v>無驗證輸出</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>配置文件有效</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C497" t="str">
-        <v>設定檔有效</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>配置文件有警告</v>
+        <v>色度基色</v>
       </c>
       <c r="C498" t="str">
-        <v>設定檔有警告</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>配置文件不合规</v>
+        <v>传递特性</v>
       </c>
       <c r="C499" t="str">
-        <v>設定檔不符合規範</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>严重验证错误</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C500" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>未知验证状态</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C501" t="str">
-        <v>未知驗證狀態</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>全范围</v>
       </c>
       <c r="C502" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>未发现警告或错误。</v>
+        <v>有限范围</v>
       </c>
       <c r="C503" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>有效</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C504" t="str">
-        <v>有效</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>警告</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C505" t="str">
-        <v>警告</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>错误</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C506" t="str">
-        <v>錯誤</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>未知</v>
+        <v>报告</v>
       </c>
       <c r="C507" t="str">
-        <v>未知</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>通过</v>
+        <v>失败</v>
       </c>
       <c r="C508" t="str">
-        <v>通過</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>失败</v>
+        <v>项检查</v>
       </c>
       <c r="C509" t="str">
-        <v>失敗</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>在上下文中查看</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C510" t="str">
-        <v>在上下文中檢視</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>验证详情</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C511" t="str">
-        <v>驗證詳情</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>触发字段</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C512" t="str">
-        <v>觸發欄位</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>字段</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C513" t="str">
-        <v>欄位</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>当前值</v>
+        <v>订阅</v>
       </c>
       <c r="C514" t="str">
-        <v>目前值</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>要求：0</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C515" t="str">
-        <v>要求：0</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>预期：{value}</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C516" t="str">
-        <v>預期：{value}</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>无效</v>
+        <v>关闭</v>
       </c>
       <c r="C517" t="str">
-        <v>無效</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C518" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>关闭</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C519" t="str">
-        <v>關閉</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>you@example.com</v>
       </c>
       <c r="C520" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C521" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>（选填）</v>
       </c>
       <c r="C522" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C523" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C524" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>取消</v>
       </c>
       <c r="C525" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>订阅</v>
       </c>
       <c r="C526" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C527" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>缩进</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C528" t="str">
-        <v>縮排</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>排序键</v>
+        <v>关闭</v>
       </c>
       <c r="C529" t="str">
-        <v>排序鍵</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="C530" t="str">
+        <v>隱私聲明</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>请输入有效的电子邮件地址。</v>
+      </c>
+      <c r="C531" t="str">
+        <v>請輸入有效的電子郵件地址。</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>请求过多，请稍后再试。</v>
+      </c>
+      <c r="C532" t="str">
+        <v>請求過多，請稍後再試。</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>请检查表单后重试。</v>
+      </c>
+      <c r="C533" t="str">
+        <v>請檢查表單後重試。</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>无法发送您的请求，请重试。</v>
+      </c>
+      <c r="C534" t="str">
+        <v>無法傳送您的請求，請重試。</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>网络错误，请重试。</v>
+      </c>
+      <c r="C535" t="str">
+        <v>網路錯誤，請重試。</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>错误：</v>
+      </c>
+      <c r="C536" t="str">
+        <v>錯誤：</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>转换为 XML</v>
+      </c>
+      <c r="C537" t="str">
+        <v>轉換為 XML</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>转换为 JSON</v>
+      </c>
+      <c r="C538" t="str">
+        <v>轉換為 JSON</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>转换为 ICC</v>
+      </c>
+      <c r="C539" t="str">
+        <v>轉換為 ICC</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>正在转换为 XML…</v>
+      </c>
+      <c r="C540" t="str">
+        <v>正在轉換為 XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>正在转换为 JSON…</v>
+      </c>
+      <c r="C541" t="str">
+        <v>正在轉換為 JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>正在转换为 ICC…</v>
+      </c>
+      <c r="C542" t="str">
+        <v>正在轉換為 ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>加载 ICC 配置文件</v>
+      </c>
+      <c r="C543" t="str">
+        <v>載入 ICC 設定檔</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>ICC 配置文件拖放区</v>
+      </c>
+      <c r="C544" t="str">
+        <v>ICC 設定檔拖放區</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>配置文件 ID</v>
+      </c>
+      <c r="C545" t="str">
+        <v>設定檔 ID</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>未找到标签。</v>
+      </c>
+      <c r="C546" t="str">
+        <v>找不到標籤。</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>标签名称</v>
+      </c>
+      <c r="C547" t="str">
+        <v>標籤名稱</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>偏移</v>
+      </c>
+      <c r="C549" t="str">
+        <v>偏移</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>大小</v>
+      </c>
+      <c r="C550" t="str">
+        <v>大小</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>填充</v>
+      </c>
+      <c r="C551" t="str">
+        <v>填充</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>加载后字节已更改</v>
+      </c>
+      <c r="C552" t="str">
+        <v>載入後位元組已變更</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>类型</v>
+      </c>
+      <c r="C553" t="str">
+        <v>類型</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>{type} 数组</v>
+      </c>
+      <c r="C554" t="str">
+        <v>{type} 陣列</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>（无内容）</v>
+      </c>
+      <c r="C555" t="str">
+        <v>（無內容）</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>字节</v>
+      </c>
+      <c r="C556" t="str">
+        <v>位元組</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>正在加载完整描述…</v>
+      </c>
+      <c r="C557" t="str">
+        <v>正在載入完整描述…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>无法加载完整描述：</v>
+      </c>
+      <c r="C558" t="str">
+        <v>無法載入完整描述：</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+      </c>
+      <c r="C559" t="str">
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+      </c>
+      <c r="C560" t="str">
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C561" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>配置文件有效</v>
+      </c>
+      <c r="C562" t="str">
+        <v>設定檔有效</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>配置文件有警告</v>
+      </c>
+      <c r="C563" t="str">
+        <v>設定檔有警告</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>配置文件不合规</v>
+      </c>
+      <c r="C564" t="str">
+        <v>設定檔不符合規範</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>严重验证错误</v>
+      </c>
+      <c r="C565" t="str">
+        <v>嚴重驗證錯誤</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C566" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C567" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C568" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C569" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C570" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C571" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C572" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C573" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C574" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C575" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C576" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C577" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C578" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C579" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C580" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C581" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C582" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C583" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C584" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C585" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C586" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C587" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C588" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C589" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C590" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C591" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C592" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C593" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C594" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C530" t="str">
+      <c r="C595" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C595"/>
+  <dimension ref="A1:C612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5541,1426 +5541,1613 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C467" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>显示余量</v>
+        <v>此浏览器可以解码</v>
       </c>
       <c r="C468" t="str">
-        <v>顯示餘量</v>
+        <v>此瀏覽器可以解碼</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>此浏览器无法解码</v>
       </c>
       <c r="C469" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>此瀏覽器無法解碼</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>基准</v>
+        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
       </c>
       <c r="C470" t="str">
-        <v>基準</v>
+        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
       </c>
       <c r="C471" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>推迟到后续版本</v>
       </c>
       <c r="C472" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>延後至後續版本</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
       </c>
       <c r="C473" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
       </c>
       <c r="C474" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
       </c>
       <c r="C475" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>查看只需解析容器，不需要编解码器</v>
       </c>
       <c r="C476" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>檢視只需解析容器，不需要編解碼器</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>HDR 显示器和 HDR 画布路径均可用</v>
       </c>
       <c r="C477" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>未知格式</v>
       </c>
       <c r="C478" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>未知格式</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>{os} 上的 {browser}</v>
       </c>
       <c r="C479" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>{os} 上的 {browser}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>此余量下应用的增益</v>
+        <v>{name} · 检测到 HDR 显示器</v>
       </c>
       <c r="C480" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>{name} · 偵測到 HDR 顯示器</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>{name} · SDR 显示器</v>
       </c>
       <c r="C481" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>{name} · SDR 顯示器</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>增益（log2 档）</v>
+        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
       </c>
       <c r="C482" t="str">
-        <v>增益（log2 檔）</v>
+        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
       </c>
       <c r="C483" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C484" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>显示余量</v>
       </c>
       <c r="C485" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>不变</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C486" t="str">
-        <v>不變</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>基准</v>
       </c>
       <c r="C487" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>{h} 档处的输出</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C488" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C489" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>识别显示器</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C490" t="str">
-        <v>識別顯示器</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C491" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C492" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C493" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C494" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>无法识别显示器。</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C495" t="str">
-        <v>無法識別顯示器。</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>显示事件</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C496" t="str">
-        <v>顯示事件</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C497" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>色度基色</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C498" t="str">
-        <v>色度基色</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>传递特性</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C499" t="str">
-        <v>轉換特性</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>矩阵系数</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C500" t="str">
-        <v>矩陣係數</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>视频全范围标志</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C501" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>全范围</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C502" t="str">
-        <v>全範圍</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>有限范围</v>
+        <v>不变</v>
       </c>
       <c r="C503" t="str">
-        <v>有限範圍</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C504" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C505" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C506" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>报告</v>
+        <v>识别显示器</v>
       </c>
       <c r="C507" t="str">
-        <v>報告</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>失败</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C508" t="str">
-        <v>失敗</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>项检查</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C509" t="str">
-        <v>項檢查</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C510" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C511" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C512" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>显示事件</v>
       </c>
       <c r="C513" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>订阅</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C514" t="str">
-        <v>訂閱</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>色度基色</v>
       </c>
       <c r="C515" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>订阅新版本通知</v>
+        <v>传递特性</v>
       </c>
       <c r="C516" t="str">
-        <v>訂閱新版本通知</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>关闭</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C517" t="str">
-        <v>關閉</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C518" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>电子邮件地址</v>
+        <v>全范围</v>
       </c>
       <c r="C519" t="str">
-        <v>電子郵件地址</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>you@example.com</v>
+        <v>有限范围</v>
       </c>
       <c r="C520" t="str">
-        <v>you@example.com</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C521" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>（选填）</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C522" t="str">
-        <v>（選填）</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C523" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>报告</v>
       </c>
       <c r="C524" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>取消</v>
+        <v>失败</v>
       </c>
       <c r="C525" t="str">
-        <v>取消</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>订阅</v>
+        <v>项检查</v>
       </c>
       <c r="C526" t="str">
-        <v>訂閱</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C527" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C528" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>关闭</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C529" t="str">
-        <v>關閉</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>隐私声明</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C530" t="str">
-        <v>隱私聲明</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>订阅</v>
       </c>
       <c r="C531" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C532" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>请检查表单后重试。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C533" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>关闭</v>
       </c>
       <c r="C534" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>网络错误，请重试。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C535" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>错误：</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C536" t="str">
-        <v>錯誤：</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>转换为 XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="C537" t="str">
-        <v>轉換為 XML</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>转换为 JSON</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C538" t="str">
-        <v>轉換為 JSON</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>转换为 ICC</v>
+        <v>（选填）</v>
       </c>
       <c r="C539" t="str">
-        <v>轉換為 ICC</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>正在转换为 XML…</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C540" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C541" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>取消</v>
       </c>
       <c r="C542" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>订阅</v>
       </c>
       <c r="C543" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C544" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>配置文件 ID</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C545" t="str">
-        <v>設定檔 ID</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>未找到标签。</v>
+        <v>关闭</v>
       </c>
       <c r="C546" t="str">
-        <v>找不到標籤。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>标签名称</v>
+        <v>隐私声明</v>
       </c>
       <c r="C547" t="str">
-        <v>標籤名稱</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C548" t="str">
-        <v>ID</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>偏移</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C549" t="str">
-        <v>偏移</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>大小</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C550" t="str">
-        <v>大小</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>填充</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C551" t="str">
-        <v>填充</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>加载后字节已更改</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C552" t="str">
-        <v>載入後位元組已變更</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>类型</v>
+        <v>错误：</v>
       </c>
       <c r="C553" t="str">
-        <v>類型</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>{type} 数组</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C554" t="str">
-        <v>{type} 陣列</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>（无内容）</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C555" t="str">
-        <v>（無內容）</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>字节</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C556" t="str">
-        <v>位元組</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>正在加载完整描述…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C557" t="str">
-        <v>正在載入完整描述…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C558" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C559" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C560" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>无验证输出</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C561" t="str">
-        <v>無驗證輸出</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>配置文件有效</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C562" t="str">
-        <v>設定檔有效</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>配置文件有警告</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C563" t="str">
-        <v>設定檔有警告</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>配置文件不合规</v>
+        <v>标签名称</v>
       </c>
       <c r="C564" t="str">
-        <v>設定檔不符合規範</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>严重验证错误</v>
+        <v>ID</v>
       </c>
       <c r="C565" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>未知验证状态</v>
+        <v>偏移</v>
       </c>
       <c r="C566" t="str">
-        <v>未知驗證狀態</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>大小</v>
       </c>
       <c r="C567" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>未发现警告或错误。</v>
+        <v>填充</v>
       </c>
       <c r="C568" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>有效</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C569" t="str">
-        <v>有效</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>警告</v>
+        <v>类型</v>
       </c>
       <c r="C570" t="str">
-        <v>警告</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>错误</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C571" t="str">
-        <v>錯誤</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>未知</v>
+        <v>（无内容）</v>
       </c>
       <c r="C572" t="str">
-        <v>未知</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>通过</v>
+        <v>字节</v>
       </c>
       <c r="C573" t="str">
-        <v>通過</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>失败</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C574" t="str">
-        <v>失敗</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>在上下文中查看</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C575" t="str">
-        <v>在上下文中檢視</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>验证详情</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C576" t="str">
-        <v>驗證詳情</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>触发字段</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C577" t="str">
-        <v>觸發欄位</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>字段</v>
+        <v>无验证输出</v>
       </c>
       <c r="C578" t="str">
-        <v>欄位</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>当前值</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C579" t="str">
-        <v>目前值</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>要求：0</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C580" t="str">
-        <v>要求：0</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>预期：{value}</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C581" t="str">
-        <v>預期：{value}</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>无效</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C582" t="str">
-        <v>無效</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C583" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>关闭</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C584" t="str">
-        <v>關閉</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C585" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>有效</v>
       </c>
       <c r="C586" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>警告</v>
       </c>
       <c r="C587" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>错误</v>
       </c>
       <c r="C588" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>未知</v>
       </c>
       <c r="C589" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>通过</v>
       </c>
       <c r="C590" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>失败</v>
       </c>
       <c r="C591" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C592" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>缩进</v>
+        <v>验证详情</v>
       </c>
       <c r="C593" t="str">
-        <v>縮排</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>排序键</v>
+        <v>触发字段</v>
       </c>
       <c r="C594" t="str">
-        <v>排序鍵</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C595" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C596" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C597" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C598" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C599" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C600" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C601" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C602" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C603" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C604" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C605" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C606" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C607" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C608" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C609" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C610" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C611" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C595" t="str">
+      <c r="C612" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C612"/>
+  <dimension ref="A1:C625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5728,1426 +5728,1569 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C484" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>显示余量</v>
+        <v>SDR 白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C485" t="str">
-        <v>顯示餘量</v>
+        <v>SDR 白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>1× —— SDR 显示器</v>
       </c>
       <c r="C486" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>1× —— SDR 顯示器</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>基准</v>
+        <v>未知</v>
       </c>
       <c r="C487" t="str">
-        <v>基準</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
       </c>
       <c r="C488" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
       </c>
       <c r="C489" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
       </c>
       <c r="C490" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>适配显示器</v>
       </c>
       <c r="C491" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>符合顯示器</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
       </c>
       <c r="C492" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>无上限</v>
       </c>
       <c r="C493" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>無上限</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>上限 {n} 档（{r}×）</v>
       </c>
       <c r="C494" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>上限 {n} 檔（{r}×）</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>SDR 白</v>
       </c>
       <c r="C495" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
       </c>
       <c r="C496" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>此余量下应用的增益</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C497" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>显示余量</v>
       </c>
       <c r="C498" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>增益（log2 档）</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C499" t="str">
-        <v>增益（log2 檔）</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>基准</v>
       </c>
       <c r="C500" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C501" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C502" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>不变</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C503" t="str">
-        <v>不變</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C504" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>{h} 档处的输出</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C505" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C506" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>识别显示器</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C507" t="str">
-        <v>識別顯示器</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C508" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C509" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C510" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C511" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>无法识别显示器。</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C512" t="str">
-        <v>無法識別顯示器。</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>显示事件</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C513" t="str">
-        <v>顯示事件</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C514" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>色度基色</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C515" t="str">
-        <v>色度基色</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>传递特性</v>
+        <v>不变</v>
       </c>
       <c r="C516" t="str">
-        <v>轉換特性</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>矩阵系数</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C517" t="str">
-        <v>矩陣係數</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>视频全范围标志</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C518" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>全范围</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C519" t="str">
-        <v>全範圍</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>有限范围</v>
+        <v>识别显示器</v>
       </c>
       <c r="C520" t="str">
-        <v>有限範圍</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C521" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C522" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C523" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>报告</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C524" t="str">
-        <v>報告</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>失败</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C525" t="str">
-        <v>失敗</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>项检查</v>
+        <v>显示事件</v>
       </c>
       <c r="C526" t="str">
-        <v>項檢查</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C527" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>色度基色</v>
       </c>
       <c r="C528" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>传递特性</v>
       </c>
       <c r="C529" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C530" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>订阅</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C531" t="str">
-        <v>訂閱</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>全范围</v>
       </c>
       <c r="C532" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>订阅新版本通知</v>
+        <v>有限范围</v>
       </c>
       <c r="C533" t="str">
-        <v>訂閱新版本通知</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>关闭</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C534" t="str">
-        <v>關閉</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C535" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>电子邮件地址</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C536" t="str">
-        <v>電子郵件地址</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>you@example.com</v>
+        <v>报告</v>
       </c>
       <c r="C537" t="str">
-        <v>you@example.com</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>失败</v>
       </c>
       <c r="C538" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>（选填）</v>
+        <v>项检查</v>
       </c>
       <c r="C539" t="str">
-        <v>（選填）</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C540" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C541" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>取消</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C542" t="str">
-        <v>取消</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C543" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C544" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C545" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C546" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C547" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C548" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C549" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>请检查表单后重试。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C550" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C551" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>网络错误，请重试。</v>
+        <v>（选填）</v>
       </c>
       <c r="C552" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>错误：</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C553" t="str">
-        <v>錯誤：</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>转换为 XML</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C554" t="str">
-        <v>轉換為 XML</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>转换为 JSON</v>
+        <v>取消</v>
       </c>
       <c r="C555" t="str">
-        <v>轉換為 JSON</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>转换为 ICC</v>
+        <v>订阅</v>
       </c>
       <c r="C556" t="str">
-        <v>轉換為 ICC</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>正在转换为 XML…</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C557" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C558" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>关闭</v>
       </c>
       <c r="C559" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>隐私声明</v>
       </c>
       <c r="C560" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C561" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>配置文件 ID</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C562" t="str">
-        <v>設定檔 ID</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>未找到标签。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C563" t="str">
-        <v>找不到標籤。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>标签名称</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C564" t="str">
-        <v>標籤名稱</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C565" t="str">
-        <v>ID</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>偏移</v>
+        <v>错误：</v>
       </c>
       <c r="C566" t="str">
-        <v>偏移</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>大小</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C567" t="str">
-        <v>大小</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>填充</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C568" t="str">
-        <v>填充</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>加载后字节已更改</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C569" t="str">
-        <v>載入後位元組已變更</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>类型</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C570" t="str">
-        <v>類型</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>{type} 数组</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C571" t="str">
-        <v>{type} 陣列</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>（无内容）</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C572" t="str">
-        <v>（無內容）</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>字节</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C573" t="str">
-        <v>位元組</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>正在加载完整描述…</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C574" t="str">
-        <v>正在載入完整描述…</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>无法加载完整描述：</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C575" t="str">
-        <v>無法載入完整描述：</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C576" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>标签名称</v>
       </c>
       <c r="C577" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>无验证输出</v>
+        <v>ID</v>
       </c>
       <c r="C578" t="str">
-        <v>無驗證輸出</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>配置文件有效</v>
+        <v>偏移</v>
       </c>
       <c r="C579" t="str">
-        <v>設定檔有效</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>配置文件有警告</v>
+        <v>大小</v>
       </c>
       <c r="C580" t="str">
-        <v>設定檔有警告</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>配置文件不合规</v>
+        <v>填充</v>
       </c>
       <c r="C581" t="str">
-        <v>設定檔不符合規範</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>严重验证错误</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C582" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>未知验证状态</v>
+        <v>类型</v>
       </c>
       <c r="C583" t="str">
-        <v>未知驗證狀態</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C584" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>未发现警告或错误。</v>
+        <v>（无内容）</v>
       </c>
       <c r="C585" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>有效</v>
+        <v>字节</v>
       </c>
       <c r="C586" t="str">
-        <v>有效</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>警告</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C587" t="str">
-        <v>警告</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>错误</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C588" t="str">
-        <v>錯誤</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>未知</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C589" t="str">
-        <v>未知</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>通过</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C590" t="str">
-        <v>通過</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>失败</v>
+        <v>无验证输出</v>
       </c>
       <c r="C591" t="str">
-        <v>失敗</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>在上下文中查看</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C592" t="str">
-        <v>在上下文中檢視</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>验证详情</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C593" t="str">
-        <v>驗證詳情</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>触发字段</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C594" t="str">
-        <v>觸發欄位</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>字段</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C595" t="str">
-        <v>欄位</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>当前值</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C596" t="str">
-        <v>目前值</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>要求：0</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C597" t="str">
-        <v>要求：0</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>预期：{value}</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C598" t="str">
-        <v>預期：{value}</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>无效</v>
+        <v>有效</v>
       </c>
       <c r="C599" t="str">
-        <v>無效</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>警告</v>
       </c>
       <c r="C600" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>关闭</v>
+        <v>错误</v>
       </c>
       <c r="C601" t="str">
-        <v>關閉</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>未知</v>
       </c>
       <c r="C602" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>通过</v>
       </c>
       <c r="C603" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>失败</v>
       </c>
       <c r="C604" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C605" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>验证详情</v>
       </c>
       <c r="C606" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>触发字段</v>
       </c>
       <c r="C607" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>字段</v>
       </c>
       <c r="C608" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>当前值</v>
       </c>
       <c r="C609" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>缩进</v>
+        <v>要求：0</v>
       </c>
       <c r="C610" t="str">
-        <v>縮排</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>排序键</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C611" t="str">
-        <v>排序鍵</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C612" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C613" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C614" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C615" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C616" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C617" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C618" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C619" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C620" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C621" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C622" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C623" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C624" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C612" t="str">
+      <c r="C625" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C625"/>
+  <dimension ref="A1:C627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5871,1426 +5871,1448 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>SDR 白色色块</v>
       </c>
       <c r="C497" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>SDR 白色色塊</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>显示余量</v>
+        <v>拖动即可移动；双击可将其放回图像旁边。</v>
       </c>
       <c r="C498" t="str">
-        <v>顯示餘量</v>
+        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C499" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>基准</v>
+        <v>显示余量</v>
       </c>
       <c r="C500" t="str">
-        <v>基準</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C501" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>基准</v>
       </c>
       <c r="C502" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C503" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C504" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C505" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C506" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C507" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C508" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C509" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>此余量下应用的增益</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C510" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C511" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>增益（log2 档）</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C512" t="str">
-        <v>增益（log2 檔）</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C513" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C514" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C515" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>不变</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C516" t="str">
-        <v>不變</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C517" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>{h} 档处的输出</v>
+        <v>不变</v>
       </c>
       <c r="C518" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C519" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>识别显示器</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C520" t="str">
-        <v>識別顯示器</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C521" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C522" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C523" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C524" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>无法识别显示器。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C525" t="str">
-        <v>無法識別顯示器。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>显示事件</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C526" t="str">
-        <v>顯示事件</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C527" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>色度基色</v>
+        <v>显示事件</v>
       </c>
       <c r="C528" t="str">
-        <v>色度基色</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>传递特性</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C529" t="str">
-        <v>轉換特性</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>矩阵系数</v>
+        <v>色度基色</v>
       </c>
       <c r="C530" t="str">
-        <v>矩陣係數</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>视频全范围标志</v>
+        <v>传递特性</v>
       </c>
       <c r="C531" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>全范围</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C532" t="str">
-        <v>全範圍</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>有限范围</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C533" t="str">
-        <v>有限範圍</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>全范围</v>
       </c>
       <c r="C534" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>有限范围</v>
       </c>
       <c r="C535" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C536" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>报告</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C537" t="str">
-        <v>報告</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>失败</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C538" t="str">
-        <v>失敗</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>项检查</v>
+        <v>报告</v>
       </c>
       <c r="C539" t="str">
-        <v>項檢查</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>失败</v>
       </c>
       <c r="C540" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>项检查</v>
       </c>
       <c r="C541" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C542" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C543" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>订阅</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C544" t="str">
-        <v>訂閱</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C545" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>订阅新版本通知</v>
+        <v>订阅</v>
       </c>
       <c r="C546" t="str">
-        <v>訂閱新版本通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>关闭</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C547" t="str">
-        <v>關閉</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C548" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>电子邮件地址</v>
+        <v>关闭</v>
       </c>
       <c r="C549" t="str">
-        <v>電子郵件地址</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>you@example.com</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C550" t="str">
-        <v>you@example.com</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C551" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>（选填）</v>
+        <v>you@example.com</v>
       </c>
       <c r="C552" t="str">
-        <v>（選填）</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C553" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>（选填）</v>
       </c>
       <c r="C554" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>取消</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C555" t="str">
-        <v>取消</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>订阅</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C556" t="str">
-        <v>訂閱</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>取消</v>
       </c>
       <c r="C557" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>订阅</v>
       </c>
       <c r="C558" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>关闭</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C559" t="str">
-        <v>關閉</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>隐私声明</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C560" t="str">
-        <v>隱私聲明</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>关闭</v>
       </c>
       <c r="C561" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C562" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C563" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C564" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>网络错误，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C565" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>错误：</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C566" t="str">
-        <v>錯誤：</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>转换为 XML</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C567" t="str">
-        <v>轉換為 XML</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>转换为 JSON</v>
+        <v>错误：</v>
       </c>
       <c r="C568" t="str">
-        <v>轉換為 JSON</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C569" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C570" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C571" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C572" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C573" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C574" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>配置文件 ID</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C575" t="str">
-        <v>設定檔 ID</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>未找到标签。</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C576" t="str">
-        <v>找不到標籤。</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>标签名称</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C577" t="str">
-        <v>標籤名稱</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C578" t="str">
-        <v>ID</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>偏移</v>
+        <v>标签名称</v>
       </c>
       <c r="C579" t="str">
-        <v>偏移</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>大小</v>
+        <v>ID</v>
       </c>
       <c r="C580" t="str">
-        <v>大小</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>填充</v>
+        <v>偏移</v>
       </c>
       <c r="C581" t="str">
-        <v>填充</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>加载后字节已更改</v>
+        <v>大小</v>
       </c>
       <c r="C582" t="str">
-        <v>載入後位元組已變更</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>类型</v>
+        <v>填充</v>
       </c>
       <c r="C583" t="str">
-        <v>類型</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>{type} 数组</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C584" t="str">
-        <v>{type} 陣列</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>（无内容）</v>
+        <v>类型</v>
       </c>
       <c r="C585" t="str">
-        <v>（無內容）</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>字节</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C586" t="str">
-        <v>位元組</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>正在加载完整描述…</v>
+        <v>（无内容）</v>
       </c>
       <c r="C587" t="str">
-        <v>正在載入完整描述…</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>无法加载完整描述：</v>
+        <v>字节</v>
       </c>
       <c r="C588" t="str">
-        <v>無法載入完整描述：</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C589" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C590" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>无验证输出</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C591" t="str">
-        <v>無驗證輸出</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>配置文件有效</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C592" t="str">
-        <v>設定檔有效</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>配置文件有警告</v>
+        <v>无验证输出</v>
       </c>
       <c r="C593" t="str">
-        <v>設定檔有警告</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C594" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C595" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>未知验证状态</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C596" t="str">
-        <v>未知驗證狀態</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C597" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>未发现警告或错误。</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C598" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>有效</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C599" t="str">
-        <v>有效</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>警告</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C600" t="str">
-        <v>警告</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>错误</v>
+        <v>有效</v>
       </c>
       <c r="C601" t="str">
-        <v>錯誤</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>未知</v>
+        <v>警告</v>
       </c>
       <c r="C602" t="str">
-        <v>未知</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>通过</v>
+        <v>错误</v>
       </c>
       <c r="C603" t="str">
-        <v>通過</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>失败</v>
+        <v>未知</v>
       </c>
       <c r="C604" t="str">
-        <v>失敗</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>在上下文中查看</v>
+        <v>通过</v>
       </c>
       <c r="C605" t="str">
-        <v>在上下文中檢視</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>验证详情</v>
+        <v>失败</v>
       </c>
       <c r="C606" t="str">
-        <v>驗證詳情</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>触发字段</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C607" t="str">
-        <v>觸發欄位</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C608" t="str">
-        <v>欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>当前值</v>
+        <v>触发字段</v>
       </c>
       <c r="C609" t="str">
-        <v>目前值</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>要求：0</v>
+        <v>字段</v>
       </c>
       <c r="C610" t="str">
-        <v>要求：0</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>预期：{value}</v>
+        <v>当前值</v>
       </c>
       <c r="C611" t="str">
-        <v>預期：{value}</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>无效</v>
+        <v>要求：0</v>
       </c>
       <c r="C612" t="str">
-        <v>無效</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C613" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>关闭</v>
+        <v>无效</v>
       </c>
       <c r="C614" t="str">
-        <v>關閉</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C615" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C616" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C617" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C618" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C619" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C620" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C621" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C622" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C623" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>排序键</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C624" t="str">
-        <v>排序鍵</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C625" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C626" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C625" t="str">
+      <c r="C627" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C627"/>
+  <dimension ref="A1:C650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5893,1426 +5893,1679 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>指定配置文件</v>
       </c>
       <c r="C499" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>指定描述檔</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>显示余量</v>
+        <v>无——按文件自身标示</v>
       </c>
       <c r="C500" t="str">
-        <v>顯示餘量</v>
+        <v>無——依檔案本身標示</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>嵌入的配置文件（{n} B）</v>
       </c>
       <c r="C501" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>嵌入的描述檔（{n} B）</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>基准</v>
+        <v>池中的 HDR 配置文件</v>
       </c>
       <c r="C502" t="str">
-        <v>基準</v>
+        <v>池中的 HDR 描述檔</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>配置文件</v>
       </c>
       <c r="C503" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>描述檔</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>嵌入的配置文件</v>
       </c>
       <c r="C504" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>嵌入的描述檔</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>色彩引擎路径</v>
       </c>
       <c r="C505" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>色彩引擎路徑</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>HDR 路径，已应用增益曲线</v>
       </c>
       <c r="C506" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>HDR 路徑，已套用增益曲線</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>HDR 路径，无增益曲线</v>
       </c>
       <c r="C507" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>HDR 路徑，無增益曲線</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>预烘焙的 AToB0——不是 HDR 路径</v>
       </c>
       <c r="C508" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>传递函数</v>
       </c>
       <c r="C509" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>傳遞函數</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>HDR 参考白</v>
       </c>
       <c r="C510" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>HDR 參考白</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>目标余量</v>
       </c>
       <c r="C511" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>目標餘量</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>此余量下应用的增益</v>
+        <v>参考白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C512" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>參考白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>色调映射</v>
       </c>
       <c r="C513" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>色調映射</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>增益（log2 档）</v>
+        <v>自动（第 8.10.3 条排序）</v>
       </c>
       <c r="C514" t="str">
-        <v>增益（log2 檔）</v>
+        <v>自動（第 8.10.3 條排序）</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>增益曲线（HAGC）</v>
       </c>
       <c r="C515" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>增益曲線（HAGC）</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>预烘焙的 SDR 回退（AToB0）</v>
       </c>
       <c r="C516" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>預先烘焙的 SDR 備援（AToB0）</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>关闭——与修订前的 CMM 相同</v>
       </c>
       <c r="C517" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>關閉——與修訂前的 CMM 相同</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>不变</v>
+        <v>正在应用配置文件…</v>
       </c>
       <c r="C518" t="str">
-        <v>不變</v>
+        <v>正在套用描述檔…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>OpenEXR 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
       </c>
       <c r="C519" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>OpenEXR 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>{h} 档处的输出</v>
+        <v>指定配置文件需要 3 通道 RGB 图像。</v>
       </c>
       <c r="C520" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>指定描述檔需要 3 通道 RGB 影像。</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>要解释其数值，请在上方指定配置文件。</v>
       </c>
       <c r="C521" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>若要解讀其數值，請在上方指定描述檔。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>识别显示器</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C522" t="str">
-        <v>識別顯示器</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>显示余量</v>
       </c>
       <c r="C523" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C524" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>基准</v>
       </c>
       <c r="C525" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C526" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>无法识别显示器。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C527" t="str">
-        <v>無法識別顯示器。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>显示事件</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C528" t="str">
-        <v>顯示事件</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C529" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>色度基色</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C530" t="str">
-        <v>色度基色</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>传递特性</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C531" t="str">
-        <v>轉換特性</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>矩阵系数</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C532" t="str">
-        <v>矩陣係數</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>视频全范围标志</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C533" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>全范围</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C534" t="str">
-        <v>全範圍</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>有限范围</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C535" t="str">
-        <v>有限範圍</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C536" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C537" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C538" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>报告</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C539" t="str">
-        <v>報告</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>失败</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C540" t="str">
-        <v>失敗</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>项检查</v>
+        <v>不变</v>
       </c>
       <c r="C541" t="str">
-        <v>項檢查</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C542" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C543" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C544" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>识别显示器</v>
       </c>
       <c r="C545" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>订阅</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C546" t="str">
-        <v>訂閱</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C547" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>订阅新版本通知</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C548" t="str">
-        <v>訂閱新版本通知</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>关闭</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C549" t="str">
-        <v>關閉</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C550" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>电子邮件地址</v>
+        <v>显示事件</v>
       </c>
       <c r="C551" t="str">
-        <v>電子郵件地址</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>you@example.com</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C552" t="str">
-        <v>you@example.com</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>色度基色</v>
       </c>
       <c r="C553" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>（选填）</v>
+        <v>传递特性</v>
       </c>
       <c r="C554" t="str">
-        <v>（選填）</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C555" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C556" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>取消</v>
+        <v>全范围</v>
       </c>
       <c r="C557" t="str">
-        <v>取消</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>订阅</v>
+        <v>有限范围</v>
       </c>
       <c r="C558" t="str">
-        <v>訂閱</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C559" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C560" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>关闭</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C561" t="str">
-        <v>關閉</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>隐私声明</v>
+        <v>报告</v>
       </c>
       <c r="C562" t="str">
-        <v>隱私聲明</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>失败</v>
       </c>
       <c r="C563" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>项检查</v>
       </c>
       <c r="C564" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>请检查表单后重试。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C565" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C566" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>网络错误，请重试。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C567" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>错误：</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C568" t="str">
-        <v>錯誤：</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>转换为 XML</v>
+        <v>订阅</v>
       </c>
       <c r="C569" t="str">
-        <v>轉換為 XML</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>转换为 JSON</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C570" t="str">
-        <v>轉換為 JSON</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>转换为 ICC</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C571" t="str">
-        <v>轉換為 ICC</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>正在转换为 XML…</v>
+        <v>关闭</v>
       </c>
       <c r="C572" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C573" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C574" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>you@example.com</v>
       </c>
       <c r="C575" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C576" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>配置文件 ID</v>
+        <v>（选填）</v>
       </c>
       <c r="C577" t="str">
-        <v>設定檔 ID</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>未找到标签。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C578" t="str">
-        <v>找不到標籤。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>标签名称</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C579" t="str">
-        <v>標籤名稱</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>取消</v>
       </c>
       <c r="C580" t="str">
-        <v>ID</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>偏移</v>
+        <v>订阅</v>
       </c>
       <c r="C581" t="str">
-        <v>偏移</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>大小</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C582" t="str">
-        <v>大小</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>填充</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C583" t="str">
-        <v>填充</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>加载后字节已更改</v>
+        <v>关闭</v>
       </c>
       <c r="C584" t="str">
-        <v>載入後位元組已變更</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>类型</v>
+        <v>隐私声明</v>
       </c>
       <c r="C585" t="str">
-        <v>類型</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>{type} 数组</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C586" t="str">
-        <v>{type} 陣列</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>（无内容）</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C587" t="str">
-        <v>（無內容）</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>字节</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C588" t="str">
-        <v>位元組</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>正在加载完整描述…</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C589" t="str">
-        <v>正在載入完整描述…</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>无法加载完整描述：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C590" t="str">
-        <v>無法載入完整描述：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>错误：</v>
       </c>
       <c r="C591" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C592" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>无验证输出</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C593" t="str">
-        <v>無驗證輸出</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>配置文件有效</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C594" t="str">
-        <v>設定檔有效</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>配置文件有警告</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C595" t="str">
-        <v>設定檔有警告</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>配置文件不合规</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C596" t="str">
-        <v>設定檔不符合規範</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>严重验证错误</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C597" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>未知验证状态</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C598" t="str">
-        <v>未知驗證狀態</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C599" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>未发现警告或错误。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C600" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>有效</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C601" t="str">
-        <v>有效</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>警告</v>
+        <v>标签名称</v>
       </c>
       <c r="C602" t="str">
-        <v>警告</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>错误</v>
+        <v>ID</v>
       </c>
       <c r="C603" t="str">
-        <v>錯誤</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>未知</v>
+        <v>偏移</v>
       </c>
       <c r="C604" t="str">
-        <v>未知</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>通过</v>
+        <v>大小</v>
       </c>
       <c r="C605" t="str">
-        <v>通過</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>失败</v>
+        <v>填充</v>
       </c>
       <c r="C606" t="str">
-        <v>失敗</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>在上下文中查看</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C607" t="str">
-        <v>在上下文中檢視</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>验证详情</v>
+        <v>类型</v>
       </c>
       <c r="C608" t="str">
-        <v>驗證詳情</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>触发字段</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C609" t="str">
-        <v>觸發欄位</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>字段</v>
+        <v>（无内容）</v>
       </c>
       <c r="C610" t="str">
-        <v>欄位</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>当前值</v>
+        <v>字节</v>
       </c>
       <c r="C611" t="str">
-        <v>目前值</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>要求：0</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C612" t="str">
-        <v>要求：0</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>预期：{value}</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C613" t="str">
-        <v>預期：{value}</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>无效</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C614" t="str">
-        <v>無效</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C615" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>关闭</v>
+        <v>无验证输出</v>
       </c>
       <c r="C616" t="str">
-        <v>關閉</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C617" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C618" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C619" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C620" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C621" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C622" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C623" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>有效</v>
       </c>
       <c r="C624" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>缩进</v>
+        <v>警告</v>
       </c>
       <c r="C625" t="str">
-        <v>縮排</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>排序键</v>
+        <v>错误</v>
       </c>
       <c r="C626" t="str">
-        <v>排序鍵</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C627" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C628" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C629" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C630" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C631" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C632" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C633" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C634" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C635" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C636" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C637" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C638" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C639" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C640" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C641" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C642" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C643" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C644" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C645" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C646" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C647" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C648" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C649" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C627" t="str">
+      <c r="C650" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C650"/>
+  <dimension ref="A1:C658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6146,1426 +6146,1514 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>HDR 配置文件</v>
       </c>
       <c r="C522" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>HDR 描述檔</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>显示余量</v>
+        <v>线性传递函数</v>
       </c>
       <c r="C523" t="str">
-        <v>顯示餘量</v>
+        <v>線性傳遞函數</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>非线性传递函数（PQ、HLG）</v>
       </c>
       <c r="C524" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>非線性傳遞函數（PQ、HLG）</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>基准</v>
+        <v>HDR 配置文件——线性传递函数</v>
       </c>
       <c r="C525" t="str">
-        <v>基準</v>
+        <v>HDR 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>HDR 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C526" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>OpenEXR 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
       </c>
       <c r="C527" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>OpenEXR 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C528" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
       </c>
       <c r="C529" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C530" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>显示余量</v>
       </c>
       <c r="C531" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C532" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>基准</v>
       </c>
       <c r="C533" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C534" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>此余量下应用的增益</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C535" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C536" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>增益（log2 档）</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C537" t="str">
-        <v>增益（log2 檔）</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C538" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C539" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C540" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>不变</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C541" t="str">
-        <v>不變</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C542" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>{h} 档处的输出</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C543" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C544" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>识别显示器</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C545" t="str">
-        <v>識別顯示器</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C546" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C547" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C548" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>不变</v>
       </c>
       <c r="C549" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>无法识别显示器。</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C550" t="str">
-        <v>無法識別顯示器。</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>显示事件</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C551" t="str">
-        <v>顯示事件</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C552" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>色度基色</v>
+        <v>识别显示器</v>
       </c>
       <c r="C553" t="str">
-        <v>色度基色</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>传递特性</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C554" t="str">
-        <v>轉換特性</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>矩阵系数</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C555" t="str">
-        <v>矩陣係數</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>视频全范围标志</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C556" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>全范围</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C557" t="str">
-        <v>全範圍</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>有限范围</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C558" t="str">
-        <v>有限範圍</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>显示事件</v>
       </c>
       <c r="C559" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C560" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>色度基色</v>
       </c>
       <c r="C561" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>报告</v>
+        <v>传递特性</v>
       </c>
       <c r="C562" t="str">
-        <v>報告</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>失败</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C563" t="str">
-        <v>失敗</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>项检查</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C564" t="str">
-        <v>項檢查</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>全范围</v>
       </c>
       <c r="C565" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>有限范围</v>
       </c>
       <c r="C566" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C567" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C568" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>订阅</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C569" t="str">
-        <v>訂閱</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>报告</v>
       </c>
       <c r="C570" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>订阅新版本通知</v>
+        <v>失败</v>
       </c>
       <c r="C571" t="str">
-        <v>訂閱新版本通知</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>关闭</v>
+        <v>项检查</v>
       </c>
       <c r="C572" t="str">
-        <v>關閉</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C573" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>电子邮件地址</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C574" t="str">
-        <v>電子郵件地址</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>you@example.com</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C575" t="str">
-        <v>you@example.com</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C576" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>（选填）</v>
+        <v>订阅</v>
       </c>
       <c r="C577" t="str">
-        <v>（選填）</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C578" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C579" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>取消</v>
+        <v>关闭</v>
       </c>
       <c r="C580" t="str">
-        <v>取消</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>订阅</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C581" t="str">
-        <v>訂閱</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C582" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C583" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>关闭</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C584" t="str">
-        <v>關閉</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>隐私声明</v>
+        <v>（选填）</v>
       </c>
       <c r="C585" t="str">
-        <v>隱私聲明</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C586" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C587" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>请检查表单后重试。</v>
+        <v>取消</v>
       </c>
       <c r="C588" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>订阅</v>
       </c>
       <c r="C589" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>网络错误，请重试。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C590" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>错误：</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C591" t="str">
-        <v>錯誤：</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>转换为 XML</v>
+        <v>关闭</v>
       </c>
       <c r="C592" t="str">
-        <v>轉換為 XML</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>转换为 JSON</v>
+        <v>隐私声明</v>
       </c>
       <c r="C593" t="str">
-        <v>轉換為 JSON</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>转换为 ICC</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C594" t="str">
-        <v>轉換為 ICC</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>正在转换为 XML…</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C595" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C596" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C597" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C598" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>错误：</v>
       </c>
       <c r="C599" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>配置文件 ID</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C600" t="str">
-        <v>設定檔 ID</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>未找到标签。</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C601" t="str">
-        <v>找不到標籤。</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>标签名称</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C602" t="str">
-        <v>標籤名稱</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C603" t="str">
-        <v>ID</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>偏移</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C604" t="str">
-        <v>偏移</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>大小</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C605" t="str">
-        <v>大小</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>填充</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C606" t="str">
-        <v>填充</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>加载后字节已更改</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C607" t="str">
-        <v>載入後位元組已變更</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>类型</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C608" t="str">
-        <v>類型</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>{type} 数组</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C609" t="str">
-        <v>{type} 陣列</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>（无内容）</v>
+        <v>标签名称</v>
       </c>
       <c r="C610" t="str">
-        <v>（無內容）</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>字节</v>
+        <v>ID</v>
       </c>
       <c r="C611" t="str">
-        <v>位元組</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>正在加载完整描述…</v>
+        <v>偏移</v>
       </c>
       <c r="C612" t="str">
-        <v>正在載入完整描述…</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>无法加载完整描述：</v>
+        <v>大小</v>
       </c>
       <c r="C613" t="str">
-        <v>無法載入完整描述：</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>填充</v>
       </c>
       <c r="C614" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C615" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>无验证输出</v>
+        <v>类型</v>
       </c>
       <c r="C616" t="str">
-        <v>無驗證輸出</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>配置文件有效</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C617" t="str">
-        <v>設定檔有效</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>配置文件有警告</v>
+        <v>（无内容）</v>
       </c>
       <c r="C618" t="str">
-        <v>設定檔有警告</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>配置文件不合规</v>
+        <v>字节</v>
       </c>
       <c r="C619" t="str">
-        <v>設定檔不符合規範</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>严重验证错误</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C620" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>未知验证状态</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C621" t="str">
-        <v>未知驗證狀態</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C622" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>未发现警告或错误。</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C623" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C624" t="str">
-        <v>有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C625" t="str">
-        <v>警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>错误</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C626" t="str">
-        <v>錯誤</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>未知</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C627" t="str">
-        <v>未知</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>通过</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C628" t="str">
-        <v>通過</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>失败</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C629" t="str">
-        <v>失敗</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>在上下文中查看</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C630" t="str">
-        <v>在上下文中檢視</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>验证详情</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C631" t="str">
-        <v>驗證詳情</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>触发字段</v>
+        <v>有效</v>
       </c>
       <c r="C632" t="str">
-        <v>觸發欄位</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>字段</v>
+        <v>警告</v>
       </c>
       <c r="C633" t="str">
-        <v>欄位</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>当前值</v>
+        <v>错误</v>
       </c>
       <c r="C634" t="str">
-        <v>目前值</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>要求：0</v>
+        <v>未知</v>
       </c>
       <c r="C635" t="str">
-        <v>要求：0</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>预期：{value}</v>
+        <v>通过</v>
       </c>
       <c r="C636" t="str">
-        <v>預期：{value}</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>无效</v>
+        <v>失败</v>
       </c>
       <c r="C637" t="str">
-        <v>無效</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C638" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>关闭</v>
+        <v>验证详情</v>
       </c>
       <c r="C639" t="str">
-        <v>關閉</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>触发字段</v>
       </c>
       <c r="C640" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>字段</v>
       </c>
       <c r="C641" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>当前值</v>
       </c>
       <c r="C642" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>要求：0</v>
       </c>
       <c r="C643" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C644" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>无效</v>
       </c>
       <c r="C645" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C646" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>关闭</v>
       </c>
       <c r="C647" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>缩进</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C648" t="str">
-        <v>縮排</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>排序键</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C649" t="str">
-        <v>排序鍵</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C650" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C651" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C652" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C653" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C654" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C655" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C656" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C657" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C650" t="str">
+      <c r="C658" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C658"/>
+  <dimension ref="A1:C659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5090,13 +5090,13 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>在此显示器上查看一张 HDR 图像。浏览器能解码的文件由浏览器自身显示；OpenEXR 由 profiletool 解码并渲染。</v>
+        <v>在此显示器上查看一张 HDR 图像。浏览器能解码的文件由浏览器自身显示；OpenEXR 和 Radiance HDR 由 profiletool 解码并渲染。</v>
       </c>
       <c r="C426" t="str">
-        <v>在此顯示器上檢視一張 HDR 影像。瀏覽器能解碼的檔案由瀏覽器自行顯示；OpenEXR 由 profiletool 解碼並算繪。</v>
+        <v>在此顯示器上檢視一張 HDR 影像。瀏覽器能解碼的檔案由瀏覽器自行顯示；OpenEXR 和 Radiance HDR 由 profiletool 解碼並算繪。</v>
       </c>
     </row>
     <row r="427">
@@ -5112,13 +5112,13 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
       </c>
       <c r="C428" t="str">
-        <v>OpenEXR、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
       </c>
     </row>
     <row r="429">
@@ -5167,2493 +5167,2504 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>正在检查…</v>
+        <v>无——Radiance HDR 通过 PRIMARIES 文件头描述颜色</v>
       </c>
       <c r="C433" t="str">
-        <v>正在檢查…</v>
+        <v>無——Radiance HDR 以 PRIMARIES 檔頭描述色彩</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>无</v>
+        <v>正在检查…</v>
       </c>
       <c r="C434" t="str">
-        <v>無</v>
+        <v>正在檢查…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>在“配置文件”标签页中打开</v>
+        <v>无</v>
       </c>
       <c r="C435" t="str">
-        <v>在「描述檔」分頁中開啟</v>
+        <v>無</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>增益图</v>
+        <v>在“配置文件”标签页中打开</v>
       </c>
       <c r="C436" t="str">
-        <v>增益圖</v>
+        <v>在「描述檔」分頁中開啟</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>已检测到，未解码</v>
+        <v>增益图</v>
       </c>
       <c r="C437" t="str">
-        <v>已偵測到，未解碼</v>
+        <v>增益圖</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>这不是图像。请通过配置文件面板加载配置文件。</v>
+        <v>已检测到，未解码</v>
       </c>
       <c r="C438" t="str">
-        <v>這不是影像。請從描述檔面板載入描述檔。</v>
+        <v>已偵測到，未解碼</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>不是 profiletool 能识别的图像格式。</v>
+        <v>这不是图像。请通过配置文件面板加载配置文件。</v>
       </c>
       <c r="C439" t="str">
-        <v>不是 profiletool 能辨識的影像格式。</v>
+        <v>這不是影像。請從描述檔面板載入描述檔。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>此处暂不显示 TIFF 像素：浏览器不解码 TIFF，且 16 位 TIFF 中如何编码 HDR 尚未确定（第 4.3 阶段）。其嵌入的配置文件可以查看。</v>
+        <v>不是 profiletool 能识别的图像格式。</v>
       </c>
       <c r="C440" t="str">
-        <v>此處暫不顯示 TIFF 像素：瀏覽器不解碼 TIFF，且 16 位元 TIFF 中如何編碼 HDR 尚未決定（第 4.3 階段）。其嵌入的描述檔可以檢視。</v>
+        <v>不是 profiletool 能辨識的影像格式。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>无法在此显示该图像：</v>
+        <v>此处暂不显示 TIFF 像素：浏览器不解码 TIFF，且 16 位 TIFF 中如何编码 HDR 尚未确定（第 4.3 阶段）。其嵌入的配置文件可以查看。</v>
       </c>
       <c r="C441" t="str">
-        <v>無法在此顯示此影像：</v>
+        <v>此處暫不顯示 TIFF 像素：瀏覽器不解碼 TIFF，且 16 位元 TIFF 中如何編碼 HDR 尚未決定（第 4.3 階段）。其嵌入的描述檔可以檢視。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>其嵌入的配置文件仍可查看。</v>
+        <v>无法在此显示该图像：</v>
       </c>
       <c r="C442" t="str">
-        <v>其嵌入的描述檔仍可檢視。</v>
+        <v>無法在此顯示此影像：</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>显示方式</v>
+        <v>其嵌入的配置文件仍可查看。</v>
       </c>
       <c r="C443" t="str">
-        <v>顯示方式</v>
+        <v>其嵌入的描述檔仍可檢視。</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>浏览器</v>
+        <v>显示方式</v>
       </c>
       <c r="C444" t="str">
-        <v>瀏覽器</v>
+        <v>顯示方式</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>浏览器</v>
       </c>
       <c r="C445" t="str">
-        <v>profiletool</v>
+        <v>瀏覽器</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>HDR 显示器</v>
+        <v>profiletool</v>
       </c>
       <c r="C446" t="str">
-        <v>HDR 顯示器</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>浏览器会忽略仅由嵌入 ICC 配置文件标示的 HDR，因此该图像可能显得暗淡、平淡。</v>
+        <v>HDR 显示器</v>
       </c>
       <c r="C447" t="str">
-        <v>瀏覽器會忽略僅由嵌入 ICC 描述檔標示的 HDR，因此此影像可能看起來暗淡、平板。</v>
+        <v>HDR 顯示器</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>此浏览器无法在 SDR 与 HDR 之间切换图像，因此按浏览器的渲染显示。</v>
+        <v>浏览器会忽略仅由嵌入 ICC 配置文件标示的 HDR，因此该图像可能显得暗淡、平淡。</v>
       </c>
       <c r="C448" t="str">
-        <v>此瀏覽器無法在 SDR 與 HDR 之間切換影像，因此依瀏覽器的算繪顯示。</v>
+        <v>瀏覽器會忽略僅由嵌入 ICC 描述檔標示的 HDR，因此此影像可能看起來暗淡、平板。</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>浏览器无法解码此图像。</v>
+        <v>此浏览器无法在 SDR 与 HDR 之间切换图像，因此按浏览器的渲染显示。</v>
       </c>
       <c r="C449" t="str">
-        <v>瀏覽器無法解碼此影像。</v>
+        <v>此瀏覽器無法在 SDR 與 HDR 之間切換影像，因此依瀏覽器的算繪顯示。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>输出</v>
+        <v>浏览器无法解码此图像。</v>
       </c>
       <c r="C450" t="str">
-        <v>輸出</v>
+        <v>瀏覽器無法解碼此影像。</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>HDR 画布（float16）</v>
+        <v>输出</v>
       </c>
       <c r="C451" t="str">
-        <v>HDR 畫布（float16）</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU（扩展范围）</v>
+        <v>HDR 画布（float16）</v>
       </c>
       <c r="C452" t="str">
-        <v>WebGPU（延伸範圍）</v>
+        <v>HDR 畫布（float16）</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>SDR 画布（色调映射）</v>
+        <v>WebGPU（扩展范围）</v>
       </c>
       <c r="C453" t="str">
-        <v>SDR 畫布（色調映射）</v>
+        <v>WebGPU（延伸範圍）</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>尺寸</v>
+        <v>SDR 画布（色调映射）</v>
       </c>
       <c r="C454" t="str">
-        <v>尺寸</v>
+        <v>SDR 畫布（色調映射）</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>最亮像素</v>
+        <v>尺寸</v>
       </c>
       <c r="C455" t="str">
-        <v>最亮像素</v>
+        <v>尺寸</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>SDR 白的 {n} 倍</v>
+        <v>最亮像素</v>
       </c>
       <c r="C456" t="str">
-        <v>SDR 白的 {n} 倍</v>
+        <v>最亮像素</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>色度坐标</v>
+        <v>SDR 白的 {n} 倍</v>
       </c>
       <c r="C457" t="str">
-        <v>色度座標</v>
+        <v>SDR 白的 {n} 倍</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>未注明——假定为 Rec. 709</v>
+        <v>色度坐标</v>
       </c>
       <c r="C458" t="str">
-        <v>未註明——假定為 Rec. 709</v>
+        <v>色度座標</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>此处无法使用 {from}（{why}）；改用下一种输出。</v>
+        <v>未注明——假定为 Rec. 709</v>
       </c>
       <c r="C459" t="str">
-        <v>此處無法使用 {from}（{why}）；改用下一種輸出。</v>
+        <v>未註明——假定為 Rec. 709</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>此输出无法承载比白色更亮的值，因此显示经色调映射的 SDR 渲染。</v>
+        <v>此处无法使用 {from}（{why}）；改用下一种输出。</v>
       </c>
       <c r="C460" t="str">
-        <v>此輸出無法承載比白色更亮的值，因此顯示經色調映射的 SDR 算繪。</v>
+        <v>此處無法使用 {from}（{why}）；改用下一種輸出。</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>曝光</v>
+        <v>此输出无法承载比白色更亮的值，因此显示经色调映射的 SDR 渲染。</v>
       </c>
       <c r="C461" t="str">
-        <v>曝光</v>
+        <v>此輸出無法承載比白色更亮的值，因此顯示經色調映射的 SDR 算繪。</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} 档</v>
+        <v>曝光</v>
       </c>
       <c r="C462" t="str">
-        <v>{n} 檔</v>
+        <v>曝光</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>无法解码：</v>
+        <v>{n} 档</v>
       </c>
       <c r="C463" t="str">
-        <v>無法解碼：</v>
+        <v>{n} 檔</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>正在解码…</v>
+        <v>无法解码：</v>
       </c>
       <c r="C464" t="str">
-        <v>正在解碼…</v>
+        <v>無法解碼：</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>动态范围</v>
+        <v>正在解码…</v>
       </c>
       <c r="C465" t="str">
-        <v>動態範圍</v>
+        <v>正在解碼…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>此浏览器只提供两个端点，不支持混合。</v>
+        <v>动态范围</v>
       </c>
       <c r="C466" t="str">
-        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
+        <v>動態範圍</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>由 profiletool 自行解码，因此与浏览器无关</v>
+        <v>此浏览器只提供两个端点，不支持混合。</v>
       </c>
       <c r="C467" t="str">
-        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
+        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>此浏览器可以解码</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C468" t="str">
-        <v>此瀏覽器可以解碼</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>此浏览器无法解码</v>
+        <v>此浏览器可以解码</v>
       </c>
       <c r="C469" t="str">
-        <v>此瀏覽器無法解碼</v>
+        <v>此瀏覽器可以解碼</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
+        <v>此浏览器无法解码</v>
       </c>
       <c r="C470" t="str">
-        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
+        <v>此瀏覽器無法解碼</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
+        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
       </c>
       <c r="C471" t="str">
-        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
+        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>推迟到后续版本</v>
+        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
       </c>
       <c r="C472" t="str">
-        <v>延後至後續版本</v>
+        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
+        <v>推迟到后续版本</v>
       </c>
       <c r="C473" t="str">
-        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
+        <v>延後至後續版本</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
+        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
       </c>
       <c r="C474" t="str">
-        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
+        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
+        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
       </c>
       <c r="C475" t="str">
-        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
+        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>查看只需解析容器，不需要编解码器</v>
+        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
       </c>
       <c r="C476" t="str">
-        <v>檢視只需解析容器，不需要編解碼器</v>
+        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>HDR 显示器和 HDR 画布路径均可用</v>
+        <v>查看只需解析容器，不需要编解码器</v>
       </c>
       <c r="C477" t="str">
-        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
+        <v>檢視只需解析容器，不需要編解碼器</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>未知格式</v>
+        <v>HDR 显示器和 HDR 画布路径均可用</v>
       </c>
       <c r="C478" t="str">
-        <v>未知格式</v>
+        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{os} 上的 {browser}</v>
+        <v>未知格式</v>
       </c>
       <c r="C479" t="str">
-        <v>{os} 上的 {browser}</v>
+        <v>未知格式</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · 检测到 HDR 显示器</v>
+        <v>{os} 上的 {browser}</v>
       </c>
       <c r="C480" t="str">
-        <v>{name} · 偵測到 HDR 顯示器</v>
+        <v>{os} 上的 {browser}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · SDR 显示器</v>
+        <v>{name} · 检测到 HDR 显示器</v>
       </c>
       <c r="C481" t="str">
-        <v>{name} · SDR 顯示器</v>
+        <v>{name} · 偵測到 HDR 顯示器</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
+        <v>{name} · SDR 显示器</v>
       </c>
       <c r="C482" t="str">
-        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
+        <v>{name} · SDR 顯示器</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
+        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
       </c>
       <c r="C483" t="str">
-        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
+        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>显示器峰值</v>
+        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
       </c>
       <c r="C484" t="str">
-        <v>顯示器峰值</v>
+        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>SDR 白的 {r} 倍（{n} 档）</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C485" t="str">
-        <v>SDR 白的 {r} 倍（{n} 檔）</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× —— SDR 显示器</v>
+        <v>SDR 白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C486" t="str">
-        <v>1× —— SDR 顯示器</v>
+        <v>SDR 白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>未知</v>
+        <v>1× —— SDR 显示器</v>
       </c>
       <c r="C487" t="str">
-        <v>未知</v>
+        <v>1× —— SDR 顯示器</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
+        <v>未知</v>
       </c>
       <c r="C488" t="str">
-        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
+        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
       </c>
       <c r="C489" t="str">
-        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
+        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
+        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
       </c>
       <c r="C490" t="str">
-        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
+        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>适配显示器</v>
+        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
       </c>
       <c r="C491" t="str">
-        <v>符合顯示器</v>
+        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
+        <v>适配显示器</v>
       </c>
       <c r="C492" t="str">
-        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
+        <v>符合顯示器</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>无上限</v>
+        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
       </c>
       <c r="C493" t="str">
-        <v>無上限</v>
+        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>上限 {n} 档（{r}×）</v>
+        <v>无上限</v>
       </c>
       <c r="C494" t="str">
-        <v>上限 {n} 檔（{r}×）</v>
+        <v>無上限</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>SDR 白</v>
+        <v>上限 {n} 档（{r}×）</v>
       </c>
       <c r="C495" t="str">
-        <v>SDR 白</v>
+        <v>上限 {n} 檔（{r}×）</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
+        <v>SDR 白</v>
       </c>
       <c r="C496" t="str">
-        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>SDR 白色色块</v>
+        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
       </c>
       <c r="C497" t="str">
-        <v>SDR 白色色塊</v>
+        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>拖动即可移动；双击可将其放回图像旁边。</v>
+        <v>SDR 白色色块</v>
       </c>
       <c r="C498" t="str">
-        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
+        <v>SDR 白色色塊</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>指定配置文件</v>
+        <v>拖动即可移动；双击可将其放回图像旁边。</v>
       </c>
       <c r="C499" t="str">
-        <v>指定描述檔</v>
+        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>无——按文件自身标示</v>
+        <v>指定配置文件</v>
       </c>
       <c r="C500" t="str">
-        <v>無——依檔案本身標示</v>
+        <v>指定描述檔</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>嵌入的配置文件（{n} B）</v>
+        <v>无——按文件自身标示</v>
       </c>
       <c r="C501" t="str">
-        <v>嵌入的描述檔（{n} B）</v>
+        <v>無——依檔案本身標示</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>池中的 HDR 配置文件</v>
+        <v>嵌入的配置文件（{n} B）</v>
       </c>
       <c r="C502" t="str">
-        <v>池中的 HDR 描述檔</v>
+        <v>嵌入的描述檔（{n} B）</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>配置文件</v>
+        <v>池中的 HDR 配置文件</v>
       </c>
       <c r="C503" t="str">
-        <v>描述檔</v>
+        <v>池中的 HDR 描述檔</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>嵌入的配置文件</v>
+        <v>配置文件</v>
       </c>
       <c r="C504" t="str">
-        <v>嵌入的描述檔</v>
+        <v>描述檔</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>色彩引擎路径</v>
+        <v>嵌入的配置文件</v>
       </c>
       <c r="C505" t="str">
-        <v>色彩引擎路徑</v>
+        <v>嵌入的描述檔</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR 路径，已应用增益曲线</v>
+        <v>色彩引擎路径</v>
       </c>
       <c r="C506" t="str">
-        <v>HDR 路徑，已套用增益曲線</v>
+        <v>色彩引擎路徑</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR 路径，无增益曲线</v>
+        <v>HDR 路径，已应用增益曲线</v>
       </c>
       <c r="C507" t="str">
-        <v>HDR 路徑，無增益曲線</v>
+        <v>HDR 路徑，已套用增益曲線</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>预烘焙的 AToB0——不是 HDR 路径</v>
+        <v>HDR 路径，无增益曲线</v>
       </c>
       <c r="C508" t="str">
-        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
+        <v>HDR 路徑，無增益曲線</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>传递函数</v>
+        <v>预烘焙的 AToB0——不是 HDR 路径</v>
       </c>
       <c r="C509" t="str">
-        <v>傳遞函數</v>
+        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>HDR 参考白</v>
+        <v>传递函数</v>
       </c>
       <c r="C510" t="str">
-        <v>HDR 參考白</v>
+        <v>傳遞函數</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>目标余量</v>
+        <v>HDR 参考白</v>
       </c>
       <c r="C511" t="str">
-        <v>目標餘量</v>
+        <v>HDR 參考白</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>参考白的 {r} 倍（{n} 档）</v>
+        <v>目标余量</v>
       </c>
       <c r="C512" t="str">
-        <v>參考白的 {r} 倍（{n} 檔）</v>
+        <v>目標餘量</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>色调映射</v>
+        <v>参考白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C513" t="str">
-        <v>色調映射</v>
+        <v>參考白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>自动（第 8.10.3 条排序）</v>
+        <v>色调映射</v>
       </c>
       <c r="C514" t="str">
-        <v>自動（第 8.10.3 條排序）</v>
+        <v>色調映射</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>增益曲线（HAGC）</v>
+        <v>自动（第 8.10.3 条排序）</v>
       </c>
       <c r="C515" t="str">
-        <v>增益曲線（HAGC）</v>
+        <v>自動（第 8.10.3 條排序）</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>预烘焙的 SDR 回退（AToB0）</v>
+        <v>增益曲线（HAGC）</v>
       </c>
       <c r="C516" t="str">
-        <v>預先烘焙的 SDR 備援（AToB0）</v>
+        <v>增益曲線（HAGC）</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>关闭——与修订前的 CMM 相同</v>
+        <v>预烘焙的 SDR 回退（AToB0）</v>
       </c>
       <c r="C517" t="str">
-        <v>關閉——與修訂前的 CMM 相同</v>
+        <v>預先烘焙的 SDR 備援（AToB0）</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>正在应用配置文件…</v>
+        <v>关闭——与修订前的 CMM 相同</v>
       </c>
       <c r="C518" t="str">
-        <v>正在套用描述檔…</v>
+        <v>關閉——與修訂前的 CMM 相同</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
+        <v>正在应用配置文件…</v>
       </c>
       <c r="C519" t="str">
-        <v>OpenEXR 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
+        <v>正在套用描述檔…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>指定配置文件需要 3 通道 RGB 图像。</v>
+        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
       </c>
       <c r="C520" t="str">
-        <v>指定描述檔需要 3 通道 RGB 影像。</v>
+        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>要解释其数值，请在上方指定配置文件。</v>
+        <v>指定配置文件需要 3 通道 RGB 图像。</v>
       </c>
       <c r="C521" t="str">
-        <v>若要解讀其數值，請在上方指定描述檔。</v>
+        <v>指定描述檔需要 3 通道 RGB 影像。</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR 配置文件</v>
+        <v>要解释其数值，请在上方指定配置文件。</v>
       </c>
       <c r="C522" t="str">
-        <v>HDR 描述檔</v>
+        <v>若要解讀其數值，請在上方指定描述檔。</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>线性传递函数</v>
+        <v>HDR 配置文件</v>
       </c>
       <c r="C523" t="str">
-        <v>線性傳遞函數</v>
+        <v>HDR 描述檔</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>非线性传递函数（PQ、HLG）</v>
+        <v>线性传递函数</v>
       </c>
       <c r="C524" t="str">
-        <v>非線性傳遞函數（PQ、HLG）</v>
+        <v>線性傳遞函數</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>HDR 配置文件——线性传递函数</v>
+        <v>非线性传递函数（PQ、HLG）</v>
       </c>
       <c r="C525" t="str">
-        <v>HDR 描述檔——線性傳遞函數</v>
+        <v>非線性傳遞函數（PQ、HLG）</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR 配置文件——PQ / HLG 传递函数</v>
+        <v>HDR 配置文件——线性传递函数</v>
       </c>
       <c r="C526" t="str">
-        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
+        <v>HDR 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
+        <v>HDR 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C527" t="str">
-        <v>OpenEXR 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
+        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
+        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
       </c>
       <c r="C528" t="str">
-        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
+        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
+        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C529" t="str">
-        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
+        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
       </c>
       <c r="C530" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>显示余量</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C531" t="str">
-        <v>顯示餘量</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>显示余量</v>
       </c>
       <c r="C532" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>基准</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C533" t="str">
-        <v>基準</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>基准</v>
       </c>
       <c r="C534" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C535" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C536" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C537" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C538" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C539" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C540" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C541" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C542" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>此余量下应用的增益</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C543" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C544" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>增益（log2 档）</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C545" t="str">
-        <v>增益（log2 檔）</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C546" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C547" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C548" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>不变</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C549" t="str">
-        <v>不變</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>不变</v>
       </c>
       <c r="C550" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>{h} 档处的输出</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C551" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C552" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>识别显示器</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C553" t="str">
-        <v>識別顯示器</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C554" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C555" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C556" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C557" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>无法识别显示器。</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C558" t="str">
-        <v>無法識別顯示器。</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>显示事件</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C559" t="str">
-        <v>顯示事件</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>显示事件</v>
       </c>
       <c r="C560" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>色度基色</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C561" t="str">
-        <v>色度基色</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>传递特性</v>
+        <v>色度基色</v>
       </c>
       <c r="C562" t="str">
-        <v>轉換特性</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>矩阵系数</v>
+        <v>传递特性</v>
       </c>
       <c r="C563" t="str">
-        <v>矩陣係數</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>视频全范围标志</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C564" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>全范围</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C565" t="str">
-        <v>全範圍</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>有限范围</v>
+        <v>全范围</v>
       </c>
       <c r="C566" t="str">
-        <v>有限範圍</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>有限范围</v>
       </c>
       <c r="C567" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C568" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C569" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>报告</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C570" t="str">
-        <v>報告</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C571" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C572" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C573" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C574" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C575" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C576" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C577" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C578" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C579" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C580" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C581" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C582" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C583" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C584" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C585" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C586" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C587" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C588" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C589" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C590" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C591" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C592" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C593" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C594" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C595" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C596" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C597" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C598" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C599" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C600" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C601" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C602" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C603" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C604" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C605" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C606" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C607" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C608" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C609" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C610" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C611" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C612" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C613" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C614" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C615" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C616" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C617" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C618" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C619" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C620" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C621" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C622" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C623" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C624" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C625" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C626" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C627" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C628" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C629" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C630" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C631" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C632" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C633" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C634" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C635" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C636" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C637" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C638" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C639" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C640" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C641" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C642" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C643" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C644" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C645" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C646" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C647" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C648" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C649" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C650" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C651" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C652" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C653" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C654" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C655" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C656" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C657" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C658" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C658" t="str">
+      <c r="C659" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C659"/>
+  <dimension ref="A1:C670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5827,1844 +5827,1965 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
+        <v>图像详情</v>
       </c>
       <c r="C493" t="str">
-        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
+        <v>影像詳細資訊</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>无上限</v>
+        <v>不可用——此图像由浏览器渲染，无法将其限制在指定峰值</v>
       </c>
       <c r="C494" t="str">
-        <v>無上限</v>
+        <v>無法使用——此影像由瀏覽器算繪，無法將其限制在指定峰值</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>上限 {n} 档（{r}×）</v>
+        <v>不可用——此输出无法显示高于 SDR 白的内容</v>
       </c>
       <c r="C495" t="str">
-        <v>上限 {n} 檔（{r}×）</v>
+        <v>無法使用——此輸出無法顯示高於 SDR 白的內容</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>SDR 白</v>
+        <v>不可用——此显示器的峰值未知</v>
       </c>
       <c r="C496" t="str">
-        <v>SDR 白</v>
+        <v>無法使用——此顯示器的峰值未知</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
+        <v>放大</v>
       </c>
       <c r="C497" t="str">
-        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
+        <v>放大</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>SDR 白色色块</v>
+        <v>缩小</v>
       </c>
       <c r="C498" t="str">
-        <v>SDR 白色色塊</v>
+        <v>縮小</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>拖动即可移动；双击可将其放回图像旁边。</v>
+        <v>适合图像</v>
       </c>
       <c r="C499" t="str">
-        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
+        <v>符合影像</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>指定配置文件</v>
+        <v>实际像素（1:1）</v>
       </c>
       <c r="C500" t="str">
-        <v>指定描述檔</v>
+        <v>實際像素（1:1）</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>无——按文件自身标示</v>
+        <v>拖动平移 · Ctrl+滚轮缩放 · 双击复位</v>
       </c>
       <c r="C501" t="str">
-        <v>無——依檔案本身標示</v>
+        <v>拖曳平移 · Ctrl+滾輪縮放 · 按兩下復位</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>嵌入的配置文件（{n} B）</v>
+        <v>拖动以调整图像区域大小；双击恢复默认大小</v>
       </c>
       <c r="C502" t="str">
-        <v>嵌入的描述檔（{n} B）</v>
+        <v>拖曳以調整影像區域大小；按兩下還原預設大小</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>池中的 HDR 配置文件</v>
+        <v>图像视图</v>
       </c>
       <c r="C503" t="str">
-        <v>池中的 HDR 描述檔</v>
+        <v>影像檢視</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>配置文件</v>
+        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
       </c>
       <c r="C504" t="str">
-        <v>描述檔</v>
+        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>嵌入的配置文件</v>
+        <v>无上限</v>
       </c>
       <c r="C505" t="str">
-        <v>嵌入的描述檔</v>
+        <v>無上限</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>色彩引擎路径</v>
+        <v>上限 {n} 档（{r}×）</v>
       </c>
       <c r="C506" t="str">
-        <v>色彩引擎路徑</v>
+        <v>上限 {n} 檔（{r}×）</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>HDR 路径，已应用增益曲线</v>
+        <v>SDR 白</v>
       </c>
       <c r="C507" t="str">
-        <v>HDR 路徑，已套用增益曲線</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>HDR 路径，无增益曲线</v>
+        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
       </c>
       <c r="C508" t="str">
-        <v>HDR 路徑，無增益曲線</v>
+        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>预烘焙的 AToB0——不是 HDR 路径</v>
+        <v>SDR 白色色块</v>
       </c>
       <c r="C509" t="str">
-        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
+        <v>SDR 白色色塊</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>传递函数</v>
+        <v>拖动即可移动；双击可将其放回图像旁边。</v>
       </c>
       <c r="C510" t="str">
-        <v>傳遞函數</v>
+        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>HDR 参考白</v>
+        <v>指定配置文件</v>
       </c>
       <c r="C511" t="str">
-        <v>HDR 參考白</v>
+        <v>指定描述檔</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>目标余量</v>
+        <v>无——按文件自身标示</v>
       </c>
       <c r="C512" t="str">
-        <v>目標餘量</v>
+        <v>無——依檔案本身標示</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>参考白的 {r} 倍（{n} 档）</v>
+        <v>嵌入的配置文件（{n} B）</v>
       </c>
       <c r="C513" t="str">
-        <v>參考白的 {r} 倍（{n} 檔）</v>
+        <v>嵌入的描述檔（{n} B）</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>色调映射</v>
+        <v>池中的 HDR 配置文件</v>
       </c>
       <c r="C514" t="str">
-        <v>色調映射</v>
+        <v>池中的 HDR 描述檔</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>自动（第 8.10.3 条排序）</v>
+        <v>配置文件</v>
       </c>
       <c r="C515" t="str">
-        <v>自動（第 8.10.3 條排序）</v>
+        <v>描述檔</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>增益曲线（HAGC）</v>
+        <v>嵌入的配置文件</v>
       </c>
       <c r="C516" t="str">
-        <v>增益曲線（HAGC）</v>
+        <v>嵌入的描述檔</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>预烘焙的 SDR 回退（AToB0）</v>
+        <v>色彩引擎路径</v>
       </c>
       <c r="C517" t="str">
-        <v>預先烘焙的 SDR 備援（AToB0）</v>
+        <v>色彩引擎路徑</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>关闭——与修订前的 CMM 相同</v>
+        <v>HDR 路径，已应用增益曲线</v>
       </c>
       <c r="C518" t="str">
-        <v>關閉——與修訂前的 CMM 相同</v>
+        <v>HDR 路徑，已套用增益曲線</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>正在应用配置文件…</v>
+        <v>HDR 路径，无增益曲线</v>
       </c>
       <c r="C519" t="str">
-        <v>正在套用描述檔…</v>
+        <v>HDR 路徑，無增益曲線</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
+        <v>预烘焙的 AToB0——不是 HDR 路径</v>
       </c>
       <c r="C520" t="str">
-        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
+        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>指定配置文件需要 3 通道 RGB 图像。</v>
+        <v>传递函数</v>
       </c>
       <c r="C521" t="str">
-        <v>指定描述檔需要 3 通道 RGB 影像。</v>
+        <v>傳遞函數</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>要解释其数值，请在上方指定配置文件。</v>
+        <v>HDR 参考白</v>
       </c>
       <c r="C522" t="str">
-        <v>若要解讀其數值，請在上方指定描述檔。</v>
+        <v>HDR 參考白</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR 配置文件</v>
+        <v>目标余量</v>
       </c>
       <c r="C523" t="str">
-        <v>HDR 描述檔</v>
+        <v>目標餘量</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>线性传递函数</v>
+        <v>参考白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C524" t="str">
-        <v>線性傳遞函數</v>
+        <v>參考白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>非线性传递函数（PQ、HLG）</v>
+        <v>色调映射</v>
       </c>
       <c r="C525" t="str">
-        <v>非線性傳遞函數（PQ、HLG）</v>
+        <v>色調映射</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>HDR 配置文件——线性传递函数</v>
+        <v>自动（第 8.10.3 条排序）</v>
       </c>
       <c r="C526" t="str">
-        <v>HDR 描述檔——線性傳遞函數</v>
+        <v>自動（第 8.10.3 條排序）</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR 配置文件——PQ / HLG 传递函数</v>
+        <v>增益曲线（HAGC）</v>
       </c>
       <c r="C527" t="str">
-        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
+        <v>增益曲線（HAGC）</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
+        <v>预烘焙的 SDR 回退（AToB0）</v>
       </c>
       <c r="C528" t="str">
-        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
+        <v>預先烘焙的 SDR 備援（AToB0）</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
+        <v>关闭——与修订前的 CMM 相同</v>
       </c>
       <c r="C529" t="str">
-        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
+        <v>關閉——與修訂前的 CMM 相同</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
+        <v>正在应用配置文件…</v>
       </c>
       <c r="C530" t="str">
-        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
+        <v>正在套用描述檔…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
       </c>
       <c r="C531" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>显示余量</v>
+        <v>指定配置文件需要 3 通道 RGB 图像。</v>
       </c>
       <c r="C532" t="str">
-        <v>顯示餘量</v>
+        <v>指定描述檔需要 3 通道 RGB 影像。</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>要解释其数值，请在上方指定配置文件。</v>
       </c>
       <c r="C533" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>若要解讀其數值，請在上方指定描述檔。</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>基准</v>
+        <v>HDR 配置文件</v>
       </c>
       <c r="C534" t="str">
-        <v>基準</v>
+        <v>HDR 描述檔</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>线性传递函数</v>
       </c>
       <c r="C535" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>線性傳遞函數</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>非线性传递函数（PQ、HLG）</v>
       </c>
       <c r="C536" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>非線性傳遞函數（PQ、HLG）</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>HDR 配置文件——线性传递函数</v>
       </c>
       <c r="C537" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>HDR 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>HDR 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C538" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
       </c>
       <c r="C539" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C540" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
       </c>
       <c r="C541" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C542" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>显示余量</v>
       </c>
       <c r="C543" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>此余量下应用的增益</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C544" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>基准</v>
       </c>
       <c r="C545" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>增益（log2 档）</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C546" t="str">
-        <v>增益（log2 檔）</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C547" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C548" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C549" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>不变</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C550" t="str">
-        <v>不變</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C551" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>{h} 档处的输出</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C552" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C553" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>识别显示器</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C554" t="str">
-        <v>識別顯示器</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C555" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C556" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C557" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C558" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>无法识别显示器。</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C559" t="str">
-        <v>無法識別顯示器。</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>显示事件</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C560" t="str">
-        <v>顯示事件</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>不变</v>
       </c>
       <c r="C561" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>色度基色</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C562" t="str">
-        <v>色度基色</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>传递特性</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C563" t="str">
-        <v>轉換特性</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>矩阵系数</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C564" t="str">
-        <v>矩陣係數</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>视频全范围标志</v>
+        <v>识别显示器</v>
       </c>
       <c r="C565" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>全范围</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C566" t="str">
-        <v>全範圍</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>有限范围</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C567" t="str">
-        <v>有限範圍</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C568" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C569" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C570" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>报告</v>
+        <v>显示事件</v>
       </c>
       <c r="C571" t="str">
-        <v>報告</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>失败</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C572" t="str">
-        <v>失敗</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>项检查</v>
+        <v>色度基色</v>
       </c>
       <c r="C573" t="str">
-        <v>項檢查</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>传递特性</v>
       </c>
       <c r="C574" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C575" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C576" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>全范围</v>
       </c>
       <c r="C577" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>订阅</v>
+        <v>有限范围</v>
       </c>
       <c r="C578" t="str">
-        <v>訂閱</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C579" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>订阅新版本通知</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C580" t="str">
-        <v>訂閱新版本通知</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>关闭</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C581" t="str">
-        <v>關閉</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>报告</v>
       </c>
       <c r="C582" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>电子邮件地址</v>
+        <v>失败</v>
       </c>
       <c r="C583" t="str">
-        <v>電子郵件地址</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>you@example.com</v>
+        <v>项检查</v>
       </c>
       <c r="C584" t="str">
-        <v>you@example.com</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C585" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>（选填）</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C586" t="str">
-        <v>（選填）</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C587" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C588" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>取消</v>
+        <v>订阅</v>
       </c>
       <c r="C589" t="str">
-        <v>取消</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>订阅</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C590" t="str">
-        <v>訂閱</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C591" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>关闭</v>
       </c>
       <c r="C592" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>关闭</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C593" t="str">
-        <v>關閉</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>隐私声明</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C594" t="str">
-        <v>隱私聲明</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C595" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C596" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>请检查表单后重试。</v>
+        <v>（选填）</v>
       </c>
       <c r="C597" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C598" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>网络错误，请重试。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C599" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>错误：</v>
+        <v>取消</v>
       </c>
       <c r="C600" t="str">
-        <v>錯誤：</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>转换为 XML</v>
+        <v>订阅</v>
       </c>
       <c r="C601" t="str">
-        <v>轉換為 XML</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>转换为 JSON</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C602" t="str">
-        <v>轉換為 JSON</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>转换为 ICC</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C603" t="str">
-        <v>轉換為 ICC</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>正在转换为 XML…</v>
+        <v>关闭</v>
       </c>
       <c r="C604" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>隐私声明</v>
       </c>
       <c r="C605" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C606" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C607" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C608" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>配置文件 ID</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C609" t="str">
-        <v>設定檔 ID</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>未找到标签。</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C610" t="str">
-        <v>找不到標籤。</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>标签名称</v>
+        <v>错误：</v>
       </c>
       <c r="C611" t="str">
-        <v>標籤名稱</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C612" t="str">
-        <v>ID</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>偏移</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C613" t="str">
-        <v>偏移</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>大小</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C614" t="str">
-        <v>大小</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>填充</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C615" t="str">
-        <v>填充</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>加载后字节已更改</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C616" t="str">
-        <v>載入後位元組已變更</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>类型</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C617" t="str">
-        <v>類型</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>{type} 数组</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C618" t="str">
-        <v>{type} 陣列</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>（无内容）</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C619" t="str">
-        <v>（無內容）</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>字节</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C620" t="str">
-        <v>位元組</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>正在加载完整描述…</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C621" t="str">
-        <v>正在載入完整描述…</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>无法加载完整描述：</v>
+        <v>标签名称</v>
       </c>
       <c r="C622" t="str">
-        <v>無法載入完整描述：</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>ID</v>
       </c>
       <c r="C623" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>偏移</v>
       </c>
       <c r="C624" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>无验证输出</v>
+        <v>大小</v>
       </c>
       <c r="C625" t="str">
-        <v>無驗證輸出</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>配置文件有效</v>
+        <v>填充</v>
       </c>
       <c r="C626" t="str">
-        <v>設定檔有效</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>配置文件有警告</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C627" t="str">
-        <v>設定檔有警告</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>配置文件不合规</v>
+        <v>类型</v>
       </c>
       <c r="C628" t="str">
-        <v>設定檔不符合規範</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>严重验证错误</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C629" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>未知验证状态</v>
+        <v>（无内容）</v>
       </c>
       <c r="C630" t="str">
-        <v>未知驗證狀態</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>字节</v>
       </c>
       <c r="C631" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>未发现警告或错误。</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C632" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>有效</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C633" t="str">
-        <v>有效</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>警告</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C634" t="str">
-        <v>警告</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>错误</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C635" t="str">
-        <v>錯誤</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>未知</v>
+        <v>无验证输出</v>
       </c>
       <c r="C636" t="str">
-        <v>未知</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>通过</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C637" t="str">
-        <v>通過</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>失败</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C638" t="str">
-        <v>失敗</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>在上下文中查看</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C639" t="str">
-        <v>在上下文中檢視</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>验证详情</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C640" t="str">
-        <v>驗證詳情</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>触发字段</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C641" t="str">
-        <v>觸發欄位</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>字段</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C642" t="str">
-        <v>欄位</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>当前值</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C643" t="str">
-        <v>目前值</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>要求：0</v>
+        <v>有效</v>
       </c>
       <c r="C644" t="str">
-        <v>要求：0</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>预期：{value}</v>
+        <v>警告</v>
       </c>
       <c r="C645" t="str">
-        <v>預期：{value}</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>无效</v>
+        <v>错误</v>
       </c>
       <c r="C646" t="str">
-        <v>無效</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>未知</v>
       </c>
       <c r="C647" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>关闭</v>
+        <v>通过</v>
       </c>
       <c r="C648" t="str">
-        <v>關閉</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>失败</v>
       </c>
       <c r="C649" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C650" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>验证详情</v>
       </c>
       <c r="C651" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>触发字段</v>
       </c>
       <c r="C652" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>字段</v>
       </c>
       <c r="C653" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>当前值</v>
       </c>
       <c r="C654" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>要求：0</v>
       </c>
       <c r="C655" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C656" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>缩进</v>
+        <v>无效</v>
       </c>
       <c r="C657" t="str">
-        <v>縮排</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>排序键</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C658" t="str">
-        <v>排序鍵</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C659" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C660" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C661" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C662" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C663" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C664" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C665" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C666" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C667" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C668" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C669" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C659" t="str">
+      <c r="C670" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C670"/>
+  <dimension ref="A1:C693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6410,1382 +6410,1635 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>通过色彩引擎预览</v>
       </c>
       <c r="C546" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>透過色彩引擎預覽</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>原始效果（基线 {h} 档，无增益）</v>
       </c>
       <c r="C547" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>原始效果（基準 {h} 檔，無增益）</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>针对 {h} 档色调映射</v>
       </c>
       <c r="C548" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>針對 {h} 檔色調對應</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
       </c>
       <c r="C549" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>参考白</v>
       </c>
       <c r="C550" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>參考白</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C551" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>预览不可用：{why}</v>
       </c>
       <c r="C552" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>無法預覽：{why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
       </c>
       <c r="C553" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>所有余量下的增益</v>
       </c>
       <c r="C554" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>所有餘裕下的增益</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>此余量下应用的增益</v>
+        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
       </c>
       <c r="C555" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>输入（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C556" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>輸入（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>增益（log2 档）</v>
+        <v>显示余量（档）</v>
       </c>
       <c r="C557" t="str">
-        <v>增益（log2 檔）</v>
+        <v>顯示餘裕（檔）</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>增益（档）</v>
       </c>
       <c r="C558" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>增益（檔）</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>标签中的曲线</v>
       </c>
       <c r="C559" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>標籤中的曲線</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>基线</v>
       </c>
       <c r="C560" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>不变</v>
+        <v>滑块</v>
       </c>
       <c r="C561" t="str">
-        <v>不變</v>
+        <v>滑桿</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>输入 = 显示器峰值</v>
       </c>
       <c r="C562" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>輸入 = 顯示器峰值</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>{h} 档处的输出</v>
+        <v>按余量的灰色色调曲线</v>
       </c>
       <c r="C563" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>依餘裕的灰色色調曲線</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
       </c>
       <c r="C564" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>识别显示器</v>
+        <v>输出（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C565" t="str">
-        <v>識別顯示器</v>
+        <v>輸出（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>{h} 档</v>
       </c>
       <c r="C566" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>{h} 檔</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>{h} 档（基线）</v>
       </c>
       <c r="C567" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>{h} 檔（基準）</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>{h} 档（滑块）</v>
       </c>
       <c r="C568" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>{h} 檔（滑桿）</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C569" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>无法识别显示器。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C570" t="str">
-        <v>無法識別顯示器。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>显示事件</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C571" t="str">
-        <v>顯示事件</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C572" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>色度基色</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C573" t="str">
-        <v>色度基色</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>传递特性</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C574" t="str">
-        <v>轉換特性</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>矩阵系数</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C575" t="str">
-        <v>矩陣係數</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>视频全范围标志</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C576" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>全范围</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C577" t="str">
-        <v>全範圍</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>有限范围</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C578" t="str">
-        <v>有限範圍</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C579" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C580" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C581" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>报告</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C582" t="str">
-        <v>報告</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>失败</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C583" t="str">
-        <v>失敗</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>项检查</v>
+        <v>不变</v>
       </c>
       <c r="C584" t="str">
-        <v>項檢查</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C585" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C586" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C587" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>识别显示器</v>
       </c>
       <c r="C588" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>订阅</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C589" t="str">
-        <v>訂閱</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C590" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>订阅新版本通知</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C591" t="str">
-        <v>訂閱新版本通知</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>关闭</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C592" t="str">
-        <v>關閉</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C593" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>电子邮件地址</v>
+        <v>显示事件</v>
       </c>
       <c r="C594" t="str">
-        <v>電子郵件地址</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>you@example.com</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C595" t="str">
-        <v>you@example.com</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>色度基色</v>
       </c>
       <c r="C596" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>（选填）</v>
+        <v>传递特性</v>
       </c>
       <c r="C597" t="str">
-        <v>（選填）</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C598" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C599" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>取消</v>
+        <v>全范围</v>
       </c>
       <c r="C600" t="str">
-        <v>取消</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>订阅</v>
+        <v>有限范围</v>
       </c>
       <c r="C601" t="str">
-        <v>訂閱</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C602" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C603" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>关闭</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C604" t="str">
-        <v>關閉</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>隐私声明</v>
+        <v>报告</v>
       </c>
       <c r="C605" t="str">
-        <v>隱私聲明</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>失败</v>
       </c>
       <c r="C606" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>项检查</v>
       </c>
       <c r="C607" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>请检查表单后重试。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C608" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C609" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>网络错误，请重试。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C610" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>错误：</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C611" t="str">
-        <v>錯誤：</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>转换为 XML</v>
+        <v>订阅</v>
       </c>
       <c r="C612" t="str">
-        <v>轉換為 XML</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>转换为 JSON</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C613" t="str">
-        <v>轉換為 JSON</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>转换为 ICC</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C614" t="str">
-        <v>轉換為 ICC</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>正在转换为 XML…</v>
+        <v>关闭</v>
       </c>
       <c r="C615" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C616" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C617" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>you@example.com</v>
       </c>
       <c r="C618" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C619" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>配置文件 ID</v>
+        <v>（选填）</v>
       </c>
       <c r="C620" t="str">
-        <v>設定檔 ID</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>未找到标签。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C621" t="str">
-        <v>找不到標籤。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>标签名称</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C622" t="str">
-        <v>標籤名稱</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>取消</v>
       </c>
       <c r="C623" t="str">
-        <v>ID</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>偏移</v>
+        <v>订阅</v>
       </c>
       <c r="C624" t="str">
-        <v>偏移</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>大小</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C625" t="str">
-        <v>大小</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>填充</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C626" t="str">
-        <v>填充</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>加载后字节已更改</v>
+        <v>关闭</v>
       </c>
       <c r="C627" t="str">
-        <v>載入後位元組已變更</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>类型</v>
+        <v>隐私声明</v>
       </c>
       <c r="C628" t="str">
-        <v>類型</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>{type} 数组</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C629" t="str">
-        <v>{type} 陣列</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>（无内容）</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C630" t="str">
-        <v>（無內容）</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>字节</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C631" t="str">
-        <v>位元組</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>正在加载完整描述…</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C632" t="str">
-        <v>正在載入完整描述…</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>无法加载完整描述：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C633" t="str">
-        <v>無法載入完整描述：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>错误：</v>
       </c>
       <c r="C634" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C635" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>无验证输出</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C636" t="str">
-        <v>無驗證輸出</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>配置文件有效</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C637" t="str">
-        <v>設定檔有效</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>配置文件有警告</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C638" t="str">
-        <v>設定檔有警告</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>配置文件不合规</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C639" t="str">
-        <v>設定檔不符合規範</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>严重验证错误</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C640" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>未知验证状态</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C641" t="str">
-        <v>未知驗證狀態</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C642" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>未发现警告或错误。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C643" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>有效</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C644" t="str">
-        <v>有效</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>警告</v>
+        <v>标签名称</v>
       </c>
       <c r="C645" t="str">
-        <v>警告</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>错误</v>
+        <v>ID</v>
       </c>
       <c r="C646" t="str">
-        <v>錯誤</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>未知</v>
+        <v>偏移</v>
       </c>
       <c r="C647" t="str">
-        <v>未知</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>通过</v>
+        <v>大小</v>
       </c>
       <c r="C648" t="str">
-        <v>通過</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>失败</v>
+        <v>填充</v>
       </c>
       <c r="C649" t="str">
-        <v>失敗</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>在上下文中查看</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C650" t="str">
-        <v>在上下文中檢視</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>验证详情</v>
+        <v>类型</v>
       </c>
       <c r="C651" t="str">
-        <v>驗證詳情</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>触发字段</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C652" t="str">
-        <v>觸發欄位</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>字段</v>
+        <v>（无内容）</v>
       </c>
       <c r="C653" t="str">
-        <v>欄位</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>当前值</v>
+        <v>字节</v>
       </c>
       <c r="C654" t="str">
-        <v>目前值</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>要求：0</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C655" t="str">
-        <v>要求：0</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>预期：{value}</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C656" t="str">
-        <v>預期：{value}</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>无效</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C657" t="str">
-        <v>無效</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C658" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>关闭</v>
+        <v>无验证输出</v>
       </c>
       <c r="C659" t="str">
-        <v>關閉</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C660" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C661" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C662" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C663" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C664" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C665" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C666" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>有效</v>
       </c>
       <c r="C667" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>缩进</v>
+        <v>警告</v>
       </c>
       <c r="C668" t="str">
-        <v>縮排</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>排序键</v>
+        <v>错误</v>
       </c>
       <c r="C669" t="str">
-        <v>排序鍵</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C670" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C671" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C672" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C673" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C674" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C675" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C676" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C677" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C678" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C679" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C680" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C681" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C682" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C683" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C684" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C685" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C686" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C687" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C688" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C689" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C690" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C691" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C692" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C670" t="str">
+      <c r="C693" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C693"/>
+  <dimension ref="A1:C700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6157,1888 +6157,1965 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>目标余量</v>
+        <v>线性值</v>
       </c>
       <c r="C523" t="str">
-        <v>目標餘量</v>
+        <v>線性值</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>参考白的 {r} 倍（{n} 档）</v>
+        <v>文件 1.0 = HDR 参考白</v>
       </c>
       <c r="C524" t="str">
-        <v>參考白的 {r} 倍（{n} 檔）</v>
+        <v>檔案 1.0 = HDR 參考白</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>色调映射</v>
+        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 条）</v>
       </c>
       <c r="C525" t="str">
-        <v>色調映射</v>
+        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 條）</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>自动（第 8.10.3 条排序）</v>
+        <v>OpenEXR 和 Radiance HDR 文件按惯例将 SDR 白置于 1.0，而 ICC 线性传递函数把 1.0 读作 1 cd/m²。默认会缩放文件，使其 1.0 落在配置文件的 HDR 参考白上。</v>
       </c>
       <c r="C526" t="str">
-        <v>自動（第 8.10.3 條排序）</v>
+        <v>OpenEXR 與 Radiance HDR 檔案依慣例將 SDR 白置於 1.0，而 ICC 線性傳遞函數將 1.0 讀作 1 cd/m²。預設會縮放檔案，使其 1.0 落在描述檔的 HDR 參考白上。</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>增益曲线（HAGC）</v>
+        <v>输入缩放</v>
       </c>
       <c r="C527" t="str">
-        <v>增益曲線（HAGC）</v>
+        <v>輸入縮放</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>预烘焙的 SDR 回退（AToB0）</v>
+        <v>×{w} — 文件 1.0 = 参考白</v>
       </c>
       <c r="C528" t="str">
-        <v>預先烘焙的 SDR 備援（AToB0）</v>
+        <v>×{w} — 檔案 1.0 = 參考白</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>关闭——与修订前的 CMM 相同</v>
+        <v>无 — 文件 1.0 = 1 cd/m²</v>
       </c>
       <c r="C529" t="str">
-        <v>關閉——與修訂前的 CMM 相同</v>
+        <v>無 — 檔案 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>正在应用配置文件…</v>
+        <v>目标余量</v>
       </c>
       <c r="C530" t="str">
-        <v>正在套用描述檔…</v>
+        <v>目標餘量</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
+        <v>参考白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C531" t="str">
-        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
+        <v>參考白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>指定配置文件需要 3 通道 RGB 图像。</v>
+        <v>色调映射</v>
       </c>
       <c r="C532" t="str">
-        <v>指定描述檔需要 3 通道 RGB 影像。</v>
+        <v>色調映射</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>要解释其数值，请在上方指定配置文件。</v>
+        <v>自动（第 8.10.3 条排序）</v>
       </c>
       <c r="C533" t="str">
-        <v>若要解讀其數值，請在上方指定描述檔。</v>
+        <v>自動（第 8.10.3 條排序）</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>HDR 配置文件</v>
+        <v>增益曲线（HAGC）</v>
       </c>
       <c r="C534" t="str">
-        <v>HDR 描述檔</v>
+        <v>增益曲線（HAGC）</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>线性传递函数</v>
+        <v>预烘焙的 SDR 回退（AToB0）</v>
       </c>
       <c r="C535" t="str">
-        <v>線性傳遞函數</v>
+        <v>預先烘焙的 SDR 備援（AToB0）</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>非线性传递函数（PQ、HLG）</v>
+        <v>关闭——与修订前的 CMM 相同</v>
       </c>
       <c r="C536" t="str">
-        <v>非線性傳遞函數（PQ、HLG）</v>
+        <v>關閉——與修訂前的 CMM 相同</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>HDR 配置文件——线性传递函数</v>
+        <v>正在应用配置文件…</v>
       </c>
       <c r="C537" t="str">
-        <v>HDR 描述檔——線性傳遞函數</v>
+        <v>正在套用描述檔…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>HDR 配置文件——PQ / HLG 传递函数</v>
+        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
       </c>
       <c r="C538" t="str">
-        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
+        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
+        <v>指定配置文件需要 3 通道 RGB 图像。</v>
       </c>
       <c r="C539" t="str">
-        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
+        <v>指定描述檔需要 3 通道 RGB 影像。</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
+        <v>要解释其数值，请在上方指定配置文件。</v>
       </c>
       <c r="C540" t="str">
-        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
+        <v>若要解讀其數值，請在上方指定描述檔。</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
+        <v>HDR 配置文件</v>
       </c>
       <c r="C541" t="str">
-        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
+        <v>HDR 描述檔</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>线性传递函数</v>
       </c>
       <c r="C542" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>線性傳遞函數</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>显示余量</v>
+        <v>非线性传递函数（PQ、HLG）</v>
       </c>
       <c r="C543" t="str">
-        <v>顯示餘量</v>
+        <v>非線性傳遞函數（PQ、HLG）</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>HDR 配置文件——线性传递函数</v>
       </c>
       <c r="C544" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>HDR 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>基准</v>
+        <v>HDR 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C545" t="str">
-        <v>基準</v>
+        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>通过色彩引擎预览</v>
+        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
       </c>
       <c r="C546" t="str">
-        <v>透過色彩引擎預覽</v>
+        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>原始效果（基线 {h} 档，无增益）</v>
+        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C547" t="str">
-        <v>原始效果（基準 {h} 檔，無增益）</v>
+        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>针对 {h} 档色调映射</v>
+        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
       </c>
       <c r="C548" t="str">
-        <v>針對 {h} 檔色調對應</v>
+        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C549" t="str">
-        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>参考白</v>
+        <v>显示余量</v>
       </c>
       <c r="C550" t="str">
-        <v>參考白</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>显示器峰值</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C551" t="str">
-        <v>顯示器峰值</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>预览不可用：{why}</v>
+        <v>基准</v>
       </c>
       <c r="C552" t="str">
-        <v>無法預覽：{why}</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
+        <v>通过色彩引擎预览</v>
       </c>
       <c r="C553" t="str">
-        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
+        <v>透過色彩引擎預覽</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>所有余量下的增益</v>
+        <v>原始效果（基线 {h} 档，无增益）</v>
       </c>
       <c r="C554" t="str">
-        <v>所有餘裕下的增益</v>
+        <v>原始效果（基準 {h} 檔，無增益）</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
+        <v>针对 {h} 档色调映射</v>
       </c>
       <c r="C555" t="str">
-        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
+        <v>針對 {h} 檔色調對應</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>输入（相对 HDR 参考白的档数）</v>
+        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
       </c>
       <c r="C556" t="str">
-        <v>輸入（相對 HDR 參考白的檔數）</v>
+        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>显示余量（档）</v>
+        <v>参考白</v>
       </c>
       <c r="C557" t="str">
-        <v>顯示餘裕（檔）</v>
+        <v>參考白</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>增益（档）</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C558" t="str">
-        <v>增益（檔）</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>标签中的曲线</v>
+        <v>预览不可用：{why}</v>
       </c>
       <c r="C559" t="str">
-        <v>標籤中的曲線</v>
+        <v>無法預覽：{why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>基线</v>
+        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
       </c>
       <c r="C560" t="str">
-        <v>基準</v>
+        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>滑块</v>
+        <v>所有余量下的增益</v>
       </c>
       <c r="C561" t="str">
-        <v>滑桿</v>
+        <v>所有餘裕下的增益</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>输入 = 显示器峰值</v>
+        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
       </c>
       <c r="C562" t="str">
-        <v>輸入 = 顯示器峰值</v>
+        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>按余量的灰色色调曲线</v>
+        <v>输入（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C563" t="str">
-        <v>依餘裕的灰色色調曲線</v>
+        <v>輸入（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
+        <v>显示余量（档）</v>
       </c>
       <c r="C564" t="str">
-        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
+        <v>顯示餘裕（檔）</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>输出（相对 HDR 参考白的档数）</v>
+        <v>增益（档）</v>
       </c>
       <c r="C565" t="str">
-        <v>輸出（相對 HDR 參考白的檔數）</v>
+        <v>增益（檔）</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} 档</v>
+        <v>标签中的曲线</v>
       </c>
       <c r="C566" t="str">
-        <v>{h} 檔</v>
+        <v>標籤中的曲線</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} 档（基线）</v>
+        <v>基线</v>
       </c>
       <c r="C567" t="str">
-        <v>{h} 檔（基準）</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>{h} 档（滑块）</v>
+        <v>滑块</v>
       </c>
       <c r="C568" t="str">
-        <v>{h} 檔（滑桿）</v>
+        <v>滑桿</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>输入 = 显示器峰值</v>
       </c>
       <c r="C569" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>輸入 = 顯示器峰值</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>按余量的灰色色调曲线</v>
       </c>
       <c r="C570" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>依餘裕的灰色色調曲線</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
       </c>
       <c r="C571" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>输出（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C572" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>輸出（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>{h} 档</v>
       </c>
       <c r="C573" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>{h} 檔</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>{h} 档（基线）</v>
       </c>
       <c r="C574" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>{h} 檔（基準）</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>{h} 档（滑块）</v>
       </c>
       <c r="C575" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>{h} 檔（滑桿）</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C576" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C577" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>此余量下应用的增益</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C578" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C579" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>增益（log2 档）</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C580" t="str">
-        <v>增益（log2 檔）</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C581" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C582" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C583" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>不变</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C584" t="str">
-        <v>不變</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C585" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>{h} 档处的输出</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C586" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C587" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>识别显示器</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C588" t="str">
-        <v>識別顯示器</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C589" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C590" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>不变</v>
       </c>
       <c r="C591" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C592" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>无法识别显示器。</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C593" t="str">
-        <v>無法識別顯示器。</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>显示事件</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C594" t="str">
-        <v>顯示事件</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C595" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>色度基色</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C596" t="str">
-        <v>色度基色</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>传递特性</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C597" t="str">
-        <v>轉換特性</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>矩阵系数</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C598" t="str">
-        <v>矩陣係數</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>视频全范围标志</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C599" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>全范围</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C600" t="str">
-        <v>全範圍</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>有限范围</v>
+        <v>显示事件</v>
       </c>
       <c r="C601" t="str">
-        <v>有限範圍</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C602" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>色度基色</v>
       </c>
       <c r="C603" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>传递特性</v>
       </c>
       <c r="C604" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>报告</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C605" t="str">
-        <v>報告</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>失败</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C606" t="str">
-        <v>失敗</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>项检查</v>
+        <v>全范围</v>
       </c>
       <c r="C607" t="str">
-        <v>項檢查</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>有限范围</v>
       </c>
       <c r="C608" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C609" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C610" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C611" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>订阅</v>
+        <v>报告</v>
       </c>
       <c r="C612" t="str">
-        <v>訂閱</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>失败</v>
       </c>
       <c r="C613" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>订阅新版本通知</v>
+        <v>项检查</v>
       </c>
       <c r="C614" t="str">
-        <v>訂閱新版本通知</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>关闭</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C615" t="str">
-        <v>關閉</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C616" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>电子邮件地址</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C617" t="str">
-        <v>電子郵件地址</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>you@example.com</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C618" t="str">
-        <v>you@example.com</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>订阅</v>
       </c>
       <c r="C619" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>（选填）</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C620" t="str">
-        <v>（選填）</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C621" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>关闭</v>
       </c>
       <c r="C622" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>取消</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C623" t="str">
-        <v>取消</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>订阅</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C624" t="str">
-        <v>訂閱</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C625" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C626" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>关闭</v>
+        <v>（选填）</v>
       </c>
       <c r="C627" t="str">
-        <v>關閉</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>隐私声明</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C628" t="str">
-        <v>隱私聲明</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C629" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>取消</v>
       </c>
       <c r="C630" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>请检查表单后重试。</v>
+        <v>订阅</v>
       </c>
       <c r="C631" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C632" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>网络错误，请重试。</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C633" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>错误：</v>
+        <v>关闭</v>
       </c>
       <c r="C634" t="str">
-        <v>錯誤：</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>转换为 XML</v>
+        <v>隐私声明</v>
       </c>
       <c r="C635" t="str">
-        <v>轉換為 XML</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>转换为 JSON</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C636" t="str">
-        <v>轉換為 JSON</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>转换为 ICC</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C637" t="str">
-        <v>轉換為 ICC</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>正在转换为 XML…</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C638" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C639" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C640" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>错误：</v>
       </c>
       <c r="C641" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C642" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>配置文件 ID</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C643" t="str">
-        <v>設定檔 ID</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>未找到标签。</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C644" t="str">
-        <v>找不到標籤。</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>标签名称</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C645" t="str">
-        <v>標籤名稱</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C646" t="str">
-        <v>ID</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>偏移</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C647" t="str">
-        <v>偏移</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>大小</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C648" t="str">
-        <v>大小</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>填充</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C649" t="str">
-        <v>填充</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>加载后字节已更改</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C650" t="str">
-        <v>載入後位元組已變更</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>类型</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C651" t="str">
-        <v>類型</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>{type} 数组</v>
+        <v>标签名称</v>
       </c>
       <c r="C652" t="str">
-        <v>{type} 陣列</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>（无内容）</v>
+        <v>ID</v>
       </c>
       <c r="C653" t="str">
-        <v>（無內容）</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>字节</v>
+        <v>偏移</v>
       </c>
       <c r="C654" t="str">
-        <v>位元組</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>正在加载完整描述…</v>
+        <v>大小</v>
       </c>
       <c r="C655" t="str">
-        <v>正在載入完整描述…</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>无法加载完整描述：</v>
+        <v>填充</v>
       </c>
       <c r="C656" t="str">
-        <v>無法載入完整描述：</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C657" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>类型</v>
       </c>
       <c r="C658" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>无验证输出</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C659" t="str">
-        <v>無驗證輸出</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>配置文件有效</v>
+        <v>（无内容）</v>
       </c>
       <c r="C660" t="str">
-        <v>設定檔有效</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>配置文件有警告</v>
+        <v>字节</v>
       </c>
       <c r="C661" t="str">
-        <v>設定檔有警告</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>配置文件不合规</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C662" t="str">
-        <v>設定檔不符合規範</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>严重验证错误</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C663" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>未知验证状态</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C664" t="str">
-        <v>未知驗證狀態</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C665" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>未发现警告或错误。</v>
+        <v>无验证输出</v>
       </c>
       <c r="C666" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>有效</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C667" t="str">
-        <v>有效</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>警告</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C668" t="str">
-        <v>警告</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C669" t="str">
-        <v>錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>未知</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C670" t="str">
-        <v>未知</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>通过</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C671" t="str">
-        <v>通過</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>失败</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C672" t="str">
-        <v>失敗</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>在上下文中查看</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C673" t="str">
-        <v>在上下文中檢視</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>验证详情</v>
+        <v>有效</v>
       </c>
       <c r="C674" t="str">
-        <v>驗證詳情</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>触发字段</v>
+        <v>警告</v>
       </c>
       <c r="C675" t="str">
-        <v>觸發欄位</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>字段</v>
+        <v>错误</v>
       </c>
       <c r="C676" t="str">
-        <v>欄位</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>当前值</v>
+        <v>未知</v>
       </c>
       <c r="C677" t="str">
-        <v>目前值</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>要求：0</v>
+        <v>通过</v>
       </c>
       <c r="C678" t="str">
-        <v>要求：0</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>预期：{value}</v>
+        <v>失败</v>
       </c>
       <c r="C679" t="str">
-        <v>預期：{value}</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>无效</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C680" t="str">
-        <v>無效</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>验证详情</v>
       </c>
       <c r="C681" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>关闭</v>
+        <v>触发字段</v>
       </c>
       <c r="C682" t="str">
-        <v>關閉</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>字段</v>
       </c>
       <c r="C683" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>当前值</v>
       </c>
       <c r="C684" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>要求：0</v>
       </c>
       <c r="C685" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C686" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>无效</v>
       </c>
       <c r="C687" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C688" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>关闭</v>
       </c>
       <c r="C689" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C690" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>缩进</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C691" t="str">
-        <v>縮排</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>排序键</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C692" t="str">
-        <v>排序鍵</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C693" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C694" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C695" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C696" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C697" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C698" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C699" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C693" t="str">
+      <c r="C700" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C700"/>
+  <dimension ref="A1:C705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5519,2603 +5519,2658 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>正在解码…</v>
+        <v>此文件为 {size} MB；HDR 标签页最多打开 {max} MB 的图像。</v>
       </c>
       <c r="C465" t="str">
-        <v>正在解碼…</v>
+        <v>此檔案為 {size} MB；HDR 分頁最多開啟 {max} MB 的影像。</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>动态范围</v>
+        <v>无法应用配置文件：</v>
       </c>
       <c r="C466" t="str">
-        <v>動態範圍</v>
+        <v>無法套用描述檔：</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>此浏览器只提供两个端点，不支持混合。</v>
+        <v>无法绘制图像：</v>
       </c>
       <c r="C467" t="str">
-        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
+        <v>無法繪製影像：</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>由 profiletool 自行解码，因此与浏览器无关</v>
+        <v>（这些原色无法构成色彩空间——已忽略，使用 Rec. 709）</v>
       </c>
       <c r="C468" t="str">
-        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
+        <v>（這些原色無法構成色彩空間——已忽略，使用 Rec. 709）</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>此浏览器可以解码</v>
+        <v>JPEG XL 的配置文件压缩在码流内部，profiletool 目前尚不能解压</v>
       </c>
       <c r="C469" t="str">
-        <v>此瀏覽器可以解碼</v>
+        <v>JPEG XL 的描述檔壓縮在碼流內部，profiletool 目前尚無法解壓縮</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>此浏览器无法解码</v>
+        <v>正在解码…</v>
       </c>
       <c r="C470" t="str">
-        <v>此瀏覽器無法解碼</v>
+        <v>正在解碼…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
+        <v>动态范围</v>
       </c>
       <c r="C471" t="str">
-        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
+        <v>動態範圍</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
+        <v>此浏览器只提供两个端点，不支持混合。</v>
       </c>
       <c r="C472" t="str">
-        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
+        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>推迟到后续版本</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C473" t="str">
-        <v>延後至後續版本</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
+        <v>此浏览器可以解码</v>
       </c>
       <c r="C474" t="str">
-        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
+        <v>此瀏覽器可以解碼</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
+        <v>此浏览器无法解码</v>
       </c>
       <c r="C475" t="str">
-        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
+        <v>此瀏覽器無法解碼</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
+        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
       </c>
       <c r="C476" t="str">
-        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
+        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>查看只需解析容器，不需要编解码器</v>
+        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
       </c>
       <c r="C477" t="str">
-        <v>檢視只需解析容器，不需要編解碼器</v>
+        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>HDR 显示器和 HDR 画布路径均可用</v>
+        <v>推迟到后续版本</v>
       </c>
       <c r="C478" t="str">
-        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
+        <v>延後至後續版本</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>未知格式</v>
+        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
       </c>
       <c r="C479" t="str">
-        <v>未知格式</v>
+        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{os} 上的 {browser}</v>
+        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
       </c>
       <c r="C480" t="str">
-        <v>{os} 上的 {browser}</v>
+        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · 检测到 HDR 显示器</v>
+        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
       </c>
       <c r="C481" t="str">
-        <v>{name} · 偵測到 HDR 顯示器</v>
+        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · SDR 显示器</v>
+        <v>查看只需解析容器，不需要编解码器</v>
       </c>
       <c r="C482" t="str">
-        <v>{name} · SDR 顯示器</v>
+        <v>檢視只需解析容器，不需要編解碼器</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
+        <v>HDR 显示器和 HDR 画布路径均可用</v>
       </c>
       <c r="C483" t="str">
-        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
+        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
+        <v>未知格式</v>
       </c>
       <c r="C484" t="str">
-        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
+        <v>未知格式</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>显示器峰值</v>
+        <v>{os} 上的 {browser}</v>
       </c>
       <c r="C485" t="str">
-        <v>顯示器峰值</v>
+        <v>{os} 上的 {browser}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>SDR 白的 {r} 倍（{n} 档）</v>
+        <v>{name} · 检测到 HDR 显示器</v>
       </c>
       <c r="C486" t="str">
-        <v>SDR 白的 {r} 倍（{n} 檔）</v>
+        <v>{name} · 偵測到 HDR 顯示器</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× —— SDR 显示器</v>
+        <v>{name} · SDR 显示器</v>
       </c>
       <c r="C487" t="str">
-        <v>1× —— SDR 顯示器</v>
+        <v>{name} · SDR 顯示器</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>未知</v>
+        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
       </c>
       <c r="C488" t="str">
-        <v>未知</v>
+        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
+        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
       </c>
       <c r="C489" t="str">
-        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
+        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C490" t="str">
-        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
+        <v>SDR 白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C491" t="str">
-        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
+        <v>SDR 白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>适配显示器</v>
+        <v>1× —— SDR 显示器</v>
       </c>
       <c r="C492" t="str">
-        <v>符合顯示器</v>
+        <v>1× —— SDR 顯示器</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>图像详情</v>
+        <v>未知</v>
       </c>
       <c r="C493" t="str">
-        <v>影像詳細資訊</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>不可用——此图像由浏览器渲染，无法将其限制在指定峰值</v>
+        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
       </c>
       <c r="C494" t="str">
-        <v>無法使用——此影像由瀏覽器算繪，無法將其限制在指定峰值</v>
+        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>不可用——此输出无法显示高于 SDR 白的内容</v>
+        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
       </c>
       <c r="C495" t="str">
-        <v>無法使用——此輸出無法顯示高於 SDR 白的內容</v>
+        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>不可用——此显示器的峰值未知</v>
+        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
       </c>
       <c r="C496" t="str">
-        <v>無法使用——此顯示器的峰值未知</v>
+        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>放大</v>
+        <v>适配显示器</v>
       </c>
       <c r="C497" t="str">
-        <v>放大</v>
+        <v>符合顯示器</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>缩小</v>
+        <v>图像详情</v>
       </c>
       <c r="C498" t="str">
-        <v>縮小</v>
+        <v>影像詳細資訊</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>适合图像</v>
+        <v>不可用——此图像由浏览器渲染，无法将其限制在指定峰值</v>
       </c>
       <c r="C499" t="str">
-        <v>符合影像</v>
+        <v>無法使用——此影像由瀏覽器算繪，無法將其限制在指定峰值</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>实际像素（1:1）</v>
+        <v>不可用——此输出无法显示高于 SDR 白的内容</v>
       </c>
       <c r="C500" t="str">
-        <v>實際像素（1:1）</v>
+        <v>無法使用——此輸出無法顯示高於 SDR 白的內容</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>拖动平移 · Ctrl+滚轮缩放 · 双击复位</v>
+        <v>不可用——此显示器的峰值未知</v>
       </c>
       <c r="C501" t="str">
-        <v>拖曳平移 · Ctrl+滾輪縮放 · 按兩下復位</v>
+        <v>無法使用——此顯示器的峰值未知</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>拖动以调整图像区域大小；双击恢复默认大小</v>
+        <v>放大</v>
       </c>
       <c r="C502" t="str">
-        <v>拖曳以調整影像區域大小；按兩下還原預設大小</v>
+        <v>放大</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>图像视图</v>
+        <v>缩小</v>
       </c>
       <c r="C503" t="str">
-        <v>影像檢視</v>
+        <v>縮小</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
+        <v>适合图像</v>
       </c>
       <c r="C504" t="str">
-        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
+        <v>符合影像</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>无上限</v>
+        <v>实际像素（1:1）</v>
       </c>
       <c r="C505" t="str">
-        <v>無上限</v>
+        <v>實際像素（1:1）</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>上限 {n} 档（{r}×）</v>
+        <v>拖动平移 · Ctrl+滚轮缩放 · 双击复位</v>
       </c>
       <c r="C506" t="str">
-        <v>上限 {n} 檔（{r}×）</v>
+        <v>拖曳平移 · Ctrl+滾輪縮放 · 按兩下復位</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>SDR 白</v>
+        <v>拖动以调整图像区域大小；双击恢复默认大小</v>
       </c>
       <c r="C507" t="str">
-        <v>SDR 白</v>
+        <v>拖曳以調整影像區域大小；按兩下還原預設大小</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
+        <v>图像视图</v>
       </c>
       <c r="C508" t="str">
-        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
+        <v>影像檢視</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>SDR 白色色块</v>
+        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
       </c>
       <c r="C509" t="str">
-        <v>SDR 白色色塊</v>
+        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>拖动即可移动；双击可将其放回图像旁边。</v>
+        <v>无上限</v>
       </c>
       <c r="C510" t="str">
-        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
+        <v>無上限</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>指定配置文件</v>
+        <v>上限 {n} 档（{r}×）</v>
       </c>
       <c r="C511" t="str">
-        <v>指定描述檔</v>
+        <v>上限 {n} 檔（{r}×）</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>无——按文件自身标示</v>
+        <v>SDR 白</v>
       </c>
       <c r="C512" t="str">
-        <v>無——依檔案本身標示</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>嵌入的配置文件（{n} B）</v>
+        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
       </c>
       <c r="C513" t="str">
-        <v>嵌入的描述檔（{n} B）</v>
+        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>池中的 HDR 配置文件</v>
+        <v>SDR 白色色块</v>
       </c>
       <c r="C514" t="str">
-        <v>池中的 HDR 描述檔</v>
+        <v>SDR 白色色塊</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>配置文件</v>
+        <v>拖动即可移动；双击可将其放回图像旁边。</v>
       </c>
       <c r="C515" t="str">
-        <v>描述檔</v>
+        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>嵌入的配置文件</v>
+        <v>指定配置文件</v>
       </c>
       <c r="C516" t="str">
-        <v>嵌入的描述檔</v>
+        <v>指定描述檔</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>色彩引擎路径</v>
+        <v>无——按文件自身标示</v>
       </c>
       <c r="C517" t="str">
-        <v>色彩引擎路徑</v>
+        <v>無——依檔案本身標示</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>HDR 路径，已应用增益曲线</v>
+        <v>嵌入的配置文件（{n} B）</v>
       </c>
       <c r="C518" t="str">
-        <v>HDR 路徑，已套用增益曲線</v>
+        <v>嵌入的描述檔（{n} B）</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR 路径，无增益曲线</v>
+        <v>池中的 HDR 配置文件</v>
       </c>
       <c r="C519" t="str">
-        <v>HDR 路徑，無增益曲線</v>
+        <v>池中的 HDR 描述檔</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>预烘焙的 AToB0——不是 HDR 路径</v>
+        <v>配置文件</v>
       </c>
       <c r="C520" t="str">
-        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
+        <v>描述檔</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>传递函数</v>
+        <v>嵌入的配置文件</v>
       </c>
       <c r="C521" t="str">
-        <v>傳遞函數</v>
+        <v>嵌入的描述檔</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>HDR 参考白</v>
+        <v>色彩引擎路径</v>
       </c>
       <c r="C522" t="str">
-        <v>HDR 參考白</v>
+        <v>色彩引擎路徑</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>线性值</v>
+        <v>HDR 路径，已应用增益曲线</v>
       </c>
       <c r="C523" t="str">
-        <v>線性值</v>
+        <v>HDR 路徑，已套用增益曲線</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>文件 1.0 = HDR 参考白</v>
+        <v>HDR 路径，无增益曲线</v>
       </c>
       <c r="C524" t="str">
-        <v>檔案 1.0 = HDR 參考白</v>
+        <v>HDR 路徑，無增益曲線</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 条）</v>
+        <v>预烘焙的 AToB0——不是 HDR 路径</v>
       </c>
       <c r="C525" t="str">
-        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 條）</v>
+        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>OpenEXR 和 Radiance HDR 文件按惯例将 SDR 白置于 1.0，而 ICC 线性传递函数把 1.0 读作 1 cd/m²。默认会缩放文件，使其 1.0 落在配置文件的 HDR 参考白上。</v>
+        <v>传递函数</v>
       </c>
       <c r="C526" t="str">
-        <v>OpenEXR 與 Radiance HDR 檔案依慣例將 SDR 白置於 1.0，而 ICC 線性傳遞函數將 1.0 讀作 1 cd/m²。預設會縮放檔案，使其 1.0 落在描述檔的 HDR 參考白上。</v>
+        <v>傳遞函數</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>输入缩放</v>
+        <v>HDR 参考白</v>
       </c>
       <c r="C527" t="str">
-        <v>輸入縮放</v>
+        <v>HDR 參考白</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — 文件 1.0 = 参考白</v>
+        <v>线性值</v>
       </c>
       <c r="C528" t="str">
-        <v>×{w} — 檔案 1.0 = 參考白</v>
+        <v>線性值</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>无 — 文件 1.0 = 1 cd/m²</v>
+        <v>文件 1.0 = HDR 参考白</v>
       </c>
       <c r="C529" t="str">
-        <v>無 — 檔案 1.0 = 1 cd/m²</v>
+        <v>檔案 1.0 = HDR 參考白</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>目标余量</v>
+        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 条）</v>
       </c>
       <c r="C530" t="str">
-        <v>目標餘量</v>
+        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 條）</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>参考白的 {r} 倍（{n} 档）</v>
+        <v>OpenEXR 和 Radiance HDR 文件按惯例将 SDR 白置于 1.0，而 ICC 线性传递函数把 1.0 读作 1 cd/m²。默认会缩放文件，使其 1.0 落在配置文件的 HDR 参考白上。</v>
       </c>
       <c r="C531" t="str">
-        <v>參考白的 {r} 倍（{n} 檔）</v>
+        <v>OpenEXR 與 Radiance HDR 檔案依慣例將 SDR 白置於 1.0，而 ICC 線性傳遞函數將 1.0 讀作 1 cd/m²。預設會縮放檔案，使其 1.0 落在描述檔的 HDR 參考白上。</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>色调映射</v>
+        <v>输入缩放</v>
       </c>
       <c r="C532" t="str">
-        <v>色調映射</v>
+        <v>輸入縮放</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>自动（第 8.10.3 条排序）</v>
+        <v>×{w} — 文件 1.0 = 参考白</v>
       </c>
       <c r="C533" t="str">
-        <v>自動（第 8.10.3 條排序）</v>
+        <v>×{w} — 檔案 1.0 = 參考白</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>增益曲线（HAGC）</v>
+        <v>无 — 文件 1.0 = 1 cd/m²</v>
       </c>
       <c r="C534" t="str">
-        <v>增益曲線（HAGC）</v>
+        <v>無 — 檔案 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>预烘焙的 SDR 回退（AToB0）</v>
+        <v>目标余量</v>
       </c>
       <c r="C535" t="str">
-        <v>預先烘焙的 SDR 備援（AToB0）</v>
+        <v>目標餘量</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>关闭——与修订前的 CMM 相同</v>
+        <v>参考白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C536" t="str">
-        <v>關閉——與修訂前的 CMM 相同</v>
+        <v>參考白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>正在应用配置文件…</v>
+        <v>色调映射</v>
       </c>
       <c r="C537" t="str">
-        <v>正在套用描述檔…</v>
+        <v>色調映射</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
+        <v>自动（第 8.10.3 条排序）</v>
       </c>
       <c r="C538" t="str">
-        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
+        <v>自動（第 8.10.3 條排序）</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>指定配置文件需要 3 通道 RGB 图像。</v>
+        <v>增益曲线（HAGC）</v>
       </c>
       <c r="C539" t="str">
-        <v>指定描述檔需要 3 通道 RGB 影像。</v>
+        <v>增益曲線（HAGC）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>要解释其数值，请在上方指定配置文件。</v>
+        <v>预烘焙的 SDR 回退（AToB0）</v>
       </c>
       <c r="C540" t="str">
-        <v>若要解讀其數值，請在上方指定描述檔。</v>
+        <v>預先烘焙的 SDR 備援（AToB0）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>HDR 配置文件</v>
+        <v>关闭——与修订前的 CMM 相同</v>
       </c>
       <c r="C541" t="str">
-        <v>HDR 描述檔</v>
+        <v>關閉——與修訂前的 CMM 相同</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>线性传递函数</v>
+        <v>正在应用配置文件…</v>
       </c>
       <c r="C542" t="str">
-        <v>線性傳遞函數</v>
+        <v>正在套用描述檔…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>非线性传递函数（PQ、HLG）</v>
+        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
       </c>
       <c r="C543" t="str">
-        <v>非線性傳遞函數（PQ、HLG）</v>
+        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR 配置文件——线性传递函数</v>
+        <v>指定配置文件需要 3 通道 RGB 图像。</v>
       </c>
       <c r="C544" t="str">
-        <v>HDR 描述檔——線性傳遞函數</v>
+        <v>指定描述檔需要 3 通道 RGB 影像。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>HDR 配置文件——PQ / HLG 传递函数</v>
+        <v>要解释其数值，请在上方指定配置文件。</v>
       </c>
       <c r="C545" t="str">
-        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
+        <v>若要解讀其數值，請在上方指定描述檔。</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
+        <v>HDR 配置文件</v>
       </c>
       <c r="C546" t="str">
-        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
+        <v>HDR 描述檔</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
+        <v>线性传递函数</v>
       </c>
       <c r="C547" t="str">
-        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
+        <v>線性傳遞函數</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
+        <v>非线性传递函数（PQ、HLG）</v>
       </c>
       <c r="C548" t="str">
-        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
+        <v>非線性傳遞函數（PQ、HLG）</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>HDR 配置文件——线性传递函数</v>
       </c>
       <c r="C549" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>HDR 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>显示余量</v>
+        <v>HDR 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C550" t="str">
-        <v>顯示餘量</v>
+        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
       </c>
       <c r="C551" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>基准</v>
+        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C552" t="str">
-        <v>基準</v>
+        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>通过色彩引擎预览</v>
+        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
       </c>
       <c r="C553" t="str">
-        <v>透過色彩引擎預覽</v>
+        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>原始效果（基线 {h} 档，无增益）</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C554" t="str">
-        <v>原始效果（基準 {h} 檔，無增益）</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>针对 {h} 档色调映射</v>
+        <v>显示余量</v>
       </c>
       <c r="C555" t="str">
-        <v>針對 {h} 檔色調對應</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C556" t="str">
-        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>参考白</v>
+        <v>基准</v>
       </c>
       <c r="C557" t="str">
-        <v>參考白</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>显示器峰值</v>
+        <v>通过色彩引擎预览</v>
       </c>
       <c r="C558" t="str">
-        <v>顯示器峰值</v>
+        <v>透過色彩引擎預覽</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>预览不可用：{why}</v>
+        <v>原始效果（基线 {h} 档，无增益）</v>
       </c>
       <c r="C559" t="str">
-        <v>無法預覽：{why}</v>
+        <v>原始效果（基準 {h} 檔，無增益）</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
+        <v>针对 {h} 档色调映射</v>
       </c>
       <c r="C560" t="str">
-        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
+        <v>針對 {h} 檔色調對應</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>所有余量下的增益</v>
+        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
       </c>
       <c r="C561" t="str">
-        <v>所有餘裕下的增益</v>
+        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
+        <v>参考白</v>
       </c>
       <c r="C562" t="str">
-        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
+        <v>參考白</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>输入（相对 HDR 参考白的档数）</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C563" t="str">
-        <v>輸入（相對 HDR 參考白的檔數）</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>显示余量（档）</v>
+        <v>预览不可用：{why}</v>
       </c>
       <c r="C564" t="str">
-        <v>顯示餘裕（檔）</v>
+        <v>無法預覽：{why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>增益（档）</v>
+        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
       </c>
       <c r="C565" t="str">
-        <v>增益（檔）</v>
+        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>标签中的曲线</v>
+        <v>所有余量下的增益</v>
       </c>
       <c r="C566" t="str">
-        <v>標籤中的曲線</v>
+        <v>所有餘裕下的增益</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>基线</v>
+        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
       </c>
       <c r="C567" t="str">
-        <v>基準</v>
+        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>滑块</v>
+        <v>输入（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C568" t="str">
-        <v>滑桿</v>
+        <v>輸入（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>输入 = 显示器峰值</v>
+        <v>显示余量（档）</v>
       </c>
       <c r="C569" t="str">
-        <v>輸入 = 顯示器峰值</v>
+        <v>顯示餘裕（檔）</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>按余量的灰色色调曲线</v>
+        <v>增益（档）</v>
       </c>
       <c r="C570" t="str">
-        <v>依餘裕的灰色色調曲線</v>
+        <v>增益（檔）</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
+        <v>标签中的曲线</v>
       </c>
       <c r="C571" t="str">
-        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
+        <v>標籤中的曲線</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>输出（相对 HDR 参考白的档数）</v>
+        <v>基线</v>
       </c>
       <c r="C572" t="str">
-        <v>輸出（相對 HDR 參考白的檔數）</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} 档</v>
+        <v>滑块</v>
       </c>
       <c r="C573" t="str">
-        <v>{h} 檔</v>
+        <v>滑桿</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} 档（基线）</v>
+        <v>输入 = 显示器峰值</v>
       </c>
       <c r="C574" t="str">
-        <v>{h} 檔（基準）</v>
+        <v>輸入 = 顯示器峰值</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>{h} 档（滑块）</v>
+        <v>按余量的灰色色调曲线</v>
       </c>
       <c r="C575" t="str">
-        <v>{h} 檔（滑桿）</v>
+        <v>依餘裕的灰色色調曲線</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
       </c>
       <c r="C576" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>输出（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C577" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>輸出（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>{h} 档</v>
       </c>
       <c r="C578" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>{h} 檔</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>{h} 档（基线）</v>
       </c>
       <c r="C579" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>{h} 檔（基準）</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>{h} 档（滑块）</v>
       </c>
       <c r="C580" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>{h} 檔（滑桿）</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C581" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C582" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C583" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C584" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>此余量下应用的增益</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C585" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C586" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>增益（log2 档）</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C587" t="str">
-        <v>增益（log2 檔）</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C588" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C589" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C590" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>不变</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C591" t="str">
-        <v>不變</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C592" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>{h} 档处的输出</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C593" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C594" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>识别显示器</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C595" t="str">
-        <v>識別顯示器</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>不变</v>
       </c>
       <c r="C596" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C597" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C598" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C599" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>无法识别显示器。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C600" t="str">
-        <v>無法識別顯示器。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>显示事件</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C601" t="str">
-        <v>顯示事件</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C602" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>色度基色</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C603" t="str">
-        <v>色度基色</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>传递特性</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C604" t="str">
-        <v>轉換特性</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>矩阵系数</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C605" t="str">
-        <v>矩陣係數</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>视频全范围标志</v>
+        <v>显示事件</v>
       </c>
       <c r="C606" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>全范围</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C607" t="str">
-        <v>全範圍</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>有限范围</v>
+        <v>色度基色</v>
       </c>
       <c r="C608" t="str">
-        <v>有限範圍</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>传递特性</v>
       </c>
       <c r="C609" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C610" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C611" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>报告</v>
+        <v>全范围</v>
       </c>
       <c r="C612" t="str">
-        <v>報告</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>失败</v>
+        <v>有限范围</v>
       </c>
       <c r="C613" t="str">
-        <v>失敗</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>项检查</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C614" t="str">
-        <v>項檢查</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C615" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C616" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>报告</v>
       </c>
       <c r="C617" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>失败</v>
       </c>
       <c r="C618" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>订阅</v>
+        <v>项检查</v>
       </c>
       <c r="C619" t="str">
-        <v>訂閱</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C620" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>订阅新版本通知</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C621" t="str">
-        <v>訂閱新版本通知</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>关闭</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C622" t="str">
-        <v>關閉</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C623" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>电子邮件地址</v>
+        <v>订阅</v>
       </c>
       <c r="C624" t="str">
-        <v>電子郵件地址</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>you@example.com</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C625" t="str">
-        <v>you@example.com</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C626" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>（选填）</v>
+        <v>关闭</v>
       </c>
       <c r="C627" t="str">
-        <v>（選填）</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C628" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C629" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>取消</v>
+        <v>you@example.com</v>
       </c>
       <c r="C630" t="str">
-        <v>取消</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>订阅</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C631" t="str">
-        <v>訂閱</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>（选填）</v>
       </c>
       <c r="C632" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C633" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>关闭</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C634" t="str">
-        <v>關閉</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>隐私声明</v>
+        <v>取消</v>
       </c>
       <c r="C635" t="str">
-        <v>隱私聲明</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>订阅</v>
       </c>
       <c r="C636" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C637" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>请检查表单后重试。</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C638" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>关闭</v>
       </c>
       <c r="C639" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>网络错误，请重试。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C640" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>错误：</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C641" t="str">
-        <v>錯誤：</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>转换为 XML</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C642" t="str">
-        <v>轉換為 XML</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>转换为 JSON</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C643" t="str">
-        <v>轉換為 JSON</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>转换为 ICC</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C644" t="str">
-        <v>轉換為 ICC</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>正在转换为 XML…</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C645" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>错误：</v>
       </c>
       <c r="C646" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C647" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C648" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C649" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>配置文件 ID</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C650" t="str">
-        <v>設定檔 ID</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>未找到标签。</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C651" t="str">
-        <v>找不到標籤。</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>标签名称</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C652" t="str">
-        <v>標籤名稱</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C653" t="str">
-        <v>ID</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>偏移</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C654" t="str">
-        <v>偏移</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>大小</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C655" t="str">
-        <v>大小</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>填充</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C656" t="str">
-        <v>填充</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>加载后字节已更改</v>
+        <v>标签名称</v>
       </c>
       <c r="C657" t="str">
-        <v>載入後位元組已變更</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>类型</v>
+        <v>ID</v>
       </c>
       <c r="C658" t="str">
-        <v>類型</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>{type} 数组</v>
+        <v>偏移</v>
       </c>
       <c r="C659" t="str">
-        <v>{type} 陣列</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>（无内容）</v>
+        <v>大小</v>
       </c>
       <c r="C660" t="str">
-        <v>（無內容）</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>字节</v>
+        <v>填充</v>
       </c>
       <c r="C661" t="str">
-        <v>位元組</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>正在加载完整描述…</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C662" t="str">
-        <v>正在載入完整描述…</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>无法加载完整描述：</v>
+        <v>类型</v>
       </c>
       <c r="C663" t="str">
-        <v>無法載入完整描述：</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C664" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>（无内容）</v>
       </c>
       <c r="C665" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>无验证输出</v>
+        <v>字节</v>
       </c>
       <c r="C666" t="str">
-        <v>無驗證輸出</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>配置文件有效</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C667" t="str">
-        <v>設定檔有效</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>配置文件有警告</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C668" t="str">
-        <v>設定檔有警告</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>配置文件不合规</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C669" t="str">
-        <v>設定檔不符合規範</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>严重验证错误</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C670" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>未知验证状态</v>
+        <v>无验证输出</v>
       </c>
       <c r="C671" t="str">
-        <v>未知驗證狀態</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C672" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>未发现警告或错误。</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C673" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>有效</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C674" t="str">
-        <v>有效</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>警告</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C675" t="str">
-        <v>警告</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>错误</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C676" t="str">
-        <v>錯誤</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>未知</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C677" t="str">
-        <v>未知</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>通过</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C678" t="str">
-        <v>通過</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>失败</v>
+        <v>有效</v>
       </c>
       <c r="C679" t="str">
-        <v>失敗</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>在上下文中查看</v>
+        <v>警告</v>
       </c>
       <c r="C680" t="str">
-        <v>在上下文中檢視</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>验证详情</v>
+        <v>错误</v>
       </c>
       <c r="C681" t="str">
-        <v>驗證詳情</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>触发字段</v>
+        <v>未知</v>
       </c>
       <c r="C682" t="str">
-        <v>觸發欄位</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>字段</v>
+        <v>通过</v>
       </c>
       <c r="C683" t="str">
-        <v>欄位</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>当前值</v>
+        <v>失败</v>
       </c>
       <c r="C684" t="str">
-        <v>目前值</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>要求：0</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C685" t="str">
-        <v>要求：0</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>预期：{value}</v>
+        <v>验证详情</v>
       </c>
       <c r="C686" t="str">
-        <v>預期：{value}</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>无效</v>
+        <v>触发字段</v>
       </c>
       <c r="C687" t="str">
-        <v>無效</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>字段</v>
       </c>
       <c r="C688" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>关闭</v>
+        <v>当前值</v>
       </c>
       <c r="C689" t="str">
-        <v>關閉</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>要求：0</v>
       </c>
       <c r="C690" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C691" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无效</v>
       </c>
       <c r="C692" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C693" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>关闭</v>
       </c>
       <c r="C694" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C695" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C696" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C697" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>缩进</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C698" t="str">
-        <v>縮排</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>排序键</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C699" t="str">
-        <v>排序鍵</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C700" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C701" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C702" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C703" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C704" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C700" t="str">
+      <c r="C705" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -5112,13 +5112,13 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC 和 JPEG XL。</v>
       </c>
       <c r="C428" t="str">
-        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC。</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC 和 JPEG XL。</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -1528,13 +1528,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并打开；点击“保存 ICC 配置文件”后才会下载。</v>
       </c>
       <c r="C103" t="str">
-        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並開啟；按下「儲存 ICC 設定檔」後才會下載。</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C705"/>
+  <dimension ref="A1:C706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1495,6682 +1495,6693 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>按名称排序</v>
+        <v>点按选择，然后点按标签页发送。</v>
       </c>
       <c r="C100" t="str">
-        <v>依名稱排序</v>
+        <v>點選以選取，然後點選分頁以傳送。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>按名称排序</v>
       </c>
       <c r="C101" t="str">
-        <v>A–Z</v>
+        <v>依名稱排序</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>从 .cube 新建配置文件</v>
+        <v>A–Z</v>
       </c>
       <c r="C102" t="str">
-        <v>從 .cube 新建設定檔</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并打开；点击“保存 ICC 配置文件”后才会下载。</v>
+        <v>从 .cube 新建配置文件</v>
       </c>
       <c r="C103" t="str">
-        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並開啟；按下「儲存 ICC 設定檔」後才會下載。</v>
+        <v>從 .cube 新建設定檔</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>选择 .cube 文件</v>
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并打开；点击“保存 ICC 配置文件”后才会下载。</v>
       </c>
       <c r="C104" t="str">
-        <v>選擇 .cube 檔案</v>
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並開啟；按下「儲存 ICC 設定檔」後才會下載。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>选择 .cube 文件</v>
+      </c>
+      <c r="C105" t="str">
+        <v>選擇 .cube 檔案</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>或拖放到此处，或在下方粘贴</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C106" t="str">
         <v>或拖放到此處，或在下方貼上</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C106" t="str" xml:space="preserve">
+      <c r="C107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>取消</v>
-      </c>
-      <c r="C107" t="str">
-        <v>取消</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>创建 DeviceLink</v>
+        <v>取消</v>
       </c>
       <c r="C108" t="str">
-        <v>建立 DeviceLink</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>正在创建…</v>
+        <v>创建 DeviceLink</v>
       </c>
       <c r="C109" t="str">
-        <v>正在建立…</v>
+        <v>建立 DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>无法读取该文件。</v>
+        <v>正在创建…</v>
       </c>
       <c r="C110" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>配置文件</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C111" t="str">
-        <v>設定檔</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>比较</v>
+        <v>配置文件</v>
       </c>
       <c r="C112" t="str">
-        <v>比較</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>链接</v>
+        <v>比较</v>
       </c>
       <c r="C113" t="str">
-        <v>連結</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>光谱</v>
+        <v>链接</v>
       </c>
       <c r="C114" t="str">
-        <v>光譜</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>将配置文件从池中拖到此选项卡</v>
+        <v>光谱</v>
       </c>
       <c r="C115" t="str">
-        <v>將設定檔從集區拖到此分頁</v>
+        <v>光譜</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>移除</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C116" t="str">
-        <v>移除</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>未选择配置文件</v>
+        <v>移除</v>
       </c>
       <c r="C117" t="str">
-        <v>未選擇設定檔</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C118" t="str">
-        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>暂无可比较的内容</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C119" t="str">
-        <v>尚無可比較的內容</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C120" t="str">
-        <v>將一個或多個設定檔拖到「比較」分頁。</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>色域比较</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C121" t="str">
-        <v>色域比較</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
+        <v>色域比较</v>
       </c>
       <c r="C122" t="str">
-        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>渲染意图</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C123" t="str">
-        <v>轉換意圖</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>外壳</v>
+        <v>渲染意图</v>
       </c>
       <c r="C124" t="str">
-        <v>外殼</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>线框</v>
+        <v>外壳</v>
       </c>
       <c r="C125" t="str">
-        <v>線框</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>轴编号</v>
+        <v>线框</v>
       </c>
       <c r="C126" t="str">
-        <v>軸編號</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>不透明度</v>
+        <v>轴编号</v>
       </c>
       <c r="C127" t="str">
-        <v>不透明度</v>
+        <v>軸編號</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>颜色</v>
+        <v>不透明度</v>
       </c>
       <c r="C128" t="str">
-        <v>色彩</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>纯色</v>
+        <v>颜色</v>
       </c>
       <c r="C129" t="str">
-        <v>純色</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>按数值</v>
+        <v>纯色</v>
       </c>
       <c r="C130" t="str">
-        <v>依數值</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>按色相</v>
+        <v>按数值</v>
       </c>
       <c r="C131" t="str">
-        <v>依色相</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>旋转</v>
+        <v>按色相</v>
       </c>
       <c r="C132" t="str">
-        <v>旋轉</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>转盘</v>
+        <v>旋转</v>
       </c>
       <c r="C133" t="str">
-        <v>轉盤</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>轨道</v>
+        <v>转盘</v>
       </c>
       <c r="C134" t="str">
-        <v>軌道</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>拖动速度</v>
+        <v>轨道</v>
       </c>
       <c r="C135" t="str">
-        <v>拖曳速度</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>翻滚</v>
+        <v>拖动速度</v>
       </c>
       <c r="C136" t="str">
-        <v>翻滾</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>翻滚速度</v>
+        <v>翻滚</v>
       </c>
       <c r="C137" t="str">
-        <v>翻滾速度</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>正在构建色域…</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C138" t="str">
-        <v>正在建構色域…</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>无色域</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C139" t="str">
-        <v>無色域</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>显示/隐藏</v>
+        <v>无色域</v>
       </c>
       <c r="C140" t="str">
-        <v>顯示/隱藏</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D 色域外壳</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C141" t="str">
-        <v>3D 色域外殼</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D 色域切片</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C142" t="str">
-        <v>2D 色域切片</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>平面</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C143" t="str">
-        <v>平面</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
       <c r="C144" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="C145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="C146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
+        <v>b*</v>
       </c>
       <c r="C147" t="str">
-        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>链接</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C148" t="str">
-        <v>連結</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
+        <v>链接</v>
       </c>
       <c r="C149" t="str">
-        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C150" t="str">
-        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4 显示器生成器</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C151" t="str">
-        <v>V4 顯示器產生器</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C152" t="str">
-        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB 显示器</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C153" t="str">
-        <v>V5 RGB 顯示器</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>拖入显示器配置文件</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C154" t="str">
-        <v>拖入顯示器設定檔</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 观察者 (PCC)</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C155" t="str">
-        <v>V5 觀察者 (PCC)</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>拖入观察者配置文件</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C156" t="str">
-        <v>拖入觀察者設定檔</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C157" t="str">
-        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>创建 V4 显示器配置文件</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C158" t="str">
-        <v>建立 V4 顯示器設定檔</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>配置文件名称</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C159" t="str">
-        <v>設定檔名稱</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>创建</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C160" t="str">
-        <v>建立</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>正在创建…</v>
+        <v>创建</v>
       </c>
       <c r="C161" t="str">
-        <v>正在建立…</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
+        <v>正在创建…</v>
       </c>
       <c r="C162" t="str">
-        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>链接流水线</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C163" t="str">
-        <v>連結管線</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
+        <v>链接流水线</v>
       </c>
       <c r="C164" t="str">
-        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
+        <v>連結管線</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>完成</v>
+        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
       </c>
       <c r="C165" t="str">
-        <v>完成</v>
+        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
+        <v>完成</v>
       </c>
       <c r="C166" t="str">
-        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>正在检查图像…</v>
+        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
       </c>
       <c r="C167" t="str">
-        <v>正在檢查影像…</v>
+        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在检查图像…</v>
       </c>
       <c r="C168" t="str">
-        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在檢查影像…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
+        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C169" t="str">
-        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
+        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>转换图像</v>
+        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
       </c>
       <c r="C170" t="str">
-        <v>轉換影像</v>
+        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>正在转换…</v>
+        <v>转换图像</v>
       </c>
       <c r="C171" t="str">
-        <v>正在轉換…</v>
+        <v>轉換影像</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>拖放配置文件以开始链条</v>
+        <v>正在转换…</v>
       </c>
       <c r="C172" t="str">
-        <v>拖放描述檔以開始鏈條</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>已移除</v>
+        <v>拖放配置文件以开始链条</v>
       </c>
       <c r="C173" t="str">
-        <v>已移除</v>
+        <v>拖放描述檔以開始鏈條</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>前移</v>
+        <v>已移除</v>
       </c>
       <c r="C174" t="str">
-        <v>前移</v>
+        <v>已移除</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>后移</v>
+        <v>前移</v>
       </c>
       <c r="C175" t="str">
-        <v>後移</v>
+        <v>前移</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>上移</v>
+        <v>后移</v>
       </c>
       <c r="C176" t="str">
-        <v>上移</v>
+        <v>後移</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>下移</v>
+        <v>上移</v>
       </c>
       <c r="C177" t="str">
-        <v>下移</v>
+        <v>上移</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>渲染意图（全部）</v>
+        <v>下移</v>
       </c>
       <c r="C178" t="str">
-        <v>演算意圖（全部）</v>
+        <v>下移</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>此转换的渲染意图</v>
+        <v>渲染意图（全部）</v>
       </c>
       <c r="C179" t="str">
-        <v>此轉換的演算意圖</v>
+        <v>演算意圖（全部）</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>各转换使用了不同的渲染意图</v>
+        <v>此转换的渲染意图</v>
       </c>
       <c r="C180" t="str">
-        <v>各轉換使用了不同的演算意圖</v>
+        <v>此轉換的演算意圖</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
+        <v>各转换使用了不同的渲染意图</v>
       </c>
       <c r="C181" t="str">
-        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
+        <v>各轉換使用了不同的演算意圖</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
+        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
       </c>
       <c r="C182" t="str">
-        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
+        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>链条</v>
+        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
       </c>
       <c r="C183" t="str">
-        <v>鏈條</v>
+        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>无法分析该链条。</v>
+        <v>链条</v>
       </c>
       <c r="C184" t="str">
-        <v>無法分析該鏈條。</v>
+        <v>鏈條</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>正在检查链条…</v>
+        <v>无法分析该链条。</v>
       </c>
       <c r="C185" t="str">
-        <v>正在檢查鏈條…</v>
+        <v>無法分析該鏈條。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>链条未能衔接（{detail}）。</v>
+        <v>正在检查链条…</v>
       </c>
       <c r="C186" t="str">
-        <v>鏈條未能銜接（{detail}）。</v>
+        <v>正在檢查鏈條…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
+        <v>链条未能衔接（{detail}）。</v>
       </c>
       <c r="C187" t="str">
-        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
+        <v>鏈條未能銜接（{detail}）。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>请先修复链条，再处理图像</v>
+        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
       </c>
       <c r="C188" t="str">
-        <v>請先修正鏈條，再處理影像</v>
+        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>清除</v>
+        <v>请先修复链条，再处理图像</v>
       </c>
       <c r="C189" t="str">
-        <v>清除</v>
+        <v>請先修正鏈條，再處理影像</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>生成 DeviceLink</v>
+        <v>清除</v>
       </c>
       <c r="C190" t="str">
-        <v>產生 DeviceLink</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink 名称</v>
+        <v>生成 DeviceLink</v>
       </c>
       <c r="C191" t="str">
-        <v>DeviceLink 名稱</v>
+        <v>產生 DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>正在生成…</v>
+        <v>DeviceLink 名称</v>
       </c>
       <c r="C192" t="str">
-        <v>正在產生…</v>
+        <v>DeviceLink 名稱</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>已创建“{name}”——已添加到池和此标签页。</v>
+        <v>正在生成…</v>
       </c>
       <c r="C193" t="str">
-        <v>已建立「{name}」——已加入集區與此分頁。</v>
+        <v>正在產生…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
+        <v>已创建“{name}”——已添加到池和此标签页。</v>
       </c>
       <c r="C194" t="str">
-        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
+        <v>已建立「{name}」——已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>构建链条以处理图像</v>
+        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
       </c>
       <c r="C195" t="str">
-        <v>建立鏈條以處理影像</v>
+        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>此链条的首尾并非图像色彩空间</v>
+        <v>构建链条以处理图像</v>
       </c>
       <c r="C196" t="str">
-        <v>此鏈條的首尾並非影像色彩空間</v>
+        <v>建立鏈條以處理影像</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>已保存转换后的图像。</v>
+        <v>此链条的首尾并非图像色彩空间</v>
       </c>
       <c r="C197" t="str">
-        <v>已儲存轉換後的影像。</v>
+        <v>此鏈條的首尾並非影像色彩空間</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
+        <v>已保存转换后的图像。</v>
       </c>
       <c r="C198" t="str">
-        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
+        <v>已儲存轉換後的影像。</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>无法读取该文件。</v>
+        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
       </c>
       <c r="C199" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>数据文件过大。</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C200" t="str">
-        <v>資料檔案過大。</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>转换数据</v>
+        <v>数据文件过大。</v>
       </c>
       <c r="C201" t="str">
-        <v>轉換資料</v>
+        <v>資料檔案過大。</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>正在转换…</v>
+        <v>转换数据</v>
       </c>
       <c r="C202" t="str">
-        <v>正在轉換…</v>
+        <v>轉換資料</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>偏好</v>
+        <v>正在转换…</v>
       </c>
       <c r="C203" t="str">
-        <v>偏好</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>观察者</v>
+        <v>偏好</v>
       </c>
       <c r="C204" t="str">
-        <v>觀察者</v>
+        <v>偏好</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>光源</v>
+        <v>观察者</v>
       </c>
       <c r="C205" t="str">
-        <v>光源</v>
+        <v>觀察者</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>条件</v>
+        <v>光源</v>
       </c>
       <c r="C206" t="str">
-        <v>條件</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>过滤 {n} 个重复项</v>
+        <v>条件</v>
       </c>
       <c r="C207" t="str">
-        <v>篩選 {n} 個重複項</v>
+        <v>條件</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>中位数</v>
+        <v>过滤 {n} 个重复项</v>
       </c>
       <c r="C208" t="str">
-        <v>中位數</v>
+        <v>篩選 {n} 個重複項</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>平均值</v>
+        <v>中位数</v>
       </c>
       <c r="C209" t="str">
-        <v>平均值</v>
+        <v>中位數</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>色块</v>
+        <v>平均值</v>
       </c>
       <c r="C210" t="str">
-        <v>色塊</v>
+        <v>平均值</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} 个重复项</v>
+        <v>色块</v>
       </c>
       <c r="C211" t="str">
-        <v>{n} 個重複項</v>
+        <v>色塊</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>转换结果</v>
+        <v>{n} 个重复项</v>
       </c>
       <c r="C212" t="str">
-        <v>轉換結果</v>
+        <v>{n} 個重複項</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} 个色块</v>
+        <v>转换结果</v>
       </c>
       <c r="C213" t="str">
-        <v>{src} → {dst} · {n} 個色塊</v>
+        <v>轉換結果</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
+        <v>{src} → {dst} · {n} 个色块</v>
       </c>
       <c r="C214" t="str">
-        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
+        <v>{src} → {dst} · {n} 個色塊</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>另存为</v>
+        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
       </c>
       <c r="C215" t="str">
-        <v>另存新檔</v>
+        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>保存</v>
+        <v>另存为</v>
       </c>
       <c r="C216" t="str">
-        <v>儲存</v>
+        <v>另存新檔</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>反向转换</v>
+        <v>保存</v>
       </c>
       <c r="C217" t="str">
-        <v>反向轉換</v>
+        <v>儲存</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>正在反向计算…</v>
+        <v>反向转换</v>
       </c>
       <c r="C218" t="str">
-        <v>正在反向計算…</v>
+        <v>反向轉換</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>反转</v>
+        <v>正在反向计算…</v>
       </c>
       <c r="C219" t="str">
-        <v>反轉</v>
+        <v>正在反向計算…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>最后阶段</v>
+        <v>反转</v>
       </c>
       <c r="C220" t="str">
-        <v>最後階段</v>
+        <v>反轉</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>第一阶段</v>
+        <v>最后阶段</v>
       </c>
       <c r="C221" t="str">
-        <v>第一階段</v>
+        <v>最後階段</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>输入数据为 {in} → 搜索 {out}</v>
+        <v>第一阶段</v>
       </c>
       <c r="C222" t="str">
-        <v>輸入資料為 {in} → 搜尋 {out}</v>
+        <v>第一階段</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>反转需要 2–3 个配置文件组成的链条</v>
+        <v>输入数据为 {in} → 搜索 {out}</v>
       </c>
       <c r="C223" t="str">
-        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
+        <v>輸入資料為 {in} → 搜尋 {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
+        <v>反转需要 2–3 个配置文件组成的链条</v>
       </c>
       <c r="C224" t="str">
-        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
+        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE 代价</v>
+        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
       </c>
       <c r="C225" t="str">
-        <v>ΔE 代價</v>
+        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>此图像嵌入了 ICC 配置文件。</v>
+        <v>ΔE 代价</v>
       </c>
       <c r="C226" t="str">
-        <v>此影像內嵌了 ICC 描述檔。</v>
+        <v>ΔE 代價</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>提取并添加到链条</v>
+        <v>此图像嵌入了 ICC 配置文件。</v>
       </c>
       <c r="C227" t="str">
-        <v>擷取並加入鏈條</v>
+        <v>此影像內嵌了 ICC 描述檔。</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>正在提取…</v>
+        <v>提取并添加到链条</v>
       </c>
       <c r="C228" t="str">
-        <v>正在擷取…</v>
+        <v>擷取並加入鏈條</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>忽略</v>
+        <v>正在提取…</v>
       </c>
       <c r="C229" t="str">
-        <v>忽略</v>
+        <v>正在擷取…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
+        <v>忽略</v>
       </c>
       <c r="C230" t="str">
-        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
+        <v>忽略</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>图像输出选项</v>
+        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
       </c>
       <c r="C231" t="str">
-        <v>影像輸出選項</v>
+        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>编码</v>
+        <v>图像输出选项</v>
       </c>
       <c r="C232" t="str">
-        <v>編碼</v>
+        <v>影像輸出選項</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>与源相同</v>
+        <v>编码</v>
       </c>
       <c r="C233" t="str">
-        <v>與來源相同</v>
+        <v>編碼</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 位</v>
+        <v>与源相同</v>
       </c>
       <c r="C234" t="str">
-        <v>8 位元</v>
+        <v>與來源相同</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 位</v>
+        <v>8 位</v>
       </c>
       <c r="C235" t="str">
-        <v>16 位元</v>
+        <v>8 位元</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>浮点（32 位）</v>
+        <v>16 位</v>
       </c>
       <c r="C236" t="str">
-        <v>浮點（32 位元）</v>
+        <v>16 位元</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>压缩</v>
+        <v>浮点（32 位）</v>
       </c>
       <c r="C237" t="str">
-        <v>壓縮</v>
+        <v>浮點（32 位元）</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>无</v>
+        <v>压缩</v>
       </c>
       <c r="C238" t="str">
-        <v>無</v>
+        <v>壓縮</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>平面格式</v>
+        <v>无</v>
       </c>
       <c r="C239" t="str">
-        <v>平面格式</v>
+        <v>無</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>交错</v>
+        <v>平面格式</v>
       </c>
       <c r="C240" t="str">
-        <v>交錯</v>
+        <v>平面格式</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>分离</v>
+        <v>交错</v>
       </c>
       <c r="C241" t="str">
-        <v>分離</v>
+        <v>交錯</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM 插值</v>
+        <v>分离</v>
       </c>
       <c r="C242" t="str">
-        <v>CMM 內插</v>
+        <v>分離</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>四面体</v>
+        <v>CMM 插值</v>
       </c>
       <c r="C243" t="str">
-        <v>四面體</v>
+        <v>CMM 內插</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>线性</v>
+        <v>四面体</v>
       </c>
       <c r="C244" t="str">
-        <v>線性</v>
+        <v>四面體</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>嵌入 ICC</v>
+        <v>线性</v>
       </c>
       <c r="C245" t="str">
-        <v>內嵌 ICC</v>
+        <v>線性</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
+        <v>嵌入 ICC</v>
       </c>
       <c r="C246" t="str">
-        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
+        <v>內嵌 ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>组装光谱 TIFF</v>
+        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
       </c>
       <c r="C247" t="str">
-        <v>組裝光譜 TIFF</v>
+        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
+        <v>组装光谱 TIFF</v>
       </c>
       <c r="C248" t="str">
-        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
+        <v>組裝光譜 TIFF</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>将光谱图像拖放到此处（或点击选择）</v>
+        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
       </c>
       <c r="C249" t="str">
-        <v>將光譜影像拖放到此處（或點擊選擇）</v>
+        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>通道</v>
+        <v>将光谱图像拖放到此处（或点击选择）</v>
       </c>
       <c r="C250" t="str">
-        <v>通道</v>
+        <v>將光譜影像拖放到此處（或點擊選擇）</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>组装并保存</v>
+        <v>通道</v>
       </c>
       <c r="C251" t="str">
-        <v>組裝並儲存</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>正在组装…</v>
+        <v>组装并保存</v>
       </c>
       <c r="C252" t="str">
-        <v>正在組裝…</v>
+        <v>組裝並儲存</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>已组装 {n} 个通道。</v>
+        <v>正在组装…</v>
       </c>
       <c r="C253" t="str">
-        <v>已組裝 {n} 個通道。</v>
+        <v>正在組裝…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
+        <v>已组装 {n} 个通道。</v>
       </c>
       <c r="C254" t="str">
-        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
+        <v>已組裝 {n} 個通道。</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>取消</v>
+        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C255" t="str">
-        <v>取消</v>
+        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>有 {n} 个文件未加载</v>
+        <v>取消</v>
       </c>
       <c r="C256" t="str">
-        <v>有 {n} 個檔案未載入</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C257" t="str">
-        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>确定</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C258" t="str">
-        <v>確定</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>确定</v>
       </c>
       <c r="C259" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>或</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C260" t="str">
-        <v>或</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>选择文件</v>
+        <v>或</v>
       </c>
       <c r="C261" t="str">
-        <v>選擇檔案</v>
+        <v>或</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>选择文件</v>
       </c>
       <c r="C262" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>标头</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C263" t="str">
-        <v>標頭</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>标签</v>
+        <v>标头</v>
       </c>
       <c r="C264" t="str">
-        <v>標籤</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>验证</v>
+        <v>标签</v>
       </c>
       <c r="C265" t="str">
-        <v>驗證</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>分析</v>
+        <v>验证</v>
       </c>
       <c r="C266" t="str">
-        <v>分析</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>中性轴墨量</v>
+        <v>分析</v>
       </c>
       <c r="C267" t="str">
-        <v>中性軸墨量</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C268" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C269" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C270" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>渲染意图</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C271" t="str">
-        <v>轉換意圖</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% 墨量</v>
+        <v>渲染意图</v>
       </c>
       <c r="C272" t="str">
-        <v>% 墨量</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* 输出（色调）</v>
+        <v>% 墨量</v>
       </c>
       <c r="C273" t="str">
-        <v>L* 輸出（色調）</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 输出（色调）</v>
       </c>
       <c r="C274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 輸出（色調）</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>极值比色</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C275" t="str">
-        <v>極值比色</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
+        <v>极值比色</v>
       </c>
       <c r="C276" t="str">
-        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
+        <v>極值比色</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
+        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
       </c>
       <c r="C277" t="str">
-        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
+        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>相对</v>
+        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
       </c>
       <c r="C278" t="str">
-        <v>相對</v>
+        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>绝对</v>
+        <v>相对</v>
       </c>
       <c r="C279" t="str">
-        <v>絕對</v>
+        <v>相對</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>白点</v>
+        <v>绝对</v>
       </c>
       <c r="C280" t="str">
-        <v>白點</v>
+        <v>絕對</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>黑点</v>
+        <v>白点</v>
       </c>
       <c r="C281" t="str">
-        <v>黑點</v>
+        <v>白點</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>黑点处的墨量</v>
+        <v>黑点</v>
       </c>
       <c r="C282" t="str">
-        <v>黑點處的墨量</v>
+        <v>黑點</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>黑点处的墨量</v>
       </c>
       <c r="C283" t="str">
-        <v>TAC</v>
+        <v>黑點處的墨量</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
+        <v>TAC</v>
       </c>
       <c r="C284" t="str">
-        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
+        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
       </c>
       <c r="C285" t="str">
-        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
+        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>实地与最大彩度</v>
+        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
       </c>
       <c r="C286" t="str">
-        <v>實地與最大彩度</v>
+        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
+        <v>实地与最大彩度</v>
       </c>
       <c r="C287" t="str">
-        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
+        <v>實地與最大彩度</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>色相</v>
+        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C288" t="str">
-        <v>色相</v>
+        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>实地</v>
+        <v>色相</v>
       </c>
       <c r="C289" t="str">
-        <v>實地</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>最大 C*</v>
+        <v>实地</v>
       </c>
       <c r="C290" t="str">
-        <v>最大 C*</v>
+        <v>實地</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>对应墨量</v>
+        <v>最大 C*</v>
       </c>
       <c r="C291" t="str">
-        <v>對應墨量</v>
+        <v>最大 C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
+        <v>对应墨量</v>
       </c>
       <c r="C292" t="str">
-        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
+        <v>對應墨量</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>暗调中的用墨</v>
+        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C293" t="str">
-        <v>暗部的用墨</v>
+        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
+        <v>暗调中的用墨</v>
       </c>
       <c r="C294" t="str">
-        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
+        <v>暗部的用墨</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
+        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
       </c>
       <c r="C295" t="str">
-        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
+        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>恒定 L* 平面</v>
+        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C296" t="str">
-        <v>固定 L* 平面</v>
+        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>黑点补偿自</v>
+        <v>恒定 L* 平面</v>
       </c>
       <c r="C297" t="str">
-        <v>黑點補償自</v>
+        <v>固定 L* 平面</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>沿路径位置</v>
+        <v>黑点补偿自</v>
       </c>
       <c r="C298" t="str">
-        <v>沿路徑位置</v>
+        <v>黑點補償自</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>路径</v>
+        <v>沿路径位置</v>
       </c>
       <c r="C299" t="str">
-        <v>路徑</v>
+        <v>沿路徑位置</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>经中性轴的原色墨路</v>
+        <v>路径</v>
       </c>
       <c r="C300" t="str">
-        <v>經中性軸的原色墨路</v>
+        <v>路徑</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>色域内的三条路径——青→红、品红→绿、黄→蓝——每条都在其两端明度的中点经过中性轴，通过所选的 B2A 表。每个采样点都在色域内，因此与暗调路径不同，某个着色剂的任何突变或反转都是 CLUT 平滑性缺陷，而非色域映射伪影。</v>
+        <v>经中性轴的原色墨路</v>
       </c>
       <c r="C301" t="str">
-        <v>色域內的三條路徑——青→紅、洋紅→綠、黃→藍——每條都在其兩端明度的中點經過中性軸，通過所選的 B2A 表。每個取樣點都在色域內，因此與暗調路徑不同，某個著色劑的任何突變或反轉都是 CLUT 平滑性缺陷，而非色域映射假影。</v>
+        <v>經中性軸的原色墨路</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>原色墨路仅适用于输出（打印机）特性文件。</v>
+        <v>色域内的三条路径——青→红、品红→绿、黄→蓝——每条都在其两端明度的中点经过中性轴，通过所选的 B2A 表。每个采样点都在色域内，因此与暗调路径不同，某个着色剂的任何突变或反转都是 CLUT 平滑性缺陷，而非色域映射伪影。</v>
       </c>
       <c r="C302" t="str">
-        <v>原色墨路僅適用於輸出（印表機）特性檔。</v>
+        <v>色域內的三條路徑——青→紅、洋紅→綠、黃→藍——每條都在其兩端明度的中點經過中性軸，通過所選的 B2A 表。每個取樣點都在色域內，因此與暗調路徑不同，某個著色劑的任何突變或反轉都是 CLUT 平滑性缺陷，而非色域映射假影。</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>沿路径的位置（中点为中性）</v>
+        <v>原色墨路仅适用于输出（打印机）特性文件。</v>
       </c>
       <c r="C303" t="str">
-        <v>沿路徑的位置（中點為中性）</v>
+        <v>原色墨路僅適用於輸出（印表機）特性檔。</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>已为此意图应用黑场补偿。</v>
+        <v>沿路径的位置（中点为中性）</v>
       </c>
       <c r="C304" t="str">
-        <v>已為此意圖套用黑場補償。</v>
+        <v>沿路徑的位置（中點為中性）</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>墨量统计</v>
+        <v>已为此意图应用黑场补偿。</v>
       </c>
       <c r="C305" t="str">
-        <v>墨量統計</v>
+        <v>已為此意圖套用黑場補償。</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>特性文件施加的每种着色剂的用量，以总量和占总量的比例表示——即分色的用墨特征。</v>
+        <v>墨量统计</v>
       </c>
       <c r="C306" t="str">
-        <v>特性檔施加的每種著色劑的用量，以總量和佔總量的比例表示——即分色的用墨特徵。</v>
+        <v>墨量統計</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>墨量统计仅适用于输出（打印机）特性文件。</v>
+        <v>特性文件施加的每种着色剂的用量，以总量和占总量的比例表示——即分色的用墨特征。</v>
       </c>
       <c r="C307" t="str">
-        <v>墨量統計僅適用於輸出（印表機）特性檔。</v>
+        <v>特性檔施加的每種著色劑的用量，以總量和佔總量的比例表示——即分色的用墨特徵。</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>中性轴</v>
+        <v>墨量统计仅适用于输出（打印机）特性文件。</v>
       </c>
       <c r="C308" t="str">
-        <v>中性軸</v>
+        <v>墨量統計僅適用於輸出（印表機）特性檔。</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>平均覆盖率</v>
+        <v>中性轴</v>
       </c>
       <c r="C309" t="str">
-        <v>平均覆蓋率</v>
+        <v>中性軸</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>墨量占比</v>
+        <v>平均覆盖率</v>
       </c>
       <c r="C310" t="str">
-        <v>墨量佔比</v>
+        <v>平均覆蓋率</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>墨量占比是中性构建的指纹——每种着色剂在施加总墨量中所占的比例，与采样数量无关。</v>
+        <v>墨量占比</v>
       </c>
       <c r="C311" t="str">
-        <v>墨量佔比是中性建構的指紋——每種著色劑在施加總墨量中所佔的比例，與取樣數量無關。</v>
+        <v>墨量佔比</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>色域内的点</v>
+        <v>墨量占比是中性构建的指纹——每种着色剂在施加总墨量中所占的比例，与采样数量无关。</v>
       </c>
       <c r="C312" t="str">
-        <v>色域內的點</v>
+        <v>墨量佔比是中性建構的指紋——每種著色劑在施加總墨量中所佔的比例，與取樣數量無關。</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>对色域内所有颜色的墨量统计需要 B2A 方向的色域边界，目前尚未构建——待完成。</v>
+        <v>色域内的点</v>
       </c>
       <c r="C313" t="str">
-        <v>對色域內所有顏色的墨量統計需要 B2A 方向的色域邊界，目前尚未建構——待完成。</v>
+        <v>色域內的點</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>没有可汇总的着色剂数据。</v>
+        <v>对色域内所有颜色的墨量统计需要 B2A 方向的色域边界，目前尚未构建——待完成。</v>
       </c>
       <c r="C314" t="str">
-        <v>沒有可彙總的著色劑資料。</v>
+        <v>對色域內所有顏色的墨量統計需要 B2A 方向的色域邊界，目前尚未建構——待完成。</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>在下方选择 B2A（PCS→设备）表，即可查看每种着色剂的灰度墨量覆盖图。</v>
+        <v>没有可汇总的着色剂数据。</v>
       </c>
       <c r="C315" t="str">
-        <v>在下方選擇 B2A（PCS→裝置）表，即可檢視每種著色劑的灰階墨量覆蓋圖。</v>
+        <v>沒有可彙總的著色劑資料。</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>每种着色剂在同一网格上的墨量覆盖（越暗表示墨量越多）。</v>
+        <v>在下方选择 B2A（PCS→设备）表，即可查看每种着色剂的灰度墨量覆盖图。</v>
       </c>
       <c r="C316" t="str">
-        <v>每種著色劑在同一網格上的墨量覆蓋（越暗表示墨量越多）。</v>
+        <v>在下方選擇 B2A（PCS→裝置）表，即可檢視每種著色劑的灰階墨量覆蓋圖。</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>青</v>
+        <v>每种着色剂在同一网格上的墨量覆盖（越暗表示墨量越多）。</v>
       </c>
       <c r="C317" t="str">
-        <v>青</v>
+        <v>每種著色劑在同一網格上的墨量覆蓋（越暗表示墨量越多）。</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>品红</v>
+        <v>青</v>
       </c>
       <c r="C318" t="str">
-        <v>洋紅</v>
+        <v>青</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>黄</v>
+        <v>品红</v>
       </c>
       <c r="C319" t="str">
-        <v>黃</v>
+        <v>洋紅</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>红</v>
+        <v>黄</v>
       </c>
       <c r="C320" t="str">
-        <v>紅</v>
+        <v>黃</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>绿</v>
+        <v>红</v>
       </c>
       <c r="C321" t="str">
-        <v>綠</v>
+        <v>紅</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>蓝</v>
+        <v>绿</v>
       </c>
       <c r="C322" t="str">
-        <v>藍</v>
+        <v>綠</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>黑</v>
+        <v>蓝</v>
       </c>
       <c r="C323" t="str">
-        <v>黑</v>
+        <v>藍</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>感知</v>
+        <v>黑</v>
       </c>
       <c r="C324" t="str">
-        <v>感知</v>
+        <v>黑</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>相对比色</v>
+        <v>感知</v>
       </c>
       <c r="C325" t="str">
-        <v>相對比色</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>饱和度</v>
+        <v>相对比色</v>
       </c>
       <c r="C326" t="str">
-        <v>飽和度</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>绝对比色</v>
+        <v>饱和度</v>
       </c>
       <c r="C327" t="str">
-        <v>絕對比色</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>特性文件统计</v>
+        <v>绝对比色</v>
       </c>
       <c r="C328" t="str">
-        <v>特性檔統計</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C329" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C330" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>渲染意图</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C331" t="str">
-        <v>轉換意圖</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>渲染意图</v>
       </c>
       <c r="C332" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>往返 ΔE</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C333" t="str">
-        <v>往返 ΔE</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C334" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>均值</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C335" t="str">
-        <v>平均</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>均值</v>
       </c>
       <c r="C336" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
       <c r="C337" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
       <c r="C338" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
       <c r="C339" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>分析</v>
       </c>
       <c r="C340" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>绘图</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C341" t="str">
-        <v>繪圖</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>原始输出</v>
+        <v>绘图</v>
       </c>
       <c r="C342" t="str">
-        <v>原始輸出</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>原始输出</v>
       </c>
       <c r="C343" t="str">
-        <v>XML</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>曲线</v>
+        <v>JSON</v>
       </c>
       <c r="C345" t="str">
-        <v>曲線</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>输入曲线</v>
+        <v>曲线</v>
       </c>
       <c r="C346" t="str">
-        <v>輸入曲線</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>输出曲线</v>
+        <v>输入曲线</v>
       </c>
       <c r="C347" t="str">
-        <v>輸出曲線</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT 图像</v>
+        <v>输出曲线</v>
       </c>
       <c r="C348" t="str">
-        <v>CLUT 影像</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>色域图像</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C349" t="str">
-        <v>色域影像</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>色度</v>
+        <v>色域图像</v>
       </c>
       <c r="C350" t="str">
-        <v>色度</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>散点图</v>
+        <v>色度</v>
       </c>
       <c r="C351" t="str">
-        <v>散佈圖</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>色调响应曲线</v>
+        <v>散点图</v>
       </c>
       <c r="C352" t="str">
-        <v>色調響應曲線</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>曲线表</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C353" t="str">
-        <v>曲線表</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>表格</v>
+        <v>曲线表</v>
       </c>
       <c r="C354" t="str">
-        <v>表格</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>数据</v>
+        <v>表格</v>
       </c>
       <c r="C355" t="str">
-        <v>資料</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>求值</v>
+        <v>数据</v>
       </c>
       <c r="C356" t="str">
-        <v>求值</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>加载中…</v>
+        <v>求值</v>
       </c>
       <c r="C357" t="str">
-        <v>載入中…</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>输入</v>
+        <v>加载中…</v>
       </c>
       <c r="C358" t="str">
-        <v>輸入</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>输出</v>
+        <v>输入</v>
       </c>
       <c r="C359" t="str">
-        <v>輸出</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>浮点值</v>
+        <v>输出</v>
       </c>
       <c r="C360" t="str">
-        <v>浮點值</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>网格点</v>
+        <v>浮点值</v>
       </c>
       <c r="C361" t="str">
-        <v>網格點</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>归一化</v>
+        <v>网格点</v>
       </c>
       <c r="C362" t="str">
-        <v>正規化</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>可读值</v>
+        <v>归一化</v>
       </c>
       <c r="C363" t="str">
-        <v>可讀值</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>设备 → PCS</v>
+        <v>可读值</v>
       </c>
       <c r="C364" t="str">
-        <v>裝置 → PCS</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → 设备</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C365" t="str">
-        <v>PCS → 裝置</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>无 CLUT 网格</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C366" t="str">
-        <v>無 CLUT 網格</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>加载中…</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C367" t="str">
-        <v>載入中…</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>加载中…</v>
       </c>
       <c r="C368" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C369" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C370" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C371" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C372" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C373" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C374" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C375" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
       <c r="C376" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>质量</v>
+        <v>符合性</v>
       </c>
       <c r="C377" t="str">
-        <v>品質</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>质量</v>
       </c>
       <c r="C378" t="str">
-        <v>HDR</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>代码点</v>
+        <v>HDR</v>
       </c>
       <c r="C379" t="str">
-        <v>代碼點</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>增益曲线</v>
+        <v>代码点</v>
       </c>
       <c r="C380" t="str">
-        <v>增益曲線</v>
+        <v>代碼點</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>环境</v>
+        <v>增益曲线</v>
       </c>
       <c r="C381" t="str">
-        <v>環境</v>
+        <v>增益曲線</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>显示 SDR 回退</v>
+        <v>环境</v>
       </c>
       <c r="C382" t="str">
-        <v>顯示 SDR 回退</v>
+        <v>環境</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>链中包含 HDR 配置文件</v>
+        <v>显示 SDR 回退</v>
       </c>
       <c r="C383" t="str">
-        <v>鏈中包含 HDR 設定檔</v>
+        <v>顯示 SDR 回退</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>通过 HDR 配置文件的转换会使用其 AToB0Tag——即 8.10.6 条款要求的固化 SDR 渲染——因为 8.10.1 条款不允许其包含 TRC 标签。结果是该回退，而非 HDR 行为。</v>
+        <v>链中包含 HDR 配置文件</v>
       </c>
       <c r="C384" t="str">
-        <v>透過 HDR 設定檔的轉換會使用其 AToB0Tag——即 8.10.6 條款要求的固化 SDR 算繪——因為 8.10.1 條款不允許其包含 TRC 標籤。結果是該回退，而非 HDR 行為。</v>
+        <v>鏈中包含 HDR 設定檔</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>这些是 HDR 配置文件，不含 TRC 标签，因此色域由 AToB0Tag 构建——即 8.10.6 条款要求为无 HDR 处理的消费者提供的固化 SDR 渲染。这不是配置文件的 HDR 色域，后者无法在有界 PCS 中绘制。</v>
+        <v>通过 HDR 配置文件的转换会使用其 AToB0Tag——即 8.10.6 条款要求的固化 SDR 渲染——因为 8.10.1 条款不允许其包含 TRC 标签。结果是该回退，而非 HDR 行为。</v>
       </c>
       <c r="C385" t="str">
-        <v>這些是 HDR 設定檔，不含 TRC 標籤，因此色域由 AToB0Tag 建構——即 8.10.6 條款要求為無 HDR 處理的消費者提供的固化 SDR 算繪。這不是設定檔的 HDR 色域，後者無法在有界 PCS 中繪製。</v>
+        <v>透過 HDR 設定檔的轉換會使用其 AToB0Tag——即 8.10.6 條款要求的固化 SDR 算繪——因為 8.10.1 條款不允許其包含 TRC 標籤。結果是該回退，而非 HDR 行為。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>检测中…</v>
+        <v>这些是 HDR 配置文件，不含 TRC 标签，因此色域由 AToB0Tag 构建——即 8.10.6 条款要求为无 HDR 处理的消费者提供的固化 SDR 渲染。这不是配置文件的 HDR 色域，后者无法在有界 PCS 中绘制。</v>
       </c>
       <c r="C386" t="str">
-        <v>偵測中…</v>
+        <v>這些是 HDR 設定檔，不含 TRC 標籤，因此色域由 AToB0Tag 建構——即 8.10.6 條款要求為無 HDR 處理的消費者提供的固化 SDR 算繪。這不是設定檔的 HDR 色域，後者無法在有界 PCS 中繪製。</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>无法检测环境。</v>
+        <v>检测中…</v>
       </c>
       <c r="C387" t="str">
-        <v>無法偵測環境。</v>
+        <v>偵測中…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>HDR 显示器</v>
+        <v>无法检测环境。</v>
       </c>
       <c r="C388" t="str">
-        <v>HDR 顯示器</v>
+        <v>無法偵測環境。</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>广色域</v>
+        <v>HDR 显示器</v>
       </c>
       <c r="C389" t="str">
-        <v>廣色域</v>
+        <v>HDR 顯示器</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>HDR 画布路径</v>
+        <v>广色域</v>
       </c>
       <c r="C390" t="str">
-        <v>HDR 畫布路徑</v>
+        <v>廣色域</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>HDR 画布路径</v>
       </c>
       <c r="C391" t="str">
-        <v>sRGB</v>
+        <v>HDR 畫布路徑</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>无</v>
+        <v>sRGB</v>
       </c>
       <c r="C392" t="str">
-        <v>無</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>是</v>
+        <v>无</v>
       </c>
       <c r="C393" t="str">
-        <v>是</v>
+        <v>無</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="C394" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>未报告</v>
+        <v>否</v>
       </c>
       <c r="C395" t="str">
-        <v>未回報</v>
+        <v>否</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>格式</v>
+        <v>未报告</v>
       </c>
       <c r="C396" t="str">
-        <v>格式</v>
+        <v>未回報</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>检查</v>
+        <v>格式</v>
       </c>
       <c r="C397" t="str">
-        <v>檢查</v>
+        <v>格式</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>显示</v>
+        <v>检查</v>
       </c>
       <c r="C398" t="str">
-        <v>顯示</v>
+        <v>檢查</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>显示</v>
       </c>
       <c r="C399" t="str">
-        <v>HDR</v>
+        <v>顯示</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>读取嵌入的 ICC 配置文件 — 无需解码器</v>
+        <v>HDR</v>
       </c>
       <c r="C400" t="str">
-        <v>讀取內嵌的 ICC 設定檔 — 不需解碼器</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>显示像素</v>
+        <v>读取嵌入的 ICC 配置文件 — 无需解码器</v>
       </c>
       <c r="C401" t="str">
-        <v>顯示像素</v>
+        <v>讀取內嵌的 ICC 設定檔 — 不需解碼器</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>渲染高于白色的亮度</v>
+        <v>显示像素</v>
       </c>
       <c r="C402" t="str">
-        <v>算繪高於白色的亮度</v>
+        <v>顯示像素</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>由 profiletool 自行解码，因此与浏览器无关</v>
+        <v>渲染高于白色的亮度</v>
       </c>
       <c r="C403" t="str">
-        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
+        <v>算繪高於白色的亮度</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>此浏览器未报告显示器的 HDR 余量，只报告了是否存在 HDR 路径。</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C404" t="str">
-        <v>此瀏覽器未回報顯示器的 HDR 餘量，只回報了是否存在 HDR 路徑。</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>浏览器标志</v>
+        <v>此浏览器未报告显示器的 HDR 余量，只报告了是否存在 HDR 路径。</v>
       </c>
       <c r="C405" t="str">
-        <v>瀏覽器旗標</v>
+        <v>此瀏覽器未回報顯示器的 HDR 餘量，只回報了是否存在 HDR 路徑。</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>已开启</v>
+        <v>浏览器标志</v>
       </c>
       <c r="C406" t="str">
-        <v>已開啟</v>
+        <v>瀏覽器旗標</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>未开启</v>
+        <v>已开启</v>
       </c>
       <c r="C407" t="str">
-        <v>未開啟</v>
+        <v>已開啟</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>此处无法检测</v>
+        <v>未开启</v>
       </c>
       <c r="C408" t="str">
-        <v>此處無法偵測</v>
+        <v>未開啟</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>此浏览器进行 HDR 渲染所必需：没有 WebGPU 时，HDR 画布是唯一途径。配置文件检查不受影响。</v>
+        <v>此处无法检测</v>
       </c>
       <c r="C409" t="str">
-        <v>此瀏覽器進行 HDR 算繪所必需：沒有 WebGPU 時，HDR 畫布是唯一途徑。設定檔檢查不受影響。</v>
+        <v>此處無法偵測</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>可选：HDR 可通过 WebGPU 渲染，但开启后会增加 HDR 画布途径，并让 profiletool 读取屏幕的真实 HDR 余量。</v>
+        <v>此浏览器进行 HDR 渲染所必需：没有 WebGPU 时，HDR 画布是唯一途径。配置文件检查不受影响。</v>
       </c>
       <c r="C410" t="str">
-        <v>選用：HDR 可透過 WebGPU 算繪，但開啟後會增加 HDR 畫布途徑，並讓 profiletool 讀取螢幕的真實 HDR 餘量。</v>
+        <v>此瀏覽器進行 HDR 算繪所必需：沒有 WebGPU 時，HDR 畫布是唯一途徑。設定檔檢查不受影響。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>网页无法打开标志页面。请将其粘贴到地址栏，设为 Enabled，然后重启浏览器。</v>
+        <v>可选：HDR 可通过 WebGPU 渲染，但开启后会增加 HDR 画布途径，并让 profiletool 读取屏幕的真实 HDR 余量。</v>
       </c>
       <c r="C411" t="str">
-        <v>網頁無法開啟旗標頁面。請將其貼到網址列，設為 Enabled，然後重新啟動瀏覽器。</v>
+        <v>選用：HDR 可透過 WebGPU 算繪，但開啟後會增加 HDR 畫布途徑，並讓 profiletool 讀取螢幕的真實 HDR 餘量。</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>复制</v>
+        <v>网页无法打开标志页面。请将其粘贴到地址栏，设为 Enabled，然后重启浏览器。</v>
       </c>
       <c r="C412" t="str">
-        <v>複製</v>
+        <v>網頁無法開啟旗標頁面。請將其貼到網址列，設為 Enabled，然後重新啟動瀏覽器。</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>已复制</v>
+        <v>复制</v>
       </c>
       <c r="C413" t="str">
-        <v>已複製</v>
+        <v>複製</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>复制失败 — 请选中地址并复制。</v>
+        <v>已复制</v>
       </c>
       <c r="C414" t="str">
-        <v>複製失敗 — 請選取網址並複製。</v>
+        <v>已複製</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>像素比</v>
+        <v>复制失败 — 请选中地址并复制。</v>
       </c>
       <c r="C415" t="str">
-        <v>像素比</v>
+        <v>複製失敗 — 請選取網址並複製。</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>当前显示器</v>
+        <v>像素比</v>
       </c>
       <c r="C416" t="str">
-        <v>目前顯示器</v>
+        <v>像素比</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>未命名</v>
+        <v>当前显示器</v>
       </c>
       <c r="C417" t="str">
-        <v>未命名</v>
+        <v>目前顯示器</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>主显示器</v>
+        <v>未命名</v>
       </c>
       <c r="C418" t="str">
-        <v>主顯示器</v>
+        <v>未命名</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>内置</v>
+        <v>主显示器</v>
       </c>
       <c r="C419" t="str">
-        <v>內建</v>
+        <v>主顯示器</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>HDR 余量</v>
+        <v>内置</v>
       </c>
       <c r="C420" t="str">
-        <v>HDR 餘量</v>
+        <v>內建</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>此浏览器未提供</v>
+        <v>HDR 余量</v>
       </c>
       <c r="C421" t="str">
-        <v>此瀏覽器未提供</v>
+        <v>HDR 餘量</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium 以“档”（stop）报告：显示器峰值亮度 ÷ SDR 白电平的 log₂。在 Windows 上，仅当 Chrome 重新读取显示器（窗口移到另一屏幕或 Chrome 重新激活）时才会刷新，调节亮度不会刷新。</v>
+        <v>此浏览器未提供</v>
       </c>
       <c r="C422" t="str">
-        <v>Chromium 以「檔」（stop）回報：顯示器峰值亮度 ÷ SDR 白色準位的 log₂。在 Windows 上，僅當 Chrome 重新讀取顯示器（視窗移到另一螢幕或 Chrome 重新啟用）時才會更新，調整亮度不會更新。</v>
+        <v>此瀏覽器未提供</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} 档（≈ SDR 白的 {ratio} 倍）</v>
+        <v>Chromium 以“档”（stop）报告：显示器峰值亮度 ÷ SDR 白电平的 log₂。在 Windows 上，仅当 Chrome 重新读取显示器（窗口移到另一屏幕或 Chrome 重新激活）时才会刷新，调节亮度不会刷新。</v>
       </c>
       <c r="C423" t="str">
-        <v>{stops} 檔（≈ SDR 白的 {ratio} 倍）</v>
+        <v>Chromium 以「檔」（stop）回報：顯示器峰值亮度 ÷ SDR 白色準位的 log₂。在 Windows 上，僅當 Chrome 重新讀取顯示器（視窗移到另一螢幕或 Chrome 重新啟用）時才會更新，調整亮度不會更新。</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} 档（≈ SDR 白的 {ratio} 倍）</v>
       </c>
       <c r="C424" t="str">
-        <v>HDR</v>
+        <v>{stops} 檔（≈ SDR 白的 {ratio} 倍）</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>指定显示余量下的增益</v>
+        <v>HDR</v>
       </c>
       <c r="C425" t="str">
-        <v>指定顯示餘量下的增益</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>在此显示器上查看一张 HDR 图像。浏览器能解码的文件由浏览器自身显示；OpenEXR 和 Radiance HDR 由 profiletool 解码并渲染。</v>
+        <v>指定显示余量下的增益</v>
       </c>
       <c r="C426" t="str">
-        <v>在此顯示器上檢視一張 HDR 影像。瀏覽器能解碼的檔案由瀏覽器自行顯示；OpenEXR 和 Radiance HDR 由 profiletool 解碼並算繪。</v>
+        <v>指定顯示餘量下的增益</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>将 HDR 图像拖放到此处，或点击选择</v>
+        <v>在此显示器上查看一张 HDR 图像。浏览器能解码的文件由浏览器自身显示；OpenEXR 和 Radiance HDR 由 profiletool 解码并渲染。</v>
       </c>
       <c r="C427" t="str">
-        <v>將 HDR 影像拖放到此處，或按一下選擇</v>
+        <v>在此顯示器上檢視一張 HDR 影像。瀏覽器能解碼的檔案由瀏覽器自行顯示；OpenEXR 和 Radiance HDR 由 profiletool 解碼並算繪。</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC 和 JPEG XL。</v>
+        <v>将 HDR 图像拖放到此处，或点击选择</v>
       </c>
       <c r="C428" t="str">
-        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC 和 JPEG XL。</v>
+        <v>將 HDR 影像拖放到此處，或按一下選擇</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>另选一张</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益图 JPEG）、PNG——以及 Safari 上的 HEIC 和 JPEG XL。</v>
       </c>
       <c r="C429" t="str">
-        <v>另選一張</v>
+        <v>OpenEXR、Radiance HDR（.hdr）、AVIF、JPEG（含增益圖 JPEG）、PNG——以及 Safari 上的 HEIC 和 JPEG XL。</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>清除</v>
+        <v>另选一张</v>
       </c>
       <c r="C430" t="str">
-        <v>清除</v>
+        <v>另選一張</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>嵌入的 ICC 配置文件</v>
+        <v>清除</v>
       </c>
       <c r="C431" t="str">
-        <v>嵌入的 ICC 描述檔</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>无——OpenEXR 通过色度坐标描述颜色</v>
+        <v>嵌入的 ICC 配置文件</v>
       </c>
       <c r="C432" t="str">
-        <v>無——OpenEXR 以色度座標描述色彩</v>
+        <v>嵌入的 ICC 描述檔</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>无——Radiance HDR 通过 PRIMARIES 文件头描述颜色</v>
+        <v>无——OpenEXR 通过色度坐标描述颜色</v>
       </c>
       <c r="C433" t="str">
-        <v>無——Radiance HDR 以 PRIMARIES 檔頭描述色彩</v>
+        <v>無——OpenEXR 以色度座標描述色彩</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>正在检查…</v>
+        <v>无——Radiance HDR 通过 PRIMARIES 文件头描述颜色</v>
       </c>
       <c r="C434" t="str">
-        <v>正在檢查…</v>
+        <v>無——Radiance HDR 以 PRIMARIES 檔頭描述色彩</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>无</v>
+        <v>正在检查…</v>
       </c>
       <c r="C435" t="str">
-        <v>無</v>
+        <v>正在檢查…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>在“配置文件”标签页中打开</v>
+        <v>无</v>
       </c>
       <c r="C436" t="str">
-        <v>在「描述檔」分頁中開啟</v>
+        <v>無</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>增益图</v>
+        <v>在“配置文件”标签页中打开</v>
       </c>
       <c r="C437" t="str">
-        <v>增益圖</v>
+        <v>在「描述檔」分頁中開啟</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>已检测到，未解码</v>
+        <v>增益图</v>
       </c>
       <c r="C438" t="str">
-        <v>已偵測到，未解碼</v>
+        <v>增益圖</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>这不是图像。请通过配置文件面板加载配置文件。</v>
+        <v>已检测到，未解码</v>
       </c>
       <c r="C439" t="str">
-        <v>這不是影像。請從描述檔面板載入描述檔。</v>
+        <v>已偵測到，未解碼</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>不是 profiletool 能识别的图像格式。</v>
+        <v>这不是图像。请通过配置文件面板加载配置文件。</v>
       </c>
       <c r="C440" t="str">
-        <v>不是 profiletool 能辨識的影像格式。</v>
+        <v>這不是影像。請從描述檔面板載入描述檔。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>此处暂不显示 TIFF 像素：浏览器不解码 TIFF，且 16 位 TIFF 中如何编码 HDR 尚未确定（第 4.3 阶段）。其嵌入的配置文件可以查看。</v>
+        <v>不是 profiletool 能识别的图像格式。</v>
       </c>
       <c r="C441" t="str">
-        <v>此處暫不顯示 TIFF 像素：瀏覽器不解碼 TIFF，且 16 位元 TIFF 中如何編碼 HDR 尚未決定（第 4.3 階段）。其嵌入的描述檔可以檢視。</v>
+        <v>不是 profiletool 能辨識的影像格式。</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>无法在此显示该图像：</v>
+        <v>此处暂不显示 TIFF 像素：浏览器不解码 TIFF，且 16 位 TIFF 中如何编码 HDR 尚未确定（第 4.3 阶段）。其嵌入的配置文件可以查看。</v>
       </c>
       <c r="C442" t="str">
-        <v>無法在此顯示此影像：</v>
+        <v>此處暫不顯示 TIFF 像素：瀏覽器不解碼 TIFF，且 16 位元 TIFF 中如何編碼 HDR 尚未決定（第 4.3 階段）。其嵌入的描述檔可以檢視。</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>其嵌入的配置文件仍可查看。</v>
+        <v>无法在此显示该图像：</v>
       </c>
       <c r="C443" t="str">
-        <v>其嵌入的描述檔仍可檢視。</v>
+        <v>無法在此顯示此影像：</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>显示方式</v>
+        <v>其嵌入的配置文件仍可查看。</v>
       </c>
       <c r="C444" t="str">
-        <v>顯示方式</v>
+        <v>其嵌入的描述檔仍可檢視。</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>浏览器</v>
+        <v>显示方式</v>
       </c>
       <c r="C445" t="str">
-        <v>瀏覽器</v>
+        <v>顯示方式</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>浏览器</v>
       </c>
       <c r="C446" t="str">
-        <v>profiletool</v>
+        <v>瀏覽器</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>HDR 显示器</v>
+        <v>profiletool</v>
       </c>
       <c r="C447" t="str">
-        <v>HDR 顯示器</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>浏览器会忽略仅由嵌入 ICC 配置文件标示的 HDR，因此该图像可能显得暗淡、平淡。</v>
+        <v>HDR 显示器</v>
       </c>
       <c r="C448" t="str">
-        <v>瀏覽器會忽略僅由嵌入 ICC 描述檔標示的 HDR，因此此影像可能看起來暗淡、平板。</v>
+        <v>HDR 顯示器</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>此浏览器无法在 SDR 与 HDR 之间切换图像，因此按浏览器的渲染显示。</v>
+        <v>浏览器会忽略仅由嵌入 ICC 配置文件标示的 HDR，因此该图像可能显得暗淡、平淡。</v>
       </c>
       <c r="C449" t="str">
-        <v>此瀏覽器無法在 SDR 與 HDR 之間切換影像，因此依瀏覽器的算繪顯示。</v>
+        <v>瀏覽器會忽略僅由嵌入 ICC 描述檔標示的 HDR，因此此影像可能看起來暗淡、平板。</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>浏览器无法解码此图像。</v>
+        <v>此浏览器无法在 SDR 与 HDR 之间切换图像，因此按浏览器的渲染显示。</v>
       </c>
       <c r="C450" t="str">
-        <v>瀏覽器無法解碼此影像。</v>
+        <v>此瀏覽器無法在 SDR 與 HDR 之間切換影像，因此依瀏覽器的算繪顯示。</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>输出</v>
+        <v>浏览器无法解码此图像。</v>
       </c>
       <c r="C451" t="str">
-        <v>輸出</v>
+        <v>瀏覽器無法解碼此影像。</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>HDR 画布（float16）</v>
+        <v>输出</v>
       </c>
       <c r="C452" t="str">
-        <v>HDR 畫布（float16）</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU（扩展范围）</v>
+        <v>HDR 画布（float16）</v>
       </c>
       <c r="C453" t="str">
-        <v>WebGPU（延伸範圍）</v>
+        <v>HDR 畫布（float16）</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>SDR 画布（色调映射）</v>
+        <v>WebGPU（扩展范围）</v>
       </c>
       <c r="C454" t="str">
-        <v>SDR 畫布（色調映射）</v>
+        <v>WebGPU（延伸範圍）</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>尺寸</v>
+        <v>SDR 画布（色调映射）</v>
       </c>
       <c r="C455" t="str">
-        <v>尺寸</v>
+        <v>SDR 畫布（色調映射）</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>最亮像素</v>
+        <v>尺寸</v>
       </c>
       <c r="C456" t="str">
-        <v>最亮像素</v>
+        <v>尺寸</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>SDR 白的 {n} 倍</v>
+        <v>最亮像素</v>
       </c>
       <c r="C457" t="str">
-        <v>SDR 白的 {n} 倍</v>
+        <v>最亮像素</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>色度坐标</v>
+        <v>SDR 白的 {n} 倍</v>
       </c>
       <c r="C458" t="str">
-        <v>色度座標</v>
+        <v>SDR 白的 {n} 倍</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>未注明——假定为 Rec. 709</v>
+        <v>色度坐标</v>
       </c>
       <c r="C459" t="str">
-        <v>未註明——假定為 Rec. 709</v>
+        <v>色度座標</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>此处无法使用 {from}（{why}）；改用下一种输出。</v>
+        <v>未注明——假定为 Rec. 709</v>
       </c>
       <c r="C460" t="str">
-        <v>此處無法使用 {from}（{why}）；改用下一種輸出。</v>
+        <v>未註明——假定為 Rec. 709</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>此输出无法承载比白色更亮的值，因此显示经色调映射的 SDR 渲染。</v>
+        <v>此处无法使用 {from}（{why}）；改用下一种输出。</v>
       </c>
       <c r="C461" t="str">
-        <v>此輸出無法承載比白色更亮的值，因此顯示經色調映射的 SDR 算繪。</v>
+        <v>此處無法使用 {from}（{why}）；改用下一種輸出。</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>曝光</v>
+        <v>此输出无法承载比白色更亮的值，因此显示经色调映射的 SDR 渲染。</v>
       </c>
       <c r="C462" t="str">
-        <v>曝光</v>
+        <v>此輸出無法承載比白色更亮的值，因此顯示經色調映射的 SDR 算繪。</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} 档</v>
+        <v>曝光</v>
       </c>
       <c r="C463" t="str">
-        <v>{n} 檔</v>
+        <v>曝光</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>无法解码：</v>
+        <v>{n} 档</v>
       </c>
       <c r="C464" t="str">
-        <v>無法解碼：</v>
+        <v>{n} 檔</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>此文件为 {size} MB；HDR 标签页最多打开 {max} MB 的图像。</v>
+        <v>无法解码：</v>
       </c>
       <c r="C465" t="str">
-        <v>此檔案為 {size} MB；HDR 分頁最多開啟 {max} MB 的影像。</v>
+        <v>無法解碼：</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>无法应用配置文件：</v>
+        <v>此文件为 {size} MB；HDR 标签页最多打开 {max} MB 的图像。</v>
       </c>
       <c r="C466" t="str">
-        <v>無法套用描述檔：</v>
+        <v>此檔案為 {size} MB；HDR 分頁最多開啟 {max} MB 的影像。</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>无法绘制图像：</v>
+        <v>无法应用配置文件：</v>
       </c>
       <c r="C467" t="str">
-        <v>無法繪製影像：</v>
+        <v>無法套用描述檔：</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>（这些原色无法构成色彩空间——已忽略，使用 Rec. 709）</v>
+        <v>无法绘制图像：</v>
       </c>
       <c r="C468" t="str">
-        <v>（這些原色無法構成色彩空間——已忽略，使用 Rec. 709）</v>
+        <v>無法繪製影像：</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>JPEG XL 的配置文件压缩在码流内部，profiletool 目前尚不能解压</v>
+        <v>（这些原色无法构成色彩空间——已忽略，使用 Rec. 709）</v>
       </c>
       <c r="C469" t="str">
-        <v>JPEG XL 的描述檔壓縮在碼流內部，profiletool 目前尚無法解壓縮</v>
+        <v>（這些原色無法構成色彩空間——已忽略，使用 Rec. 709）</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>正在解码…</v>
+        <v>JPEG XL 的配置文件压缩在码流内部，profiletool 目前尚不能解压</v>
       </c>
       <c r="C470" t="str">
-        <v>正在解碼…</v>
+        <v>JPEG XL 的描述檔壓縮在碼流內部，profiletool 目前尚無法解壓縮</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>动态范围</v>
+        <v>正在解码…</v>
       </c>
       <c r="C471" t="str">
-        <v>動態範圍</v>
+        <v>正在解碼…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>此浏览器只提供两个端点，不支持混合。</v>
+        <v>动态范围</v>
       </c>
       <c r="C472" t="str">
-        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
+        <v>動態範圍</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>由 profiletool 自行解码，因此与浏览器无关</v>
+        <v>此浏览器只提供两个端点，不支持混合。</v>
       </c>
       <c r="C473" t="str">
-        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
+        <v>此瀏覽器只提供兩個端點，不支援混合。</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>此浏览器可以解码</v>
+        <v>由 profiletool 自行解码，因此与浏览器无关</v>
       </c>
       <c r="C474" t="str">
-        <v>此瀏覽器可以解碼</v>
+        <v>由 profiletool 自行解碼，因此與瀏覽器無關</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>此浏览器无法解码</v>
+        <v>此浏览器可以解码</v>
       </c>
       <c r="C475" t="str">
-        <v>此瀏覽器無法解碼</v>
+        <v>此瀏覽器可以解碼</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
+        <v>此浏览器无法解码</v>
       </c>
       <c r="C476" t="str">
-        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
+        <v>此瀏覽器無法解碼</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
+        <v>显示 HEIC 需要 Safari 或其他 WebKit 浏览器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解码 HEIC</v>
       </c>
       <c r="C477" t="str">
-        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
+        <v>顯示 HEIC 需要 Safari 或其他 WebKit 瀏覽器——Chrome 和 Firefox 在任何平台（包括 macOS）上都不解碼 HEIC</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>推迟到后续版本</v>
+        <v>显示 JPEG XL 需要 Safari；其他浏览器尚未支持</v>
       </c>
       <c r="C478" t="str">
-        <v>延後至後續版本</v>
+        <v>顯示 JPEG XL 需要 Safari；其他瀏覽器尚未支援</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
+        <v>推迟到后续版本</v>
       </c>
       <c r="C479" t="str">
-        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
+        <v>延後至後續版本</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
+        <v>此显示器未报告 HDR 路径，因此 HDR 以色调映射后的 SDR 显示</v>
       </c>
       <c r="C480" t="str">
-        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
+        <v>此顯示器未回報 HDR 路徑，因此 HDR 以色調映射後的 SDR 顯示</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
+        <v>此浏览器没有 HDR 画布路径（需要 float16 画布或 WebGPU）</v>
       </c>
       <c r="C481" t="str">
-        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
+        <v>此瀏覽器沒有 HDR 畫布路徑（需要 float16 畫布或 WebGPU）</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>查看只需解析容器，不需要编解码器</v>
+        <v>Firefox 不显示 HDR 图像，也不读取增益图；HDR 内容以 SDR 显示</v>
       </c>
       <c r="C482" t="str">
-        <v>檢視只需解析容器，不需要編解碼器</v>
+        <v>Firefox 不顯示 HDR 影像，也不讀取增益圖；HDR 內容以 SDR 顯示</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>HDR 显示器和 HDR 画布路径均可用</v>
+        <v>查看只需解析容器，不需要编解码器</v>
       </c>
       <c r="C483" t="str">
-        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
+        <v>檢視只需解析容器，不需要編解碼器</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>未知格式</v>
+        <v>HDR 显示器和 HDR 画布路径均可用</v>
       </c>
       <c r="C484" t="str">
-        <v>未知格式</v>
+        <v>HDR 顯示器和 HDR 畫布路徑皆可用</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{os} 上的 {browser}</v>
+        <v>未知格式</v>
       </c>
       <c r="C485" t="str">
-        <v>{os} 上的 {browser}</v>
+        <v>未知格式</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · 检测到 HDR 显示器</v>
+        <v>{os} 上的 {browser}</v>
       </c>
       <c r="C486" t="str">
-        <v>{name} · 偵測到 HDR 顯示器</v>
+        <v>{os} 上的 {browser}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · SDR 显示器</v>
+        <v>{name} · 检测到 HDR 显示器</v>
       </c>
       <c r="C487" t="str">
-        <v>{name} · SDR 顯示器</v>
+        <v>{name} · 偵測到 HDR 顯示器</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
+        <v>{name} · SDR 显示器</v>
       </c>
       <c r="C488" t="str">
-        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
+        <v>{name} · SDR 顯示器</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
+        <v>WebGPU 应用了色调映射“{mode}”，因此输出被限制为 SDR</v>
       </c>
       <c r="C489" t="str">
-        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
+        <v>WebGPU 套用了色調映射「{mode}」，因此輸出被限制為 SDR</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>显示器峰值</v>
+        <v>此浏览器未报告所应用的 WebGPU 色调映射，因此 HDR 输出未经确认</v>
       </c>
       <c r="C490" t="str">
-        <v>顯示器峰值</v>
+        <v>此瀏覽器未回報所套用的 WebGPU 色調映射，因此 HDR 輸出未經確認</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>SDR 白的 {r} 倍（{n} 档）</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C491" t="str">
-        <v>SDR 白的 {r} 倍（{n} 檔）</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× —— SDR 显示器</v>
+        <v>SDR 白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C492" t="str">
-        <v>1× —— SDR 顯示器</v>
+        <v>SDR 白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>未知</v>
+        <v>1× —— SDR 显示器</v>
       </c>
       <c r="C493" t="str">
-        <v>未知</v>
+        <v>1× —— SDR 顯示器</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
+        <v>未知</v>
       </c>
       <c r="C494" t="str">
-        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
+        <v>此显示器未报告 HDR，因此浏览器在两端都以 SDR 显示此图像。</v>
       </c>
       <c r="C495" t="str">
-        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
+        <v>此顯示器未回報 HDR，因此瀏覽器在兩端都以 SDR 顯示此影像。</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
+        <v>此显示器未报告 HDR，因此比 SDR 白更亮的部分会被截断。“适配显示器”改为显示色调映射后的渲染。</v>
       </c>
       <c r="C496" t="str">
-        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
+        <v>此顯示器未回報 HDR，因此比 SDR 白更亮的部分會被裁切。「符合顯示器」改為顯示色調映射後的算繪。</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>适配显示器</v>
+        <v>此图像需要 SDR 白的 {img} 倍，但此显示器最高只能显示 {disp} 倍，更亮的值会被截断。“适配显示器”会将它们平滑压缩到显示器峰值。</v>
       </c>
       <c r="C497" t="str">
-        <v>符合顯示器</v>
+        <v>此影像需要 SDR 白的 {img} 倍，但此顯示器最高只能顯示 {disp} 倍，較亮的值會被裁切。「符合顯示器」會將它們平滑壓縮到顯示器峰值。</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>图像详情</v>
+        <v>适配显示器</v>
       </c>
       <c r="C498" t="str">
-        <v>影像詳細資訊</v>
+        <v>符合顯示器</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>不可用——此图像由浏览器渲染，无法将其限制在指定峰值</v>
+        <v>图像详情</v>
       </c>
       <c r="C499" t="str">
-        <v>無法使用——此影像由瀏覽器算繪，無法將其限制在指定峰值</v>
+        <v>影像詳細資訊</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>不可用——此输出无法显示高于 SDR 白的内容</v>
+        <v>不可用——此图像由浏览器渲染，无法将其限制在指定峰值</v>
       </c>
       <c r="C500" t="str">
-        <v>無法使用——此輸出無法顯示高於 SDR 白的內容</v>
+        <v>無法使用——此影像由瀏覽器算繪，無法將其限制在指定峰值</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>不可用——此显示器的峰值未知</v>
+        <v>不可用——此输出无法显示高于 SDR 白的内容</v>
       </c>
       <c r="C501" t="str">
-        <v>無法使用——此顯示器的峰值未知</v>
+        <v>無法使用——此輸出無法顯示高於 SDR 白的內容</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>放大</v>
+        <v>不可用——此显示器的峰值未知</v>
       </c>
       <c r="C502" t="str">
-        <v>放大</v>
+        <v>無法使用——此顯示器的峰值未知</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>缩小</v>
+        <v>放大</v>
       </c>
       <c r="C503" t="str">
-        <v>縮小</v>
+        <v>放大</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>适合图像</v>
+        <v>缩小</v>
       </c>
       <c r="C504" t="str">
-        <v>符合影像</v>
+        <v>縮小</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>实际像素（1:1）</v>
+        <v>适合图像</v>
       </c>
       <c r="C505" t="str">
-        <v>實際像素（1:1）</v>
+        <v>符合影像</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>拖动平移 · Ctrl+滚轮缩放 · 双击复位</v>
+        <v>实际像素（1:1）</v>
       </c>
       <c r="C506" t="str">
-        <v>拖曳平移 · Ctrl+滾輪縮放 · 按兩下復位</v>
+        <v>實際像素（1:1）</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>拖动以调整图像区域大小；双击恢复默认大小</v>
+        <v>拖动平移 · Ctrl+滚轮缩放 · 双击复位</v>
       </c>
       <c r="C507" t="str">
-        <v>拖曳以調整影像區域大小；按兩下還原預設大小</v>
+        <v>拖曳平移 · Ctrl+滾輪縮放 · 按兩下復位</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>图像视图</v>
+        <v>拖动以调整图像区域大小；双击恢复默认大小</v>
       </c>
       <c r="C508" t="str">
-        <v>影像檢視</v>
+        <v>拖曳以調整影像區域大小；按兩下還原預設大小</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
+        <v>图像视图</v>
       </c>
       <c r="C509" t="str">
-        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
+        <v>影像檢視</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>无上限</v>
+        <v>将亮度上限设为此显示器报告的峰值。在 Windows 上该值可能滞后于亮度变化。</v>
       </c>
       <c r="C510" t="str">
-        <v>無上限</v>
+        <v>將亮度上限設為此顯示器回報的峰值。在 Windows 上此值可能落後於亮度變化。</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>上限 {n} 档（{r}×）</v>
+        <v>无上限</v>
       </c>
       <c r="C511" t="str">
-        <v>上限 {n} 檔（{r}×）</v>
+        <v>無上限</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>SDR 白</v>
+        <v>上限 {n} 档（{r}×）</v>
       </c>
       <c r="C512" t="str">
-        <v>SDR 白</v>
+        <v>上限 {n} 檔（{r}×）</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
+        <v>SDR 白</v>
       </c>
       <c r="C513" t="str">
-        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
+        <v>SDR 白</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>SDR 白色色块</v>
+        <v>普通 SDR 白，用于对比。在 HDR 显示器上，HDR 高光看起来比它更亮。</v>
       </c>
       <c r="C514" t="str">
-        <v>SDR 白色色塊</v>
+        <v>一般 SDR 白，供比較。在 HDR 顯示器上，HDR 高光看起來比它更亮。</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>拖动即可移动；双击可将其放回图像旁边。</v>
+        <v>SDR 白色色块</v>
       </c>
       <c r="C515" t="str">
-        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
+        <v>SDR 白色色塊</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>指定配置文件</v>
+        <v>拖动即可移动；双击可将其放回图像旁边。</v>
       </c>
       <c r="C516" t="str">
-        <v>指定描述檔</v>
+        <v>拖曳即可移動；按兩下可將其放回影像旁邊。</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>无——按文件自身标示</v>
+        <v>指定配置文件</v>
       </c>
       <c r="C517" t="str">
-        <v>無——依檔案本身標示</v>
+        <v>指定描述檔</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>嵌入的配置文件（{n} B）</v>
+        <v>无——按文件自身标示</v>
       </c>
       <c r="C518" t="str">
-        <v>嵌入的描述檔（{n} B）</v>
+        <v>無——依檔案本身標示</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>池中的 HDR 配置文件</v>
+        <v>嵌入的配置文件（{n} B）</v>
       </c>
       <c r="C519" t="str">
-        <v>池中的 HDR 描述檔</v>
+        <v>嵌入的描述檔（{n} B）</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>配置文件</v>
+        <v>池中的 HDR 配置文件</v>
       </c>
       <c r="C520" t="str">
-        <v>描述檔</v>
+        <v>池中的 HDR 描述檔</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>嵌入的配置文件</v>
+        <v>配置文件</v>
       </c>
       <c r="C521" t="str">
-        <v>嵌入的描述檔</v>
+        <v>描述檔</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>色彩引擎路径</v>
+        <v>嵌入的配置文件</v>
       </c>
       <c r="C522" t="str">
-        <v>色彩引擎路徑</v>
+        <v>嵌入的描述檔</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>HDR 路径，已应用增益曲线</v>
+        <v>色彩引擎路径</v>
       </c>
       <c r="C523" t="str">
-        <v>HDR 路徑，已套用增益曲線</v>
+        <v>色彩引擎路徑</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>HDR 路径，无增益曲线</v>
+        <v>HDR 路径，已应用增益曲线</v>
       </c>
       <c r="C524" t="str">
-        <v>HDR 路徑，無增益曲線</v>
+        <v>HDR 路徑，已套用增益曲線</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>预烘焙的 AToB0——不是 HDR 路径</v>
+        <v>HDR 路径，无增益曲线</v>
       </c>
       <c r="C525" t="str">
-        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
+        <v>HDR 路徑，無增益曲線</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>传递函数</v>
+        <v>预烘焙的 AToB0——不是 HDR 路径</v>
       </c>
       <c r="C526" t="str">
-        <v>傳遞函數</v>
+        <v>預先烘焙的 AToB0——不是 HDR 路徑</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>HDR 参考白</v>
+        <v>传递函数</v>
       </c>
       <c r="C527" t="str">
-        <v>HDR 參考白</v>
+        <v>傳遞函數</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>线性值</v>
+        <v>HDR 参考白</v>
       </c>
       <c r="C528" t="str">
-        <v>線性值</v>
+        <v>HDR 參考白</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>文件 1.0 = HDR 参考白</v>
+        <v>线性值</v>
       </c>
       <c r="C529" t="str">
-        <v>檔案 1.0 = HDR 參考白</v>
+        <v>線性值</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 条）</v>
+        <v>文件 1.0 = HDR 参考白</v>
       </c>
       <c r="C530" t="str">
-        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 條）</v>
+        <v>檔案 1.0 = HDR 參考白</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>OpenEXR 和 Radiance HDR 文件按惯例将 SDR 白置于 1.0，而 ICC 线性传递函数把 1.0 读作 1 cd/m²。默认会缩放文件，使其 1.0 落在配置文件的 HDR 参考白上。</v>
+        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 条）</v>
       </c>
       <c r="C531" t="str">
-        <v>OpenEXR 與 Radiance HDR 檔案依慣例將 SDR 白置於 1.0，而 ICC 線性傳遞函數將 1.0 讀作 1 cd/m²。預設會縮放檔案，使其 1.0 落在描述檔的 HDR 參考白上。</v>
+        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 條）</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>输入缩放</v>
+        <v>OpenEXR 和 Radiance HDR 文件按惯例将 SDR 白置于 1.0，而 ICC 线性传递函数把 1.0 读作 1 cd/m²。默认会缩放文件，使其 1.0 落在配置文件的 HDR 参考白上。</v>
       </c>
       <c r="C532" t="str">
-        <v>輸入縮放</v>
+        <v>OpenEXR 與 Radiance HDR 檔案依慣例將 SDR 白置於 1.0，而 ICC 線性傳遞函數將 1.0 讀作 1 cd/m²。預設會縮放檔案，使其 1.0 落在描述檔的 HDR 參考白上。</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — 文件 1.0 = 参考白</v>
+        <v>输入缩放</v>
       </c>
       <c r="C533" t="str">
-        <v>×{w} — 檔案 1.0 = 參考白</v>
+        <v>輸入縮放</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>无 — 文件 1.0 = 1 cd/m²</v>
+        <v>×{w} — 文件 1.0 = 参考白</v>
       </c>
       <c r="C534" t="str">
-        <v>無 — 檔案 1.0 = 1 cd/m²</v>
+        <v>×{w} — 檔案 1.0 = 參考白</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>目标余量</v>
+        <v>无 — 文件 1.0 = 1 cd/m²</v>
       </c>
       <c r="C535" t="str">
-        <v>目標餘量</v>
+        <v>無 — 檔案 1.0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>参考白的 {r} 倍（{n} 档）</v>
+        <v>目标余量</v>
       </c>
       <c r="C536" t="str">
-        <v>參考白的 {r} 倍（{n} 檔）</v>
+        <v>目標餘量</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>色调映射</v>
+        <v>参考白的 {r} 倍（{n} 档）</v>
       </c>
       <c r="C537" t="str">
-        <v>色調映射</v>
+        <v>參考白的 {r} 倍（{n} 檔）</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>自动（第 8.10.3 条排序）</v>
+        <v>色调映射</v>
       </c>
       <c r="C538" t="str">
-        <v>自動（第 8.10.3 條排序）</v>
+        <v>色調映射</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>增益曲线（HAGC）</v>
+        <v>自动（第 8.10.3 条排序）</v>
       </c>
       <c r="C539" t="str">
-        <v>增益曲線（HAGC）</v>
+        <v>自動（第 8.10.3 條排序）</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>预烘焙的 SDR 回退（AToB0）</v>
+        <v>增益曲线（HAGC）</v>
       </c>
       <c r="C540" t="str">
-        <v>預先烘焙的 SDR 備援（AToB0）</v>
+        <v>增益曲線（HAGC）</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>关闭——与修订前的 CMM 相同</v>
+        <v>预烘焙的 SDR 回退（AToB0）</v>
       </c>
       <c r="C541" t="str">
-        <v>關閉——與修訂前的 CMM 相同</v>
+        <v>預先烘焙的 SDR 備援（AToB0）</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>正在应用配置文件…</v>
+        <v>关闭——与修订前的 CMM 相同</v>
       </c>
       <c r="C542" t="str">
-        <v>正在套用描述檔…</v>
+        <v>關閉——與修訂前的 CMM 相同</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
+        <v>正在应用配置文件…</v>
       </c>
       <c r="C543" t="str">
-        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
+        <v>正在套用描述檔…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>指定配置文件需要 3 通道 RGB 图像。</v>
+        <v>{format} 存储的是线性光，因此需要传递函数为 Linear（8）的配置文件。</v>
       </c>
       <c r="C544" t="str">
-        <v>指定描述檔需要 3 通道 RGB 影像。</v>
+        <v>{format} 儲存的是線性光，因此需要傳遞函數為 Linear（8）的描述檔。</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>要解释其数值，请在上方指定配置文件。</v>
+        <v>指定配置文件需要 3 通道 RGB 图像。</v>
       </c>
       <c r="C545" t="str">
-        <v>若要解讀其數值，請在上方指定描述檔。</v>
+        <v>指定描述檔需要 3 通道 RGB 影像。</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>HDR 配置文件</v>
+        <v>要解释其数值，请在上方指定配置文件。</v>
       </c>
       <c r="C546" t="str">
-        <v>HDR 描述檔</v>
+        <v>若要解讀其數值，請在上方指定描述檔。</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>线性传递函数</v>
+        <v>HDR 配置文件</v>
       </c>
       <c r="C547" t="str">
-        <v>線性傳遞函數</v>
+        <v>HDR 描述檔</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>非线性传递函数（PQ、HLG）</v>
+        <v>线性传递函数</v>
       </c>
       <c r="C548" t="str">
-        <v>非線性傳遞函數（PQ、HLG）</v>
+        <v>線性傳遞函數</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>HDR 配置文件——线性传递函数</v>
+        <v>非线性传递函数（PQ、HLG）</v>
       </c>
       <c r="C549" t="str">
-        <v>HDR 描述檔——線性傳遞函數</v>
+        <v>非線性傳遞函數（PQ、HLG）</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR 配置文件——PQ / HLG 传递函数</v>
+        <v>HDR 配置文件——线性传递函数</v>
       </c>
       <c r="C550" t="str">
-        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
+        <v>HDR 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
+        <v>HDR 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C551" t="str">
-        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
+        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
+        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
       </c>
       <c r="C552" t="str">
-        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
+        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
+        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C553" t="str">
-        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
+        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
       </c>
       <c r="C554" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>显示余量</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
       </c>
       <c r="C555" t="str">
-        <v>顯示餘量</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>显示余量</v>
       </c>
       <c r="C556" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>基准</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C557" t="str">
-        <v>基準</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>通过色彩引擎预览</v>
+        <v>基准</v>
       </c>
       <c r="C558" t="str">
-        <v>透過色彩引擎預覽</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>原始效果（基线 {h} 档，无增益）</v>
+        <v>通过色彩引擎预览</v>
       </c>
       <c r="C559" t="str">
-        <v>原始效果（基準 {h} 檔，無增益）</v>
+        <v>透過色彩引擎預覽</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>针对 {h} 档色调映射</v>
+        <v>原始效果（基线 {h} 档，无增益）</v>
       </c>
       <c r="C560" t="str">
-        <v>針對 {h} 檔色調對應</v>
+        <v>原始效果（基準 {h} 檔，無增益）</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
+        <v>针对 {h} 档色调映射</v>
       </c>
       <c r="C561" t="str">
-        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
+        <v>針對 {h} 檔色調對應</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>参考白</v>
+        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
       </c>
       <c r="C562" t="str">
-        <v>參考白</v>
+        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>显示器峰值</v>
+        <v>参考白</v>
       </c>
       <c r="C563" t="str">
-        <v>顯示器峰值</v>
+        <v>參考白</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>预览不可用：{why}</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C564" t="str">
-        <v>無法預覽：{why}</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
+        <v>预览不可用：{why}</v>
       </c>
       <c r="C565" t="str">
-        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
+        <v>無法預覽：{why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>所有余量下的增益</v>
+        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
       </c>
       <c r="C566" t="str">
-        <v>所有餘裕下的增益</v>
+        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
+        <v>所有余量下的增益</v>
       </c>
       <c r="C567" t="str">
-        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
+        <v>所有餘裕下的增益</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>输入（相对 HDR 参考白的档数）</v>
+        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
       </c>
       <c r="C568" t="str">
-        <v>輸入（相對 HDR 參考白的檔數）</v>
+        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>显示余量（档）</v>
+        <v>输入（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C569" t="str">
-        <v>顯示餘裕（檔）</v>
+        <v>輸入（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>增益（档）</v>
+        <v>显示余量（档）</v>
       </c>
       <c r="C570" t="str">
-        <v>增益（檔）</v>
+        <v>顯示餘裕（檔）</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>标签中的曲线</v>
+        <v>增益（档）</v>
       </c>
       <c r="C571" t="str">
-        <v>標籤中的曲線</v>
+        <v>增益（檔）</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>基线</v>
+        <v>标签中的曲线</v>
       </c>
       <c r="C572" t="str">
-        <v>基準</v>
+        <v>標籤中的曲線</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>滑块</v>
+        <v>基线</v>
       </c>
       <c r="C573" t="str">
-        <v>滑桿</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>输入 = 显示器峰值</v>
+        <v>滑块</v>
       </c>
       <c r="C574" t="str">
-        <v>輸入 = 顯示器峰值</v>
+        <v>滑桿</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>按余量的灰色色调曲线</v>
+        <v>输入 = 显示器峰值</v>
       </c>
       <c r="C575" t="str">
-        <v>依餘裕的灰色色調曲線</v>
+        <v>輸入 = 顯示器峰值</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
+        <v>按余量的灰色色调曲线</v>
       </c>
       <c r="C576" t="str">
-        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
+        <v>依餘裕的灰色色調曲線</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>输出（相对 HDR 参考白的档数）</v>
+        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
       </c>
       <c r="C577" t="str">
-        <v>輸出（相對 HDR 參考白的檔數）</v>
+        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} 档</v>
+        <v>输出（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C578" t="str">
-        <v>{h} 檔</v>
+        <v>輸出（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} 档（基线）</v>
+        <v>{h} 档</v>
       </c>
       <c r="C579" t="str">
-        <v>{h} 檔（基準）</v>
+        <v>{h} 檔</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} 档（滑块）</v>
+        <v>{h} 档（基线）</v>
       </c>
       <c r="C580" t="str">
-        <v>{h} 檔（滑桿）</v>
+        <v>{h} 檔（基準）</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>{h} 档（滑块）</v>
       </c>
       <c r="C581" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>{h} 檔（滑桿）</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C582" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C583" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C584" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C585" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C586" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C587" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C588" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C589" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>此余量下应用的增益</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C590" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C591" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>增益（log2 档）</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C592" t="str">
-        <v>增益（log2 檔）</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C593" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C594" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C595" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>不变</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C596" t="str">
-        <v>不變</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>不变</v>
       </c>
       <c r="C597" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>{h} 档处的输出</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C598" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C599" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>识别显示器</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C600" t="str">
-        <v>識別顯示器</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C601" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C602" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C603" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C604" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>无法识别显示器。</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C605" t="str">
-        <v>無法識別顯示器。</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>显示事件</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C606" t="str">
-        <v>顯示事件</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>显示事件</v>
       </c>
       <c r="C607" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>色度基色</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C608" t="str">
-        <v>色度基色</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>传递特性</v>
+        <v>色度基色</v>
       </c>
       <c r="C609" t="str">
-        <v>轉換特性</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>矩阵系数</v>
+        <v>传递特性</v>
       </c>
       <c r="C610" t="str">
-        <v>矩陣係數</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>视频全范围标志</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C611" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>全范围</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C612" t="str">
-        <v>全範圍</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>有限范围</v>
+        <v>全范围</v>
       </c>
       <c r="C613" t="str">
-        <v>有限範圍</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>有限范围</v>
       </c>
       <c r="C614" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C615" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C616" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>报告</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C617" t="str">
-        <v>報告</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C618" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C619" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C620" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C621" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C622" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C623" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C624" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C625" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C626" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C627" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C628" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C629" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C630" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C631" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C632" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C633" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C634" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C635" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C636" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C637" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C638" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C639" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C640" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C641" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C642" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C643" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C644" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C645" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C646" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C647" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C648" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C649" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C650" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C651" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C652" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C653" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C654" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C655" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C656" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C657" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C658" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C659" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C660" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C661" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C662" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C663" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C664" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C665" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C666" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C667" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C668" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C669" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C670" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C671" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C672" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C673" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C674" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C675" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C676" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C677" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C678" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C679" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C680" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C681" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C682" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C683" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C684" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C685" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C686" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C687" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C688" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C689" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C690" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C691" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C692" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C693" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C694" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C695" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C696" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C697" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C698" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C699" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C700" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C701" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C702" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C703" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C704" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C705" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C705" t="str">
+      <c r="C706" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C466"/>
+  <dimension ref="A1:C467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1495,4053 +1495,4064 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>按名称排序</v>
+        <v>点按选择，然后点按标签页发送。</v>
       </c>
       <c r="C100" t="str">
-        <v>依名稱排序</v>
+        <v>點選以選取，然後點選分頁以傳送。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>按名称排序</v>
       </c>
       <c r="C101" t="str">
-        <v>A–Z</v>
+        <v>依名稱排序</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>从 .cube 新建配置文件</v>
+        <v>A–Z</v>
       </c>
       <c r="C102" t="str">
-        <v>從 .cube 新建設定檔</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并打开；点击“保存 ICC 配置文件”后才会下载。</v>
+        <v>从 .cube 新建配置文件</v>
       </c>
       <c r="C103" t="str">
-        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並開啟；按下「儲存 ICC 設定檔」後才會下載。</v>
+        <v>從 .cube 新建設定檔</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>选择 .cube 文件</v>
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并打开；点击“保存 ICC 配置文件”后才会下载。</v>
       </c>
       <c r="C104" t="str">
-        <v>選擇 .cube 檔案</v>
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並開啟；按下「儲存 ICC 設定檔」後才會下載。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>选择 .cube 文件</v>
+      </c>
+      <c r="C105" t="str">
+        <v>選擇 .cube 檔案</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>或拖放到此处，或在下方粘贴</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C106" t="str">
         <v>或拖放到此處，或在下方貼上</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C106" t="str" xml:space="preserve">
+      <c r="C107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>取消</v>
-      </c>
-      <c r="C107" t="str">
-        <v>取消</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>创建 DeviceLink</v>
+        <v>取消</v>
       </c>
       <c r="C108" t="str">
-        <v>建立 DeviceLink</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>正在创建…</v>
+        <v>创建 DeviceLink</v>
       </c>
       <c r="C109" t="str">
-        <v>正在建立…</v>
+        <v>建立 DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>无法读取该文件。</v>
+        <v>正在创建…</v>
       </c>
       <c r="C110" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>配置文件</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C111" t="str">
-        <v>設定檔</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>比较</v>
+        <v>配置文件</v>
       </c>
       <c r="C112" t="str">
-        <v>比較</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>链接</v>
+        <v>比较</v>
       </c>
       <c r="C113" t="str">
-        <v>連結</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>光谱</v>
+        <v>链接</v>
       </c>
       <c r="C114" t="str">
-        <v>光譜</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>将配置文件从池中拖到此选项卡</v>
+        <v>光谱</v>
       </c>
       <c r="C115" t="str">
-        <v>將設定檔從集區拖到此分頁</v>
+        <v>光譜</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>移除</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C116" t="str">
-        <v>移除</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>未选择配置文件</v>
+        <v>移除</v>
       </c>
       <c r="C117" t="str">
-        <v>未選擇設定檔</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C118" t="str">
-        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>暂无可比较的内容</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C119" t="str">
-        <v>尚無可比較的內容</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C120" t="str">
-        <v>將一個或多個設定檔拖到「比較」分頁。</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>色域比较</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C121" t="str">
-        <v>色域比較</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
+        <v>色域比较</v>
       </c>
       <c r="C122" t="str">
-        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>渲染意图</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C123" t="str">
-        <v>轉換意圖</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>外壳</v>
+        <v>渲染意图</v>
       </c>
       <c r="C124" t="str">
-        <v>外殼</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>线框</v>
+        <v>外壳</v>
       </c>
       <c r="C125" t="str">
-        <v>線框</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>轴编号</v>
+        <v>线框</v>
       </c>
       <c r="C126" t="str">
-        <v>軸編號</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>不透明度</v>
+        <v>轴编号</v>
       </c>
       <c r="C127" t="str">
-        <v>不透明度</v>
+        <v>軸編號</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>颜色</v>
+        <v>不透明度</v>
       </c>
       <c r="C128" t="str">
-        <v>色彩</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>纯色</v>
+        <v>颜色</v>
       </c>
       <c r="C129" t="str">
-        <v>純色</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>按数值</v>
+        <v>纯色</v>
       </c>
       <c r="C130" t="str">
-        <v>依數值</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>按色相</v>
+        <v>按数值</v>
       </c>
       <c r="C131" t="str">
-        <v>依色相</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>旋转</v>
+        <v>按色相</v>
       </c>
       <c r="C132" t="str">
-        <v>旋轉</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>转盘</v>
+        <v>旋转</v>
       </c>
       <c r="C133" t="str">
-        <v>轉盤</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>轨道</v>
+        <v>转盘</v>
       </c>
       <c r="C134" t="str">
-        <v>軌道</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>拖动速度</v>
+        <v>轨道</v>
       </c>
       <c r="C135" t="str">
-        <v>拖曳速度</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>翻滚</v>
+        <v>拖动速度</v>
       </c>
       <c r="C136" t="str">
-        <v>翻滾</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>翻滚速度</v>
+        <v>翻滚</v>
       </c>
       <c r="C137" t="str">
-        <v>翻滾速度</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>正在构建色域…</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C138" t="str">
-        <v>正在建構色域…</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>无色域</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C139" t="str">
-        <v>無色域</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>显示/隐藏</v>
+        <v>无色域</v>
       </c>
       <c r="C140" t="str">
-        <v>顯示/隱藏</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>3D 色域外壳</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C141" t="str">
-        <v>3D 色域外殼</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>2D 色域切片</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C142" t="str">
-        <v>2D 色域切片</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>平面</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C143" t="str">
-        <v>平面</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
       <c r="C144" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="C145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="C146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
+        <v>b*</v>
       </c>
       <c r="C147" t="str">
-        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>链接</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C148" t="str">
-        <v>連結</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
+        <v>链接</v>
       </c>
       <c r="C149" t="str">
-        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C150" t="str">
-        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>V4 显示器生成器</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C151" t="str">
-        <v>V4 顯示器產生器</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C152" t="str">
-        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 RGB 显示器</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C153" t="str">
-        <v>V5 RGB 顯示器</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>拖入显示器配置文件</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C154" t="str">
-        <v>拖入顯示器設定檔</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>V5 观察者 (PCC)</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C155" t="str">
-        <v>V5 觀察者 (PCC)</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>拖入观察者配置文件</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C156" t="str">
-        <v>拖入觀察者設定檔</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C157" t="str">
-        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>创建 V4 显示器配置文件</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C158" t="str">
-        <v>建立 V4 顯示器設定檔</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>配置文件名称</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C159" t="str">
-        <v>設定檔名稱</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>创建</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C160" t="str">
-        <v>建立</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>正在创建…</v>
+        <v>创建</v>
       </c>
       <c r="C161" t="str">
-        <v>正在建立…</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
+        <v>正在创建…</v>
       </c>
       <c r="C162" t="str">
-        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>链接流水线</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C163" t="str">
-        <v>連結管線</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
+        <v>链接流水线</v>
       </c>
       <c r="C164" t="str">
-        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
+        <v>連結管線</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>完成</v>
+        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
       </c>
       <c r="C165" t="str">
-        <v>完成</v>
+        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
+        <v>完成</v>
       </c>
       <c r="C166" t="str">
-        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>正在检查图像…</v>
+        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
       </c>
       <c r="C167" t="str">
-        <v>正在檢查影像…</v>
+        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在检查图像…</v>
       </c>
       <c r="C168" t="str">
-        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在檢查影像…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
+        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C169" t="str">
-        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
+        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>转换图像</v>
+        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
       </c>
       <c r="C170" t="str">
-        <v>轉換影像</v>
+        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>正在转换…</v>
+        <v>转换图像</v>
       </c>
       <c r="C171" t="str">
-        <v>正在轉換…</v>
+        <v>轉換影像</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>拖放配置文件以开始链条</v>
+        <v>正在转换…</v>
       </c>
       <c r="C172" t="str">
-        <v>拖放描述檔以開始鏈條</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>已移除</v>
+        <v>拖放配置文件以开始链条</v>
       </c>
       <c r="C173" t="str">
-        <v>已移除</v>
+        <v>拖放描述檔以開始鏈條</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>前移</v>
+        <v>已移除</v>
       </c>
       <c r="C174" t="str">
-        <v>前移</v>
+        <v>已移除</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>后移</v>
+        <v>前移</v>
       </c>
       <c r="C175" t="str">
-        <v>後移</v>
+        <v>前移</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>上移</v>
+        <v>后移</v>
       </c>
       <c r="C176" t="str">
-        <v>上移</v>
+        <v>後移</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>下移</v>
+        <v>上移</v>
       </c>
       <c r="C177" t="str">
-        <v>下移</v>
+        <v>上移</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>渲染意图（全部）</v>
+        <v>下移</v>
       </c>
       <c r="C178" t="str">
-        <v>演算意圖（全部）</v>
+        <v>下移</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>此转换的渲染意图</v>
+        <v>渲染意图（全部）</v>
       </c>
       <c r="C179" t="str">
-        <v>此轉換的演算意圖</v>
+        <v>演算意圖（全部）</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>各转换使用了不同的渲染意图</v>
+        <v>此转换的渲染意图</v>
       </c>
       <c r="C180" t="str">
-        <v>各轉換使用了不同的演算意圖</v>
+        <v>此轉換的演算意圖</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
+        <v>各转换使用了不同的渲染意图</v>
       </c>
       <c r="C181" t="str">
-        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
+        <v>各轉換使用了不同的演算意圖</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
+        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
       </c>
       <c r="C182" t="str">
-        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
+        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>链条</v>
+        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
       </c>
       <c r="C183" t="str">
-        <v>鏈條</v>
+        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>无法分析该链条。</v>
+        <v>链条</v>
       </c>
       <c r="C184" t="str">
-        <v>無法分析該鏈條。</v>
+        <v>鏈條</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>正在检查链条…</v>
+        <v>无法分析该链条。</v>
       </c>
       <c r="C185" t="str">
-        <v>正在檢查鏈條…</v>
+        <v>無法分析該鏈條。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>链条未能衔接（{detail}）。</v>
+        <v>正在检查链条…</v>
       </c>
       <c r="C186" t="str">
-        <v>鏈條未能銜接（{detail}）。</v>
+        <v>正在檢查鏈條…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
+        <v>链条未能衔接（{detail}）。</v>
       </c>
       <c r="C187" t="str">
-        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
+        <v>鏈條未能銜接（{detail}）。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>请先修复链条，再处理图像</v>
+        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
       </c>
       <c r="C188" t="str">
-        <v>請先修正鏈條，再處理影像</v>
+        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>清除</v>
+        <v>请先修复链条，再处理图像</v>
       </c>
       <c r="C189" t="str">
-        <v>清除</v>
+        <v>請先修正鏈條，再處理影像</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>生成 DeviceLink</v>
+        <v>清除</v>
       </c>
       <c r="C190" t="str">
-        <v>產生 DeviceLink</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>DeviceLink 名称</v>
+        <v>生成 DeviceLink</v>
       </c>
       <c r="C191" t="str">
-        <v>DeviceLink 名稱</v>
+        <v>產生 DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>正在生成…</v>
+        <v>DeviceLink 名称</v>
       </c>
       <c r="C192" t="str">
-        <v>正在產生…</v>
+        <v>DeviceLink 名稱</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>已创建“{name}”——已添加到池和此标签页。</v>
+        <v>正在生成…</v>
       </c>
       <c r="C193" t="str">
-        <v>已建立「{name}」——已加入集區與此分頁。</v>
+        <v>正在產生…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
+        <v>已创建“{name}”——已添加到池和此标签页。</v>
       </c>
       <c r="C194" t="str">
-        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
+        <v>已建立「{name}」——已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>构建链条以处理图像</v>
+        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
       </c>
       <c r="C195" t="str">
-        <v>建立鏈條以處理影像</v>
+        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>此链条的首尾并非图像色彩空间</v>
+        <v>构建链条以处理图像</v>
       </c>
       <c r="C196" t="str">
-        <v>此鏈條的首尾並非影像色彩空間</v>
+        <v>建立鏈條以處理影像</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>已保存转换后的图像。</v>
+        <v>此链条的首尾并非图像色彩空间</v>
       </c>
       <c r="C197" t="str">
-        <v>已儲存轉換後的影像。</v>
+        <v>此鏈條的首尾並非影像色彩空間</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
+        <v>已保存转换后的图像。</v>
       </c>
       <c r="C198" t="str">
-        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
+        <v>已儲存轉換後的影像。</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>无法读取该文件。</v>
+        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
       </c>
       <c r="C199" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>数据文件过大。</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C200" t="str">
-        <v>資料檔案過大。</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>转换数据</v>
+        <v>数据文件过大。</v>
       </c>
       <c r="C201" t="str">
-        <v>轉換資料</v>
+        <v>資料檔案過大。</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>正在转换…</v>
+        <v>转换数据</v>
       </c>
       <c r="C202" t="str">
-        <v>正在轉換…</v>
+        <v>轉換資料</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>偏好</v>
+        <v>正在转换…</v>
       </c>
       <c r="C203" t="str">
-        <v>偏好</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>观察者</v>
+        <v>偏好</v>
       </c>
       <c r="C204" t="str">
-        <v>觀察者</v>
+        <v>偏好</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>光源</v>
+        <v>观察者</v>
       </c>
       <c r="C205" t="str">
-        <v>光源</v>
+        <v>觀察者</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>条件</v>
+        <v>光源</v>
       </c>
       <c r="C206" t="str">
-        <v>條件</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>过滤 {n} 个重复项</v>
+        <v>条件</v>
       </c>
       <c r="C207" t="str">
-        <v>篩選 {n} 個重複項</v>
+        <v>條件</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>中位数</v>
+        <v>过滤 {n} 个重复项</v>
       </c>
       <c r="C208" t="str">
-        <v>中位數</v>
+        <v>篩選 {n} 個重複項</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>平均值</v>
+        <v>中位数</v>
       </c>
       <c r="C209" t="str">
-        <v>平均值</v>
+        <v>中位數</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>色块</v>
+        <v>平均值</v>
       </c>
       <c r="C210" t="str">
-        <v>色塊</v>
+        <v>平均值</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} 个重复项</v>
+        <v>色块</v>
       </c>
       <c r="C211" t="str">
-        <v>{n} 個重複項</v>
+        <v>色塊</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>转换结果</v>
+        <v>{n} 个重复项</v>
       </c>
       <c r="C212" t="str">
-        <v>轉換結果</v>
+        <v>{n} 個重複項</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} 个色块</v>
+        <v>转换结果</v>
       </c>
       <c r="C213" t="str">
-        <v>{src} → {dst} · {n} 個色塊</v>
+        <v>轉換結果</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
+        <v>{src} → {dst} · {n} 个色块</v>
       </c>
       <c r="C214" t="str">
-        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
+        <v>{src} → {dst} · {n} 個色塊</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>另存为</v>
+        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
       </c>
       <c r="C215" t="str">
-        <v>另存新檔</v>
+        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>保存</v>
+        <v>另存为</v>
       </c>
       <c r="C216" t="str">
-        <v>儲存</v>
+        <v>另存新檔</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>反向转换</v>
+        <v>保存</v>
       </c>
       <c r="C217" t="str">
-        <v>反向轉換</v>
+        <v>儲存</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>正在反向计算…</v>
+        <v>反向转换</v>
       </c>
       <c r="C218" t="str">
-        <v>正在反向計算…</v>
+        <v>反向轉換</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>反转</v>
+        <v>正在反向计算…</v>
       </c>
       <c r="C219" t="str">
-        <v>反轉</v>
+        <v>正在反向計算…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>最后阶段</v>
+        <v>反转</v>
       </c>
       <c r="C220" t="str">
-        <v>最後階段</v>
+        <v>反轉</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>第一阶段</v>
+        <v>最后阶段</v>
       </c>
       <c r="C221" t="str">
-        <v>第一階段</v>
+        <v>最後階段</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>输入数据为 {in} → 搜索 {out}</v>
+        <v>第一阶段</v>
       </c>
       <c r="C222" t="str">
-        <v>輸入資料為 {in} → 搜尋 {out}</v>
+        <v>第一階段</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>反转需要 2–3 个配置文件组成的链条</v>
+        <v>输入数据为 {in} → 搜索 {out}</v>
       </c>
       <c r="C223" t="str">
-        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
+        <v>輸入資料為 {in} → 搜尋 {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
+        <v>反转需要 2–3 个配置文件组成的链条</v>
       </c>
       <c r="C224" t="str">
-        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
+        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>ΔE 代价</v>
+        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
       </c>
       <c r="C225" t="str">
-        <v>ΔE 代價</v>
+        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>此图像嵌入了 ICC 配置文件。</v>
+        <v>ΔE 代价</v>
       </c>
       <c r="C226" t="str">
-        <v>此影像內嵌了 ICC 描述檔。</v>
+        <v>ΔE 代價</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>提取并添加到链条</v>
+        <v>此图像嵌入了 ICC 配置文件。</v>
       </c>
       <c r="C227" t="str">
-        <v>擷取並加入鏈條</v>
+        <v>此影像內嵌了 ICC 描述檔。</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>正在提取…</v>
+        <v>提取并添加到链条</v>
       </c>
       <c r="C228" t="str">
-        <v>正在擷取…</v>
+        <v>擷取並加入鏈條</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>忽略</v>
+        <v>正在提取…</v>
       </c>
       <c r="C229" t="str">
-        <v>忽略</v>
+        <v>正在擷取…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
+        <v>忽略</v>
       </c>
       <c r="C230" t="str">
-        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
+        <v>忽略</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>图像输出选项</v>
+        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
       </c>
       <c r="C231" t="str">
-        <v>影像輸出選項</v>
+        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>编码</v>
+        <v>图像输出选项</v>
       </c>
       <c r="C232" t="str">
-        <v>編碼</v>
+        <v>影像輸出選項</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>与源相同</v>
+        <v>编码</v>
       </c>
       <c r="C233" t="str">
-        <v>與來源相同</v>
+        <v>編碼</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 位</v>
+        <v>与源相同</v>
       </c>
       <c r="C234" t="str">
-        <v>8 位元</v>
+        <v>與來源相同</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 位</v>
+        <v>8 位</v>
       </c>
       <c r="C235" t="str">
-        <v>16 位元</v>
+        <v>8 位元</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>浮点（32 位）</v>
+        <v>16 位</v>
       </c>
       <c r="C236" t="str">
-        <v>浮點（32 位元）</v>
+        <v>16 位元</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>压缩</v>
+        <v>浮点（32 位）</v>
       </c>
       <c r="C237" t="str">
-        <v>壓縮</v>
+        <v>浮點（32 位元）</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>无</v>
+        <v>压缩</v>
       </c>
       <c r="C238" t="str">
-        <v>無</v>
+        <v>壓縮</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>平面格式</v>
+        <v>无</v>
       </c>
       <c r="C239" t="str">
-        <v>平面格式</v>
+        <v>無</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>交错</v>
+        <v>平面格式</v>
       </c>
       <c r="C240" t="str">
-        <v>交錯</v>
+        <v>平面格式</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>分离</v>
+        <v>交错</v>
       </c>
       <c r="C241" t="str">
-        <v>分離</v>
+        <v>交錯</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>CMM 插值</v>
+        <v>分离</v>
       </c>
       <c r="C242" t="str">
-        <v>CMM 內插</v>
+        <v>分離</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>四面体</v>
+        <v>CMM 插值</v>
       </c>
       <c r="C243" t="str">
-        <v>四面體</v>
+        <v>CMM 內插</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>线性</v>
+        <v>四面体</v>
       </c>
       <c r="C244" t="str">
-        <v>線性</v>
+        <v>四面體</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>嵌入 ICC</v>
+        <v>线性</v>
       </c>
       <c r="C245" t="str">
-        <v>內嵌 ICC</v>
+        <v>線性</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
+        <v>嵌入 ICC</v>
       </c>
       <c r="C246" t="str">
-        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
+        <v>內嵌 ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>组装光谱 TIFF</v>
+        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
       </c>
       <c r="C247" t="str">
-        <v>組裝光譜 TIFF</v>
+        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
+        <v>组装光谱 TIFF</v>
       </c>
       <c r="C248" t="str">
-        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
+        <v>組裝光譜 TIFF</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>将光谱图像拖放到此处（或点击选择）</v>
+        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
       </c>
       <c r="C249" t="str">
-        <v>將光譜影像拖放到此處（或點擊選擇）</v>
+        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>通道</v>
+        <v>将光谱图像拖放到此处（或点击选择）</v>
       </c>
       <c r="C250" t="str">
-        <v>通道</v>
+        <v>將光譜影像拖放到此處（或點擊選擇）</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>组装并保存</v>
+        <v>通道</v>
       </c>
       <c r="C251" t="str">
-        <v>組裝並儲存</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>正在组装…</v>
+        <v>组装并保存</v>
       </c>
       <c r="C252" t="str">
-        <v>正在組裝…</v>
+        <v>組裝並儲存</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>已组装 {n} 个通道。</v>
+        <v>正在组装…</v>
       </c>
       <c r="C253" t="str">
-        <v>已組裝 {n} 個通道。</v>
+        <v>正在組裝…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
+        <v>已组装 {n} 个通道。</v>
       </c>
       <c r="C254" t="str">
-        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
+        <v>已組裝 {n} 個通道。</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>取消</v>
+        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C255" t="str">
-        <v>取消</v>
+        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>有 {n} 个文件未加载</v>
+        <v>取消</v>
       </c>
       <c r="C256" t="str">
-        <v>有 {n} 個檔案未載入</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C257" t="str">
-        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>确定</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C258" t="str">
-        <v>確定</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>确定</v>
       </c>
       <c r="C259" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>或</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C260" t="str">
-        <v>或</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>选择文件</v>
+        <v>或</v>
       </c>
       <c r="C261" t="str">
-        <v>選擇檔案</v>
+        <v>或</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>选择文件</v>
       </c>
       <c r="C262" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>标头</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C263" t="str">
-        <v>標頭</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>标签</v>
+        <v>标头</v>
       </c>
       <c r="C264" t="str">
-        <v>標籤</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>验证</v>
+        <v>标签</v>
       </c>
       <c r="C265" t="str">
-        <v>驗證</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>分析</v>
+        <v>验证</v>
       </c>
       <c r="C266" t="str">
-        <v>分析</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>中性轴墨量</v>
+        <v>分析</v>
       </c>
       <c r="C267" t="str">
-        <v>中性軸墨量</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C268" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C269" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C270" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>渲染意图</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C271" t="str">
-        <v>轉換意圖</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% 墨量</v>
+        <v>渲染意图</v>
       </c>
       <c r="C272" t="str">
-        <v>% 墨量</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* 输出（色调）</v>
+        <v>% 墨量</v>
       </c>
       <c r="C273" t="str">
-        <v>L* 輸出（色調）</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 输出（色调）</v>
       </c>
       <c r="C274" t="str">
-        <v>Δa*b*</v>
+        <v>L* 輸出（色調）</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>极值比色</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C275" t="str">
-        <v>極值比色</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
+        <v>极值比色</v>
       </c>
       <c r="C276" t="str">
-        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
+        <v>極值比色</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
+        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
       </c>
       <c r="C277" t="str">
-        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
+        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>相对</v>
+        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
       </c>
       <c r="C278" t="str">
-        <v>相對</v>
+        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>绝对</v>
+        <v>相对</v>
       </c>
       <c r="C279" t="str">
-        <v>絕對</v>
+        <v>相對</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>白点</v>
+        <v>绝对</v>
       </c>
       <c r="C280" t="str">
-        <v>白點</v>
+        <v>絕對</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>黑点</v>
+        <v>白点</v>
       </c>
       <c r="C281" t="str">
-        <v>黑點</v>
+        <v>白點</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>黑点处的墨量</v>
+        <v>黑点</v>
       </c>
       <c r="C282" t="str">
-        <v>黑點處的墨量</v>
+        <v>黑點</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>黑点处的墨量</v>
       </c>
       <c r="C283" t="str">
-        <v>TAC</v>
+        <v>黑點處的墨量</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
+        <v>TAC</v>
       </c>
       <c r="C284" t="str">
-        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
+        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
       </c>
       <c r="C285" t="str">
-        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
+        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>实地与最大彩度</v>
+        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
       </c>
       <c r="C286" t="str">
-        <v>實地與最大彩度</v>
+        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
+        <v>实地与最大彩度</v>
       </c>
       <c r="C287" t="str">
-        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
+        <v>實地與最大彩度</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>色相</v>
+        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C288" t="str">
-        <v>色相</v>
+        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>实地</v>
+        <v>色相</v>
       </c>
       <c r="C289" t="str">
-        <v>實地</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>最大 C*</v>
+        <v>实地</v>
       </c>
       <c r="C290" t="str">
-        <v>最大 C*</v>
+        <v>實地</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>对应墨量</v>
+        <v>最大 C*</v>
       </c>
       <c r="C291" t="str">
-        <v>對應墨量</v>
+        <v>最大 C*</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
+        <v>对应墨量</v>
       </c>
       <c r="C292" t="str">
-        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
+        <v>對應墨量</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>暗调中的用墨</v>
+        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C293" t="str">
-        <v>暗部的用墨</v>
+        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
+        <v>暗调中的用墨</v>
       </c>
       <c r="C294" t="str">
-        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
+        <v>暗部的用墨</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
+        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
       </c>
       <c r="C295" t="str">
-        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
+        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>恒定 L* 平面</v>
+        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C296" t="str">
-        <v>固定 L* 平面</v>
+        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>黑点补偿自</v>
+        <v>恒定 L* 平面</v>
       </c>
       <c r="C297" t="str">
-        <v>黑點補償自</v>
+        <v>固定 L* 平面</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>沿路径位置</v>
+        <v>黑点补偿自</v>
       </c>
       <c r="C298" t="str">
-        <v>沿路徑位置</v>
+        <v>黑點補償自</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>路径</v>
+        <v>沿路径位置</v>
       </c>
       <c r="C299" t="str">
-        <v>路徑</v>
+        <v>沿路徑位置</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>经中性轴的原色墨路</v>
+        <v>路径</v>
       </c>
       <c r="C300" t="str">
-        <v>經中性軸的原色墨路</v>
+        <v>路徑</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>色域内的三条路径——青→红、品红→绿、黄→蓝——每条都在其两端明度的中点经过中性轴，通过所选的 B2A 表。每个采样点都在色域内，因此与暗调路径不同，某个着色剂的任何突变或反转都是 CLUT 平滑性缺陷，而非色域映射伪影。</v>
+        <v>经中性轴的原色墨路</v>
       </c>
       <c r="C301" t="str">
-        <v>色域內的三條路徑——青→紅、洋紅→綠、黃→藍——每條都在其兩端明度的中點經過中性軸，通過所選的 B2A 表。每個取樣點都在色域內，因此與暗調路徑不同，某個著色劑的任何突變或反轉都是 CLUT 平滑性缺陷，而非色域映射假影。</v>
+        <v>經中性軸的原色墨路</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>原色墨路仅适用于输出（打印机）特性文件。</v>
+        <v>色域内的三条路径——青→红、品红→绿、黄→蓝——每条都在其两端明度的中点经过中性轴，通过所选的 B2A 表。每个采样点都在色域内，因此与暗调路径不同，某个着色剂的任何突变或反转都是 CLUT 平滑性缺陷，而非色域映射伪影。</v>
       </c>
       <c r="C302" t="str">
-        <v>原色墨路僅適用於輸出（印表機）特性檔。</v>
+        <v>色域內的三條路徑——青→紅、洋紅→綠、黃→藍——每條都在其兩端明度的中點經過中性軸，通過所選的 B2A 表。每個取樣點都在色域內，因此與暗調路徑不同，某個著色劑的任何突變或反轉都是 CLUT 平滑性缺陷，而非色域映射假影。</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>沿路径的位置（中点为中性）</v>
+        <v>原色墨路仅适用于输出（打印机）特性文件。</v>
       </c>
       <c r="C303" t="str">
-        <v>沿路徑的位置（中點為中性）</v>
+        <v>原色墨路僅適用於輸出（印表機）特性檔。</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>已为此意图应用黑场补偿。</v>
+        <v>沿路径的位置（中点为中性）</v>
       </c>
       <c r="C304" t="str">
-        <v>已為此意圖套用黑場補償。</v>
+        <v>沿路徑的位置（中點為中性）</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>墨量统计</v>
+        <v>已为此意图应用黑场补偿。</v>
       </c>
       <c r="C305" t="str">
-        <v>墨量統計</v>
+        <v>已為此意圖套用黑場補償。</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>特性文件施加的每种着色剂的用量，以总量和占总量的比例表示——即分色的用墨特征。</v>
+        <v>墨量统计</v>
       </c>
       <c r="C306" t="str">
-        <v>特性檔施加的每種著色劑的用量，以總量和佔總量的比例表示——即分色的用墨特徵。</v>
+        <v>墨量統計</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>墨量统计仅适用于输出（打印机）特性文件。</v>
+        <v>特性文件施加的每种着色剂的用量，以总量和占总量的比例表示——即分色的用墨特征。</v>
       </c>
       <c r="C307" t="str">
-        <v>墨量統計僅適用於輸出（印表機）特性檔。</v>
+        <v>特性檔施加的每種著色劑的用量，以總量和佔總量的比例表示——即分色的用墨特徵。</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>中性轴</v>
+        <v>墨量统计仅适用于输出（打印机）特性文件。</v>
       </c>
       <c r="C308" t="str">
-        <v>中性軸</v>
+        <v>墨量統計僅適用於輸出（印表機）特性檔。</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>平均覆盖率</v>
+        <v>中性轴</v>
       </c>
       <c r="C309" t="str">
-        <v>平均覆蓋率</v>
+        <v>中性軸</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>墨量占比</v>
+        <v>平均覆盖率</v>
       </c>
       <c r="C310" t="str">
-        <v>墨量佔比</v>
+        <v>平均覆蓋率</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>墨量占比是中性构建的指纹——每种着色剂在施加总墨量中所占的比例，与采样数量无关。</v>
+        <v>墨量占比</v>
       </c>
       <c r="C311" t="str">
-        <v>墨量佔比是中性建構的指紋——每種著色劑在施加總墨量中所佔的比例，與取樣數量無關。</v>
+        <v>墨量佔比</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>色域内的点</v>
+        <v>墨量占比是中性构建的指纹——每种着色剂在施加总墨量中所占的比例，与采样数量无关。</v>
       </c>
       <c r="C312" t="str">
-        <v>色域內的點</v>
+        <v>墨量佔比是中性建構的指紋——每種著色劑在施加總墨量中所佔的比例，與取樣數量無關。</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>对色域内所有颜色的墨量统计需要 B2A 方向的色域边界，目前尚未构建——待完成。</v>
+        <v>色域内的点</v>
       </c>
       <c r="C313" t="str">
-        <v>對色域內所有顏色的墨量統計需要 B2A 方向的色域邊界，目前尚未建構——待完成。</v>
+        <v>色域內的點</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>没有可汇总的着色剂数据。</v>
+        <v>对色域内所有颜色的墨量统计需要 B2A 方向的色域边界，目前尚未构建——待完成。</v>
       </c>
       <c r="C314" t="str">
-        <v>沒有可彙總的著色劑資料。</v>
+        <v>對色域內所有顏色的墨量統計需要 B2A 方向的色域邊界，目前尚未建構——待完成。</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>在下方选择 B2A（PCS→设备）表，即可查看每种着色剂的灰度墨量覆盖图。</v>
+        <v>没有可汇总的着色剂数据。</v>
       </c>
       <c r="C315" t="str">
-        <v>在下方選擇 B2A（PCS→裝置）表，即可檢視每種著色劑的灰階墨量覆蓋圖。</v>
+        <v>沒有可彙總的著色劑資料。</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>每种着色剂在同一网格上的墨量覆盖（越暗表示墨量越多）。</v>
+        <v>在下方选择 B2A（PCS→设备）表，即可查看每种着色剂的灰度墨量覆盖图。</v>
       </c>
       <c r="C316" t="str">
-        <v>每種著色劑在同一網格上的墨量覆蓋（越暗表示墨量越多）。</v>
+        <v>在下方選擇 B2A（PCS→裝置）表，即可檢視每種著色劑的灰階墨量覆蓋圖。</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>青</v>
+        <v>每种着色剂在同一网格上的墨量覆盖（越暗表示墨量越多）。</v>
       </c>
       <c r="C317" t="str">
-        <v>青</v>
+        <v>每種著色劑在同一網格上的墨量覆蓋（越暗表示墨量越多）。</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>品红</v>
+        <v>青</v>
       </c>
       <c r="C318" t="str">
-        <v>洋紅</v>
+        <v>青</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>黄</v>
+        <v>品红</v>
       </c>
       <c r="C319" t="str">
-        <v>黃</v>
+        <v>洋紅</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>红</v>
+        <v>黄</v>
       </c>
       <c r="C320" t="str">
-        <v>紅</v>
+        <v>黃</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>绿</v>
+        <v>红</v>
       </c>
       <c r="C321" t="str">
-        <v>綠</v>
+        <v>紅</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>蓝</v>
+        <v>绿</v>
       </c>
       <c r="C322" t="str">
-        <v>藍</v>
+        <v>綠</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>黑</v>
+        <v>蓝</v>
       </c>
       <c r="C323" t="str">
-        <v>黑</v>
+        <v>藍</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>感知</v>
+        <v>黑</v>
       </c>
       <c r="C324" t="str">
-        <v>感知</v>
+        <v>黑</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>相对比色</v>
+        <v>感知</v>
       </c>
       <c r="C325" t="str">
-        <v>相對比色</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>饱和度</v>
+        <v>相对比色</v>
       </c>
       <c r="C326" t="str">
-        <v>飽和度</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>绝对比色</v>
+        <v>饱和度</v>
       </c>
       <c r="C327" t="str">
-        <v>絕對比色</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>特性文件统计</v>
+        <v>绝对比色</v>
       </c>
       <c r="C328" t="str">
-        <v>特性檔統計</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C329" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C330" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>渲染意图</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C331" t="str">
-        <v>轉換意圖</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>渲染意图</v>
       </c>
       <c r="C332" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>往返 ΔE</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C333" t="str">
-        <v>往返 ΔE</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C334" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>均值</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C335" t="str">
-        <v>平均</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>均值</v>
       </c>
       <c r="C336" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
       <c r="C337" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
       <c r="C338" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
       <c r="C339" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>分析</v>
       </c>
       <c r="C340" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>绘图</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C341" t="str">
-        <v>繪圖</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>原始输出</v>
+        <v>绘图</v>
       </c>
       <c r="C342" t="str">
-        <v>原始輸出</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>原始输出</v>
       </c>
       <c r="C343" t="str">
-        <v>XML</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>曲线</v>
+        <v>JSON</v>
       </c>
       <c r="C345" t="str">
-        <v>曲線</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>输入曲线</v>
+        <v>曲线</v>
       </c>
       <c r="C346" t="str">
-        <v>輸入曲線</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>输出曲线</v>
+        <v>输入曲线</v>
       </c>
       <c r="C347" t="str">
-        <v>輸出曲線</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>CLUT 图像</v>
+        <v>输出曲线</v>
       </c>
       <c r="C348" t="str">
-        <v>CLUT 影像</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>色域图像</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C349" t="str">
-        <v>色域影像</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>色度</v>
+        <v>色域图像</v>
       </c>
       <c r="C350" t="str">
-        <v>色度</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>散点图</v>
+        <v>色度</v>
       </c>
       <c r="C351" t="str">
-        <v>散佈圖</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>色调响应曲线</v>
+        <v>散点图</v>
       </c>
       <c r="C352" t="str">
-        <v>色調響應曲線</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>曲线表</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C353" t="str">
-        <v>曲線表</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>表格</v>
+        <v>曲线表</v>
       </c>
       <c r="C354" t="str">
-        <v>表格</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>数据</v>
+        <v>表格</v>
       </c>
       <c r="C355" t="str">
-        <v>資料</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>求值</v>
+        <v>数据</v>
       </c>
       <c r="C356" t="str">
-        <v>求值</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>加载中…</v>
+        <v>求值</v>
       </c>
       <c r="C357" t="str">
-        <v>載入中…</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>输入</v>
+        <v>加载中…</v>
       </c>
       <c r="C358" t="str">
-        <v>輸入</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>输出</v>
+        <v>输入</v>
       </c>
       <c r="C359" t="str">
-        <v>輸出</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>浮点值</v>
+        <v>输出</v>
       </c>
       <c r="C360" t="str">
-        <v>浮點值</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>网格点</v>
+        <v>浮点值</v>
       </c>
       <c r="C361" t="str">
-        <v>網格點</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>归一化</v>
+        <v>网格点</v>
       </c>
       <c r="C362" t="str">
-        <v>正規化</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>可读值</v>
+        <v>归一化</v>
       </c>
       <c r="C363" t="str">
-        <v>可讀值</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>设备 → PCS</v>
+        <v>可读值</v>
       </c>
       <c r="C364" t="str">
-        <v>裝置 → PCS</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → 设备</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C365" t="str">
-        <v>PCS → 裝置</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>无 CLUT 网格</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C366" t="str">
-        <v>無 CLUT 網格</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>加载中…</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C367" t="str">
-        <v>載入中…</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>加载中…</v>
       </c>
       <c r="C368" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C369" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C370" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C371" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C372" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C373" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C374" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C375" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
       <c r="C376" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>质量</v>
+        <v>符合性</v>
       </c>
       <c r="C377" t="str">
-        <v>品質</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>报告</v>
+        <v>质量</v>
       </c>
       <c r="C378" t="str">
-        <v>報告</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C379" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C380" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C381" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C382" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C383" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C384" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C385" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C386" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C387" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C388" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C389" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C390" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C391" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C392" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C393" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C394" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C395" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C396" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C397" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C398" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C399" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C400" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C401" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C402" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C403" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C404" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C405" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C406" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C407" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C408" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C409" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C410" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C411" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C412" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C413" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C414" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C415" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C416" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C417" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C418" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C419" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C420" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C421" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C422" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C423" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C424" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C425" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C426" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C427" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C428" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C429" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C430" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C431" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C432" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C433" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C434" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C435" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C436" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C437" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C438" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C439" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C440" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C441" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C442" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C443" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C444" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C445" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C446" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C447" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C448" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C449" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C450" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C451" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C452" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C453" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C454" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C455" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C456" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C457" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C458" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C459" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C460" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C461" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C462" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C463" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C464" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C465" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C466" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C466" t="str">
+      <c r="C467" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C706"/>
+  <dimension ref="A1:C707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4628,35 +4628,35 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>链中包含 HDR 配置文件</v>
+        <v>链中包含 HDR ColorSpace 配置文件</v>
       </c>
       <c r="C384" t="str">
-        <v>鏈中包含 HDR 設定檔</v>
+        <v>鏈中包含 HDR ColorSpace 設定檔</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>通过 HDR 配置文件的转换会使用其 AToB0Tag——即 8.10.6 条款要求的固化 SDR 渲染——因为 8.10.1 条款不允许其包含 TRC 标签。结果是该回退，而非 HDR 行为。</v>
+        <v>通过 HDR 配置文件的转换会使用其 AToB0Tag——即 8.7.1.5 条款要求的固化 SDR 渲染——因为 ColorSpace 配置文件本身不含 TRC 标签。结果是该回退，而非 HDR 行为。</v>
       </c>
       <c r="C385" t="str">
-        <v>透過 HDR 設定檔的轉換會使用其 AToB0Tag——即 8.10.6 條款要求的固化 SDR 算繪——因為 8.10.1 條款不允許其包含 TRC 標籤。結果是該回退，而非 HDR 行為。</v>
+        <v>透過 HDR 設定檔的轉換會使用其 AToB0Tag——即 8.7.1.5 條款要求的固化 SDR 算繪——因為 ColorSpace 設定檔本身不含 TRC 標籤。結果是該回退，而非 HDR 行為。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>这些是 HDR 配置文件，不含 TRC 标签，因此色域由 AToB0Tag 构建——即 8.10.6 条款要求为无 HDR 处理的消费者提供的固化 SDR 渲染。这不是配置文件的 HDR 色域，后者无法在有界 PCS 中绘制。</v>
+        <v>这些是 HDR 配置文件，不含 TRC 标签，因此色域由 AToB0Tag 构建——即 8.7.1.5 条款要求为无 HDR 处理的消费者提供的固化 SDR 渲染。这不是配置文件的 HDR 色域，后者无法在有界 PCS 中绘制。</v>
       </c>
       <c r="C386" t="str">
-        <v>這些是 HDR 設定檔，不含 TRC 標籤，因此色域由 AToB0Tag 建構——即 8.10.6 條款要求為無 HDR 處理的消費者提供的固化 SDR 算繪。這不是設定檔的 HDR 色域，後者無法在有界 PCS 中繪製。</v>
+        <v>這些是 HDR 設定檔，不含 TRC 標籤，因此色域由 AToB0Tag 建構——即 8.7.1.5 條款要求為無 HDR 處理的消費者提供的固化 SDR 算繪。這不是設定檔的 HDR 色域，後者無法在有界 PCS 中繪製。</v>
       </c>
     </row>
     <row r="387">
@@ -6245,13 +6245,13 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 条）</v>
+        <v>文件 1.0 = 1 cd/m²（ICC.1 第 8.7.1.2 a 条）</v>
       </c>
       <c r="C531" t="str">
-        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.10.2 a 條）</v>
+        <v>檔案 1.0 = 1 cd/m²（ICC.1 第 8.7.1.2 a 條）</v>
       </c>
     </row>
     <row r="532">
@@ -6333,13 +6333,13 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>自动（第 8.10.3 条排序）</v>
+        <v>自动（第 8.7.1.3 条排序）</v>
       </c>
       <c r="C539" t="str">
-        <v>自動（第 8.10.3 條排序）</v>
+        <v>自動（第 8.7.1.3 條排序）</v>
       </c>
     </row>
     <row r="540">
@@ -6421,13 +6421,13 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>HDR 配置文件</v>
+        <v>HDR ColorSpace 配置文件</v>
       </c>
       <c r="C547" t="str">
-        <v>HDR 描述檔</v>
+        <v>HDR ColorSpace 描述檔</v>
       </c>
     </row>
     <row r="548">
@@ -6454,1734 +6454,1745 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>HDR 配置文件——线性传递函数</v>
+        <v>HDR ColorSpace 配置文件——线性传递函数</v>
       </c>
       <c r="C550" t="str">
-        <v>HDR 描述檔——線性傳遞函數</v>
+        <v>HDR ColorSpace 描述檔——線性傳遞函數</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>HDR 配置文件——PQ / HLG 传递函数</v>
+        <v>HDR ColorSpace 配置文件——PQ / HLG 传递函数</v>
       </c>
       <c r="C551" t="str">
-        <v>HDR 描述檔——PQ / HLG 傳遞函數</v>
+        <v>HDR ColorSpace 描述檔——PQ / HLG 傳遞函數</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR 配置文件。</v>
+        <v>{format} 存储的是线性光，因此只能指定传递函数为线性的 HDR ColorSpace 配置文件。</v>
       </c>
       <c r="C552" t="str">
-        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR 描述檔。</v>
+        <v>{format} 儲存的是線性光，因此只能指定傳遞函數為線性的 HDR ColorSpace 描述檔。</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>池中有 {n} 个 PQ/HLG HDR 配置文件未提供——配置文件面板将它们列在“HDR 配置文件 › 非线性传递函数”下。</v>
+        <v>池中有 {n} 个 PQ/HLG HDR ColorSpace 配置文件未提供——配置文件面板将它们列在“HDR ColorSpace 配置文件 › 非线性传递函数”下。</v>
       </c>
       <c r="C553" t="str">
-        <v>池中有 {n} 個 PQ/HLG HDR 描述檔未提供——描述檔面板將它們列在「HDR 描述檔 › 非線性傳遞函數」下。</v>
+        <v>池中有 {n} 個 PQ/HLG HDR ColorSpace 描述檔未提供——描述檔面板將它們列在「HDR ColorSpace 描述檔 › 非線性傳遞函數」下。</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>池中尚无线性传递函数的 HDR 配置文件；配置文件面板按传递函数对 HDR 配置文件分组。</v>
+        <v>池中尚无线性传递函数的 HDR ColorSpace 配置文件；配置文件面板按传递函数对 HDR ColorSpace 配置文件分组。</v>
       </c>
       <c r="C554" t="str">
-        <v>池中尚無線性傳遞函數的 HDR 描述檔；描述檔面板依傳遞函數將 HDR 描述檔分組。</v>
+        <v>池中尚無線性傳遞函數的 HDR ColorSpace 描述檔；描述檔面板依傳遞函數將 HDR ColorSpace 描述檔分組。</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.10.3 条）。</v>
+        <v>未指定原色：此版本无 HDR 路径</v>
       </c>
       <c r="C555" t="str">
-        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.10.3 條）。</v>
+        <v>未指定原色：此版本無 HDR 路徑</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>显示余量</v>
+        <v>IccProfLib 拒绝应用此增益曲线：{why}。CMM 会退回到下一个色调映射描述符（第 8.7.1.3 条）。</v>
       </c>
       <c r="C556" t="str">
-        <v>顯示餘量</v>
+        <v>IccProfLib 拒絕套用此增益曲線：{why}。CMM 會退回下一個色調映射描述子（第 8.7.1.3 條）。</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
+        <v>显示余量</v>
       </c>
       <c r="C557" t="str">
-        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
+        <v>顯示餘量</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>基准</v>
+        <v>{n} 档（≈ 参考白的 {r} 倍）</v>
       </c>
       <c r="C558" t="str">
-        <v>基準</v>
+        <v>{n} 檔（≈ 參考白的 {r} 倍）</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>通过色彩引擎预览</v>
+        <v>基准</v>
       </c>
       <c r="C559" t="str">
-        <v>透過色彩引擎預覽</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>原始效果（基线 {h} 档，无增益）</v>
+        <v>通过色彩引擎预览</v>
       </c>
       <c r="C560" t="str">
-        <v>原始效果（基準 {h} 檔，無增益）</v>
+        <v>透過色彩引擎預覽</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>针对 {h} 档色调映射</v>
+        <v>原始效果（基线 {h} 档，无增益）</v>
       </c>
       <c r="C561" t="str">
-        <v>針對 {h} 檔色調對應</v>
+        <v>原始效果（基準 {h} 檔，無增益）</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
+        <v>针对 {h} 档色调映射</v>
       </c>
       <c r="C562" t="str">
-        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
+        <v>針對 {h} 檔色調對應</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>参考白</v>
+        <v>同一组测试像素（{transfer} 信号从左到右递增：灰色，然后 R、G、B、Y、C、M）经过 IccProfLib 的 HDR 变换。两条色带都限制在 HDR 参考白的 {r} 倍，即具有 {h} 档余量的显示器所能显示的效果：上方色带被截平的地方，增益曲线会平滑压缩高光。</v>
       </c>
       <c r="C563" t="str">
-        <v>參考白</v>
+        <v>同一組測試像素（{transfer} 訊號由左至右遞增：灰色，接著 R、G、B、Y、C、M）經過 IccProfLib 的 HDR 轉換。兩條色帶都限制在 HDR 參考白的 {r} 倍，即具有 {h} 檔餘裕的顯示器所能呈現的效果：上方色帶被截平之處，增益曲線會平滑壓縮亮部。</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>显示器峰值</v>
+        <v>参考白</v>
       </c>
       <c r="C564" t="str">
-        <v>顯示器峰值</v>
+        <v>參考白</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>预览不可用：{why}</v>
+        <v>显示器峰值</v>
       </c>
       <c r="C565" t="str">
-        <v>無法預覽：{why}</v>
+        <v>顯示器峰值</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
+        <v>预览不可用：{why}</v>
       </c>
       <c r="C566" t="str">
-        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
+        <v>無法預覽：{why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>所有余量下的增益</v>
+        <v>色彩引擎未对此配置文件采用 HDR 路径</v>
       </c>
       <c r="C567" t="str">
-        <v>所有餘裕下的增益</v>
+        <v>色彩引擎未對此描述檔採用 HDR 路徑</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
+        <v>所有余量下的增益</v>
       </c>
       <c r="C568" t="str">
-        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
+        <v>所有餘裕下的增益</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>输入（相对 HDR 参考白的档数）</v>
+        <v>在每个显示余量下施加于灰色输入的增益：蓝色表示压缩，红色表示扩展，白色表示不变。点线标出标签中的曲线，实线为基线，琥珀色线为滑块；虚线对角线是输入达到显示器峰值的位置。点击可移动滑块。</v>
       </c>
       <c r="C569" t="str">
-        <v>輸入（相對 HDR 參考白的檔數）</v>
+        <v>在每個顯示餘裕下套用於灰色輸入的增益：藍色代表壓縮，紅色代表擴展，白色代表不變。點線標示標籤中的曲線，實線為基準，琥珀色線為滑桿；虛線對角線是輸入達到顯示器峰值的位置。按一下可移動滑桿。</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>显示余量（档）</v>
+        <v>输入（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C570" t="str">
-        <v>顯示餘裕（檔）</v>
+        <v>輸入（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>增益（档）</v>
+        <v>显示余量（档）</v>
       </c>
       <c r="C571" t="str">
-        <v>增益（檔）</v>
+        <v>顯示餘裕（檔）</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>标签中的曲线</v>
+        <v>增益（档）</v>
       </c>
       <c r="C572" t="str">
-        <v>標籤中的曲線</v>
+        <v>增益（檔）</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>基线</v>
+        <v>标签中的曲线</v>
       </c>
       <c r="C573" t="str">
-        <v>基準</v>
+        <v>標籤中的曲線</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>滑块</v>
+        <v>基线</v>
       </c>
       <c r="C574" t="str">
-        <v>滑桿</v>
+        <v>基準</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>输入 = 显示器峰值</v>
+        <v>滑块</v>
       </c>
       <c r="C575" t="str">
-        <v>輸入 = 顯示器峰值</v>
+        <v>滑桿</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>按余量的灰色色调曲线</v>
+        <v>输入 = 显示器峰值</v>
       </c>
       <c r="C576" t="str">
-        <v>依餘裕的灰色色調曲線</v>
+        <v>輸入 = 顯示器峰值</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
+        <v>按余量的灰色色调曲线</v>
       </c>
       <c r="C577" t="str">
-        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
+        <v>依餘裕的灰色色調曲線</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>输出（相对 HDR 参考白的档数）</v>
+        <v>标签存储的每个余量下的灰色色调曲线，从低（蓝）到高（红）着色，滑块对应曲线为琥珀色。两轴均以档为单位，对角线表示不变。</v>
       </c>
       <c r="C578" t="str">
-        <v>輸出（相對 HDR 參考白的檔數）</v>
+        <v>標籤儲存的每個餘裕下的灰色色調曲線，由低（藍）到高（紅）著色，滑桿對應曲線為琥珀色。兩軸皆以檔為單位，對角線表示不變。</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} 档</v>
+        <v>输出（相对 HDR 参考白的档数）</v>
       </c>
       <c r="C579" t="str">
-        <v>{h} 檔</v>
+        <v>輸出（相對 HDR 參考白的檔數）</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} 档（基线）</v>
+        <v>{h} 档</v>
       </c>
       <c r="C580" t="str">
-        <v>{h} 檔（基準）</v>
+        <v>{h} 檔</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>{h} 档（滑块）</v>
+        <v>{h} 档（基线）</v>
       </c>
       <c r="C581" t="str">
-        <v>{h} 檔（滑桿）</v>
+        <v>{h} 檔（基準）</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
+        <v>{h} 档（滑块）</v>
       </c>
       <c r="C582" t="str">
-        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
+        <v>{h} 檔（滑桿）</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
+        <v>标签中的曲线（按余量）：{list} 档。基准 {b} 档，HDR 参考白 {w} cd/m²。</v>
       </c>
       <c r="C583" t="str">
-        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
+        <v>標籤中的曲線（依餘量）：{list} 檔。基準 {b} 檔，HDR 參考白 {w} cd/m²。</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
+        <v>此余量超出标签中曲线的范围，因此原样使用最近的曲线——该库不会向外外推。</v>
       </c>
       <c r="C584" t="str">
-        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
+        <v>此餘量超出標籤中曲線的範圍，因此原樣使用最近的曲線——此程式庫不會向外外插。</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
+        <v>部分斜率是推导得出的（PCHIP），并未存储在标签中。该推导重建了一条 SMPTE 条款，因此这些曲线的形状应视为暂定。</v>
       </c>
       <c r="C585" t="str">
-        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
+        <v>部分斜率是推導而得（PCHIP），並未儲存在標籤中。此推導重建了一條 SMPTE 條款，因此這些曲線的形狀應視為暫定。</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
+        <v>该标签要求基于参考白的色调映射，因此其曲线由库构造而非从文件读取（一种委员会草案中的构造）。</v>
       </c>
       <c r="C586" t="str">
-        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
+        <v>此標籤要求以參考白為準的色調映射，因此其曲線由程式庫建構而非從檔案讀取（一種委員會草案中的建構）。</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
+        <v>没有替代图像：该标签不要求色调映射，只要求限制在显示器的色域体积内。</v>
       </c>
       <c r="C587" t="str">
-        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
+        <v>沒有替代影像：此標籤不要求色調映射，只要求限制在顯示器的色彩體積內。</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>{h} 档处的曲线（无增益）</v>
+        <v>在此余量下混合的两条曲线对颜色通道的混合方式不同，因此无法绘制单一增益曲线。下方的色调曲线仍然精确。</v>
       </c>
       <c r="C588" t="str">
-        <v>{h} 檔處的曲線（無增益）</v>
+        <v>在此餘量下混合的兩條曲線對色彩通道的混合方式不同，因此無法繪製單一增益曲線。下方的色調曲線仍然精確。</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>{h} 档处的曲线</v>
+        <v>{h} 档处的曲线（无增益）</v>
       </c>
       <c r="C589" t="str">
-        <v>{h} 檔處的曲線</v>
+        <v>{h} 檔處的曲線（無增益）</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>在 {h} 档处应用</v>
+        <v>{h} 档处的曲线</v>
       </c>
       <c r="C590" t="str">
-        <v>在 {h} 檔處套用</v>
+        <v>{h} 檔處的曲線</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>此余量下应用的增益</v>
+        <v>在 {h} 档处应用</v>
       </c>
       <c r="C591" t="str">
-        <v>此餘量下套用的增益</v>
+        <v>在 {h} 檔處套用</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>混合输入（线性，1.0 = HDR 参考白）</v>
+        <v>此余量下应用的增益</v>
       </c>
       <c r="C592" t="str">
-        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
+        <v>此餘量下套用的增益</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>增益（log2 档）</v>
+        <v>混合输入（线性，1.0 = HDR 参考白）</v>
       </c>
       <c r="C593" t="str">
-        <v>增益（log2 檔）</v>
+        <v>混合輸入（線性，1.0 = HDR 參考白）</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>此余量下的灰阶色调曲线</v>
+        <v>增益（log2 档）</v>
       </c>
       <c r="C594" t="str">
-        <v>此餘量下的灰階色調曲線</v>
+        <v>增益（log2 檔）</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>输入（× HDR 参考白）</v>
+        <v>此余量下的灰阶色调曲线</v>
       </c>
       <c r="C595" t="str">
-        <v>輸入（× HDR 參考白）</v>
+        <v>此餘量下的灰階色調曲線</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>输出（× HDR 参考白）</v>
+        <v>输入（× HDR 参考白）</v>
       </c>
       <c r="C596" t="str">
-        <v>輸出（× HDR 參考白）</v>
+        <v>輸入（× HDR 參考白）</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>不变</v>
+        <v>输出（× HDR 参考白）</v>
       </c>
       <c r="C597" t="str">
-        <v>不變</v>
+        <v>輸出（× HDR 參考白）</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>{h} 档处的显示器峰值</v>
+        <v>不变</v>
       </c>
       <c r="C598" t="str">
-        <v>{h} 檔處的顯示器峰值</v>
+        <v>不變</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>{h} 档处的输出</v>
+        <v>{h} 档处的显示器峰值</v>
       </c>
       <c r="C599" t="str">
-        <v>{h} 檔處的輸出</v>
+        <v>{h} 檔處的顯示器峰值</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
+        <v>{h} 档处的输出</v>
       </c>
       <c r="C600" t="str">
-        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
+        <v>{h} 檔處的輸出</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>识别显示器</v>
+        <v>窗口移到 HDR、色域或像素比不同的屏幕时，这些信息会自动刷新。</v>
       </c>
       <c r="C601" t="str">
-        <v>識別顯示器</v>
+        <v>視窗移到 HDR、色域或像素比不同的螢幕時，這些資訊會自動重新整理。</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
+        <v>识别显示器</v>
       </c>
       <c r="C602" t="str">
-        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
+        <v>識別顯示器</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>正在跟踪此窗口所在的显示器。</v>
+        <v>请求权限以获知此窗口位于哪台显示器，这样在两台看起来相同的屏幕之间也能刷新，并在浏览器提供时显示 HDR 余量。</v>
       </c>
       <c r="C603" t="str">
-        <v>正在追蹤此視窗所在的顯示器。</v>
+        <v>請求權限以得知此視窗位於哪台顯示器，這樣在兩台看起來相同的螢幕之間也能重新整理，並在瀏覽器提供時顯示 HDR 餘量。</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
+        <v>正在跟踪此窗口所在的显示器。</v>
       </c>
       <c r="C604" t="str">
-        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
+        <v>正在追蹤此視窗所在的顯示器。</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
+        <v>识别显示器的权限被拒绝。可在此网站的设置中更改。</v>
       </c>
       <c r="C605" t="str">
-        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
+        <v>識別顯示器的權限遭拒。可在此網站的設定中變更。</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>无法识别显示器。</v>
+        <v>此浏览器无法识别显示器；仅适用上方的自动刷新。</v>
       </c>
       <c r="C606" t="str">
-        <v>無法識別顯示器。</v>
+        <v>此瀏覽器無法識別顯示器；僅適用上方的自動重新整理。</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>显示事件</v>
+        <v>无法识别显示器。</v>
       </c>
       <c r="C607" t="str">
-        <v>顯示事件</v>
+        <v>無法識別顯示器。</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>暂无事件。请将窗口拖到另一台显示器。</v>
+        <v>显示事件</v>
       </c>
       <c r="C608" t="str">
-        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
+        <v>顯示事件</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>色度基色</v>
+        <v>暂无事件。请将窗口拖到另一台显示器。</v>
       </c>
       <c r="C609" t="str">
-        <v>色度基色</v>
+        <v>尚無事件。請將視窗拖到另一台顯示器。</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>传递特性</v>
+        <v>色度基色</v>
       </c>
       <c r="C610" t="str">
-        <v>轉換特性</v>
+        <v>色度基色</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>矩阵系数</v>
+        <v>传递特性</v>
       </c>
       <c r="C611" t="str">
-        <v>矩陣係數</v>
+        <v>轉換特性</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>视频全范围标志</v>
+        <v>矩阵系数</v>
       </c>
       <c r="C612" t="str">
-        <v>視訊全範圍旗標</v>
+        <v>矩陣係數</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>全范围</v>
+        <v>视频全范围标志</v>
       </c>
       <c r="C613" t="str">
-        <v>全範圍</v>
+        <v>視訊全範圍旗標</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>有限范围</v>
+        <v>全范围</v>
       </c>
       <c r="C614" t="str">
-        <v>有限範圍</v>
+        <v>全範圍</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>ITU-T H.273 未分配</v>
+        <v>有限范围</v>
       </c>
       <c r="C615" t="str">
-        <v>ITU-T H.273 未指派</v>
+        <v>有限範圍</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
+        <v>ITU-T H.273 未分配</v>
       </c>
       <c r="C616" t="str">
-        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
+        <v>ITU-T H.273 未指派</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>此标签的四个保留字节并非全为零。</v>
+        <v>基色 2（未指定）将基色交由配置文件本身决定——基色取自着色剂标签，而非此标签。</v>
       </c>
       <c r="C617" t="str">
-        <v>此標籤的四個保留位元組並非全為零。</v>
+        <v>基色 2（未指定）將基色交由設定檔本身決定——基色取自著色劑標籤，而非此標籤。</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>报告</v>
+        <v>此标签的四个保留字节并非全为零。</v>
       </c>
       <c r="C618" t="str">
-        <v>報告</v>
+        <v>此標籤的四個保留位元組並非全為零。</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C619" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C620" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C621" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C622" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C623" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C624" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C625" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C626" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C627" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C628" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C629" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C630" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C631" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C632" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C633" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C634" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C635" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C636" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C637" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C638" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C639" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C640" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C641" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C642" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C643" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C644" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C645" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C646" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C647" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C648" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C649" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C650" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C651" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C652" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C653" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C654" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C655" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C656" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C657" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C658" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C659" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C660" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C661" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C662" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C663" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C664" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C665" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C666" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C667" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C668" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C669" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C670" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C671" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C672" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C673" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C674" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C675" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C676" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C677" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C678" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C679" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C680" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C681" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C682" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C683" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C684" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C685" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C686" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C687" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C688" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C689" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C690" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C691" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C692" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C693" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C694" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C695" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C696" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C697" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C698" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C699" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C700" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C701" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C702" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C703" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C704" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C705" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C706" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C706" t="str">
+      <c r="C707" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C707"/>
   </ignoredErrors>
 </worksheet>
 </file>